--- a/output/Tables/7000 steps/add_cases_prev_7000steps.xlsx
+++ b/output/Tables/7000 steps/add_cases_prev_7000steps.xlsx
@@ -1,21 +1,101 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10119"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ines/Documents/PhD/PROJETS/MARCHE/steps/output/Tables/7000 steps/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB17437F-2D0C-5341-966F-0E9383ACC844}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="-36240" yWindow="-680" windowWidth="30920" windowHeight="11580" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="23">
+  <si>
+    <t>disease</t>
+  </si>
+  <si>
+    <t>sex</t>
+  </si>
+  <si>
+    <t>tot_cases_2019</t>
+  </si>
+  <si>
+    <t>tot_cases_se_2019</t>
+  </si>
+  <si>
+    <t>tot_cases_low_2019</t>
+  </si>
+  <si>
+    <t>tot_cases_up_2019</t>
+  </si>
+  <si>
+    <t>tot_cases_RECO</t>
+  </si>
+  <si>
+    <t>tot_cases_se_RECO</t>
+  </si>
+  <si>
+    <t>tot_cases_low_RECO</t>
+  </si>
+  <si>
+    <t>tot_cases_up_RECO</t>
+  </si>
+  <si>
+    <t>tot_cases_RECO_diff</t>
+  </si>
+  <si>
+    <t>tot_cases_se_RECO_diff</t>
+  </si>
+  <si>
+    <t>tot_cases_low_RECO_diff</t>
+  </si>
+  <si>
+    <t>tot_cases_up_RECO_diff</t>
+  </si>
+  <si>
+    <t>mort</t>
+  </si>
+  <si>
+    <t>Female</t>
+  </si>
+  <si>
+    <t>Male</t>
+  </si>
+  <si>
+    <t>cvd</t>
+  </si>
+  <si>
+    <t>bc</t>
+  </si>
+  <si>
+    <t>cancer</t>
+  </si>
+  <si>
+    <t>diab2</t>
+  </si>
+  <si>
+    <t>dem</t>
+  </si>
+  <si>
+    <t>dep</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -63,13 +143,21 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -107,7 +195,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -141,6 +229,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -175,9 +264,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -350,92 +440,74 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:N15"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="3" max="3" width="13.1640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.1640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.6640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="17" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="16" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="16.6640625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="19.1640625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="20.33203125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="19.5" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>disease</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>sex</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>tot_cases_2019</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>tot_cases_se_2019</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>tot_cases_low_2019</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>tot_cases_up_2019</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>tot_cases_RECO</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>tot_cases_se_RECO</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>tot_cases_low_RECO</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>tot_cases_up_RECO</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>tot_cases_RECO_diff</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>tot_cases_se_RECO_diff</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>tot_cases_low_RECO_diff</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>tot_cases_up_RECO_diff</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>mort</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Female</t>
-        </is>
+    <row r="1" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2" t="s">
+        <v>15</v>
       </c>
       <c r="C2">
         <v>15936.81738220334</v>
@@ -447,43 +519,39 @@
         <v>13465.37902192904</v>
       </c>
       <c r="F2">
-        <v>18235.8410572486</v>
+        <v>18235.841057248599</v>
       </c>
       <c r="G2">
-        <v>66398.76344547827</v>
+        <v>66398.763445478267</v>
       </c>
       <c r="H2">
-        <v>6115.251494207865</v>
+        <v>6115.2514942078651</v>
       </c>
       <c r="I2">
-        <v>57325.170730447</v>
+        <v>57325.170730446996</v>
       </c>
       <c r="J2">
-        <v>75035.38575438136</v>
+        <v>75035.385754381365</v>
       </c>
       <c r="K2">
-        <v>50461.94606327493</v>
+        <v>50461.946063274932</v>
       </c>
       <c r="L2">
-        <v>4457.460085457389</v>
+        <v>4457.4600854573891</v>
       </c>
       <c r="M2">
-        <v>43859.79170851796</v>
+        <v>43859.791708517958</v>
       </c>
       <c r="N2">
-        <v>56799.54469713276</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>mort</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Male</t>
-        </is>
+        <v>56799.544697132762</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" t="s">
+        <v>16</v>
       </c>
       <c r="C3">
         <v>21720.57273946307</v>
@@ -492,16 +560,16 @@
         <v>1961.307719038575</v>
       </c>
       <c r="E3">
-        <v>18430.69426501219</v>
+        <v>18430.694265012189</v>
       </c>
       <c r="F3">
-        <v>24778.78513585294</v>
+        <v>24778.785135852941</v>
       </c>
       <c r="G3">
         <v>101339.8996129359</v>
       </c>
       <c r="H3">
-        <v>7426.082993779324</v>
+        <v>7426.0829937793242</v>
       </c>
       <c r="I3">
         <v>87491.4945048355</v>
@@ -510,55 +578,51 @@
         <v>114521.3866220694</v>
       </c>
       <c r="K3">
-        <v>79619.32687347288</v>
+        <v>79619.326873472877</v>
       </c>
       <c r="L3">
-        <v>5464.775274740749</v>
+        <v>5464.7752747407494</v>
       </c>
       <c r="M3">
-        <v>69060.80023982331</v>
+        <v>69060.800239823307</v>
       </c>
       <c r="N3">
-        <v>89742.60148621647</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>cvd</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Female</t>
-        </is>
+        <v>89742.601486216474</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B4" t="s">
+        <v>15</v>
       </c>
       <c r="C4">
-        <v>4568.353925209686</v>
+        <v>4568.3539252096862</v>
       </c>
       <c r="D4">
-        <v>415.3966729889607</v>
+        <v>415.39667298896069</v>
       </c>
       <c r="E4">
-        <v>2849.464034995572</v>
+        <v>2849.4640349955721</v>
       </c>
       <c r="F4">
-        <v>6238.16508253809</v>
+        <v>6238.1650825380902</v>
       </c>
       <c r="G4">
         <v>21087.17857458489</v>
       </c>
       <c r="H4">
-        <v>1575.26491287042</v>
+        <v>1575.2649128704199</v>
       </c>
       <c r="I4">
         <v>12932.80264864024</v>
       </c>
       <c r="J4">
-        <v>28548.6070925464</v>
+        <v>28548.607092546401</v>
       </c>
       <c r="K4">
-        <v>16518.8246493752</v>
+        <v>16518.824649375201</v>
       </c>
       <c r="L4">
         <v>1159.868239881459</v>
@@ -567,115 +631,79 @@
         <v>10083.33861364467</v>
       </c>
       <c r="N4">
-        <v>22310.44201000832</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>cvd</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Male</t>
-        </is>
+        <v>22310.442010008319</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>17</v>
+      </c>
+      <c r="B5" t="s">
+        <v>16</v>
       </c>
       <c r="C5">
-        <v>5967.064047088697</v>
+        <v>5967.0640470886974</v>
       </c>
       <c r="D5">
-        <v>460.5257894142127</v>
+        <v>460.52578941421268</v>
       </c>
       <c r="E5">
         <v>3836.491649555051</v>
       </c>
       <c r="F5">
-        <v>8013.065296051683</v>
+        <v>8013.0652960516827</v>
       </c>
       <c r="G5">
-        <v>32689.22736066739</v>
+        <v>32689.227360667392</v>
       </c>
       <c r="H5">
-        <v>2078.28541757923</v>
+        <v>2078.2854175792299</v>
       </c>
       <c r="I5">
-        <v>20048.35899201673</v>
+        <v>20048.358992016729</v>
       </c>
       <c r="J5">
-        <v>44255.89249779395</v>
+        <v>44255.892497793953</v>
       </c>
       <c r="K5">
-        <v>26722.16331357869</v>
+        <v>26722.163313578691</v>
       </c>
       <c r="L5">
-        <v>1617.759628165017</v>
+        <v>1617.7596281650169</v>
       </c>
       <c r="M5">
         <v>16211.86734246167</v>
       </c>
       <c r="N5">
-        <v>36242.82720174227</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>bc</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Female</t>
-        </is>
+        <v>36242.827201742271</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>18</v>
+      </c>
+      <c r="B6" t="s">
+        <v>15</v>
       </c>
       <c r="C6">
         <v>3629.613692065931</v>
       </c>
       <c r="D6">
-        <v>276.4774555870436</v>
+        <v>276.47745558704361</v>
       </c>
       <c r="E6">
-        <v>4578.371663237075</v>
+        <v>4578.3716632370752</v>
       </c>
       <c r="F6">
-        <v>1987.566796274164</v>
-      </c>
-      <c r="G6">
-        <v>3629.613692065931</v>
-      </c>
-      <c r="H6">
-        <v>276.4774555870436</v>
-      </c>
-      <c r="I6">
-        <v>4578.371663237075</v>
-      </c>
-      <c r="J6">
-        <v>1987.566796274164</v>
-      </c>
-      <c r="K6">
-        <v>0</v>
-      </c>
-      <c r="L6">
-        <v>-5.684341886080801E-14</v>
-      </c>
-      <c r="M6">
-        <v>0</v>
-      </c>
-      <c r="N6">
-        <v>-4.547473508864641E-13</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>bc</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Male</t>
-        </is>
+        <v>1987.5667962741641</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>18</v>
+      </c>
+      <c r="B7" t="s">
+        <v>16</v>
       </c>
       <c r="C7">
         <v>0</v>
@@ -689,98 +717,66 @@
       <c r="F7">
         <v>0</v>
       </c>
-      <c r="G7">
-        <v>0</v>
-      </c>
-      <c r="H7">
-        <v>0</v>
-      </c>
-      <c r="I7">
-        <v>0</v>
-      </c>
-      <c r="J7">
-        <v>0</v>
-      </c>
-      <c r="K7">
-        <v>0</v>
-      </c>
-      <c r="L7">
-        <v>0</v>
-      </c>
-      <c r="M7">
-        <v>0</v>
-      </c>
-      <c r="N7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>cancer</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Female</t>
-        </is>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>19</v>
+      </c>
+      <c r="B8" t="s">
+        <v>15</v>
       </c>
       <c r="C8">
-        <v>2347.224404253075</v>
+        <v>2347.2244042530751</v>
       </c>
       <c r="D8">
-        <v>182.9556301445923</v>
+        <v>182.95563014459231</v>
       </c>
       <c r="E8">
-        <v>73.16137126765993</v>
+        <v>73.161371267659931</v>
       </c>
       <c r="F8">
-        <v>4750.237302797428</v>
+        <v>4750.2373027974281</v>
       </c>
       <c r="G8">
         <v>10676.70647867835</v>
       </c>
       <c r="H8">
-        <v>656.5097886851622</v>
+        <v>656.50978868516222</v>
       </c>
       <c r="I8">
-        <v>-110.1153824553654</v>
+        <v>-110.11538245536541</v>
       </c>
       <c r="J8">
-        <v>21767.73203914123</v>
+        <v>21767.732039141229</v>
       </c>
       <c r="K8">
         <v>8329.482074425272</v>
       </c>
       <c r="L8">
-        <v>473.5541585405699</v>
+        <v>473.55415854056992</v>
       </c>
       <c r="M8">
-        <v>-183.2767537230254</v>
+        <v>-183.27675372302539</v>
       </c>
       <c r="N8">
         <v>17017.4947363438</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>cancer</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Male</t>
-        </is>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>19</v>
+      </c>
+      <c r="B9" t="s">
+        <v>16</v>
       </c>
       <c r="C9">
-        <v>2529.569307391621</v>
+        <v>2529.5693073916209</v>
       </c>
       <c r="D9">
-        <v>191.5269402468302</v>
+        <v>191.52694024683021</v>
       </c>
       <c r="E9">
-        <v>34.23615350539696</v>
+        <v>34.236153505396963</v>
       </c>
       <c r="F9">
         <v>5106.121412363852</v>
@@ -789,85 +785,77 @@
         <v>12750.78908252082</v>
       </c>
       <c r="H9">
-        <v>812.0306083441208</v>
+        <v>812.03060834412076</v>
       </c>
       <c r="I9">
-        <v>-131.5066607135276</v>
+        <v>-131.50666071352759</v>
       </c>
       <c r="J9">
         <v>25996.3838652124</v>
       </c>
       <c r="K9">
-        <v>10221.2197751292</v>
+        <v>10221.219775129201</v>
       </c>
       <c r="L9">
-        <v>620.5036680972905</v>
+        <v>620.50366809729053</v>
       </c>
       <c r="M9">
-        <v>-165.7428142189246</v>
+        <v>-165.74281421892459</v>
       </c>
       <c r="N9">
         <v>20890.26245284855</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>diab2</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Female</t>
-        </is>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>20</v>
+      </c>
+      <c r="B10" t="s">
+        <v>15</v>
       </c>
       <c r="C10">
-        <v>3237.642755560177</v>
+        <v>3237.6427555601772</v>
       </c>
       <c r="D10">
         <v>260.9789878250358</v>
       </c>
       <c r="E10">
-        <v>-66.36838101779699</v>
+        <v>-66.368381017796992</v>
       </c>
       <c r="F10">
-        <v>6016.77774961595</v>
+        <v>6016.7777496159497</v>
       </c>
       <c r="G10">
-        <v>14609.69221040514</v>
+        <v>14609.692210405139</v>
       </c>
       <c r="H10">
-        <v>883.2828775745671</v>
+        <v>883.28287757456712</v>
       </c>
       <c r="I10">
-        <v>-232.3548881812114</v>
+        <v>-232.35488818121141</v>
       </c>
       <c r="J10">
         <v>27299.79210828945</v>
       </c>
       <c r="K10">
-        <v>11372.04945484496</v>
+        <v>11372.049454844961</v>
       </c>
       <c r="L10">
-        <v>622.3038897495313</v>
+        <v>622.30388974953132</v>
       </c>
       <c r="M10">
-        <v>-165.9865071634144</v>
+        <v>-165.98650716341439</v>
       </c>
       <c r="N10">
-        <v>21283.0143586735</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>diab2</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Male</t>
-        </is>
+        <v>21283.014358673499</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>20</v>
+      </c>
+      <c r="B11" t="s">
+        <v>16</v>
       </c>
       <c r="C11">
         <v>3222.915557927578</v>
@@ -876,13 +864,13 @@
         <v>238.7480035513384</v>
       </c>
       <c r="E11">
-        <v>-45.8080836867474</v>
+        <v>-45.808083686747402</v>
       </c>
       <c r="F11">
-        <v>5925.365518466964</v>
+        <v>5925.3655184669642</v>
       </c>
       <c r="G11">
-        <v>16823.58541287801</v>
+        <v>16823.585412878008</v>
       </c>
       <c r="H11">
         <v>1041.841811288914</v>
@@ -894,196 +882,180 @@
         <v>31436.69131924065</v>
       </c>
       <c r="K11">
-        <v>13600.66985495043</v>
+        <v>13600.669854950431</v>
       </c>
       <c r="L11">
-        <v>803.0938077375761</v>
+        <v>803.09380773757607</v>
       </c>
       <c r="M11">
-        <v>-221.756917075711</v>
+        <v>-221.75691707571099</v>
       </c>
       <c r="N11">
-        <v>25511.32580077369</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>dem</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Female</t>
-        </is>
+        <v>25511.325800773691</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>21</v>
+      </c>
+      <c r="B12" t="s">
+        <v>15</v>
       </c>
       <c r="C12">
-        <v>2384.448403736423</v>
+        <v>2384.4484037364232</v>
       </c>
       <c r="D12">
-        <v>303.0994159039039</v>
+        <v>303.09941590390389</v>
       </c>
       <c r="E12">
-        <v>1718.398198899412</v>
+        <v>1718.3981988994119</v>
       </c>
       <c r="F12">
-        <v>2981.24789460943</v>
+        <v>2981.2478946094302</v>
       </c>
       <c r="G12">
-        <v>11295.22216359617</v>
+        <v>11295.222163596171</v>
       </c>
       <c r="H12">
         <v>1272.159851681472</v>
       </c>
       <c r="I12">
-        <v>8177.773310166796</v>
+        <v>8177.7733101667964</v>
       </c>
       <c r="J12">
         <v>14005.53935045447</v>
       </c>
       <c r="K12">
-        <v>8910.773759859741</v>
+        <v>8910.7737598597414</v>
       </c>
       <c r="L12">
         <v>969.0604357775685</v>
       </c>
       <c r="M12">
-        <v>6459.375111267384</v>
+        <v>6459.3751112673845</v>
       </c>
       <c r="N12">
-        <v>11024.29145584504</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>dem</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Male</t>
-        </is>
+        <v>11024.291455845039</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>21</v>
+      </c>
+      <c r="B13" t="s">
+        <v>16</v>
       </c>
       <c r="C13">
         <v>1190.702010578538</v>
       </c>
       <c r="D13">
-        <v>137.0433326068824</v>
+        <v>137.04333260688239</v>
       </c>
       <c r="E13">
-        <v>858.7854577214898</v>
+        <v>858.78545772148982</v>
       </c>
       <c r="F13">
         <v>1486.42548531547</v>
       </c>
       <c r="G13">
-        <v>6108.10108827936</v>
+        <v>6108.1010882793598</v>
       </c>
       <c r="H13">
-        <v>571.3012458570594</v>
+        <v>571.30124585705937</v>
       </c>
       <c r="I13">
-        <v>4422.282743275283</v>
+        <v>4422.2827432752829</v>
       </c>
       <c r="J13">
-        <v>7573.755425914868</v>
+        <v>7573.7554259148683</v>
       </c>
       <c r="K13">
-        <v>4917.399077700822</v>
+        <v>4917.3990777008221</v>
       </c>
       <c r="L13">
-        <v>434.257913250177</v>
+        <v>434.25791325017701</v>
       </c>
       <c r="M13">
-        <v>3563.497285553793</v>
+        <v>3563.4972855537931</v>
       </c>
       <c r="N13">
-        <v>6087.329940599398</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>dep</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Female</t>
-        </is>
+        <v>6087.3299405993976</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>22</v>
+      </c>
+      <c r="B14" t="s">
+        <v>15</v>
       </c>
       <c r="C14">
         <v>132514.5131922857</v>
       </c>
       <c r="D14">
-        <v>9565.357379365007</v>
+        <v>9565.3573793650066</v>
       </c>
       <c r="E14">
-        <v>98674.44200563467</v>
+        <v>98674.442005634672</v>
       </c>
       <c r="F14">
-        <v>160176.1595485081</v>
+        <v>160176.15954850809</v>
       </c>
       <c r="G14">
-        <v>627401.4401708276</v>
+        <v>627401.44017082755</v>
       </c>
       <c r="H14">
-        <v>35468.71647922999</v>
+        <v>35468.716479229988</v>
       </c>
       <c r="I14">
-        <v>461939.5259119386</v>
+        <v>461939.52591193857</v>
       </c>
       <c r="J14">
-        <v>755869.0542637333</v>
+        <v>755869.05426373333</v>
       </c>
       <c r="K14">
-        <v>494886.9269785419</v>
+        <v>494886.92697854189</v>
       </c>
       <c r="L14">
-        <v>25903.35909986498</v>
+        <v>25903.359099864982</v>
       </c>
       <c r="M14">
-        <v>363265.083906304</v>
+        <v>363265.08390630397</v>
       </c>
       <c r="N14">
-        <v>595692.8947152252</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>dep</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Male</t>
-        </is>
+        <v>595692.89471522521</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
+        <v>22</v>
+      </c>
+      <c r="B15" t="s">
+        <v>16</v>
       </c>
       <c r="C15">
-        <v>45862.4334559237</v>
+        <v>45862.433455923703</v>
       </c>
       <c r="D15">
-        <v>3487.525465558493</v>
+        <v>3487.5254655584931</v>
       </c>
       <c r="E15">
-        <v>34205.12877766402</v>
+        <v>34205.128777664017</v>
       </c>
       <c r="F15">
-        <v>55395.18123943473</v>
+        <v>55395.181239434729</v>
       </c>
       <c r="G15">
-        <v>277727.4893059632</v>
+        <v>277727.48930596322</v>
       </c>
       <c r="H15">
-        <v>16149.36229350632</v>
+        <v>16149.362293506319</v>
       </c>
       <c r="I15">
-        <v>204483.5993806107</v>
+        <v>204483.59938061071</v>
       </c>
       <c r="J15">
-        <v>334595.3662898528</v>
+        <v>334595.36628985283</v>
       </c>
       <c r="K15">
         <v>231865.0558500395</v>
@@ -1092,10 +1064,10 @@
         <v>12661.83682794782</v>
       </c>
       <c r="M15">
-        <v>170278.4706029466</v>
+        <v>170278.47060294659</v>
       </c>
       <c r="N15">
-        <v>279200.185050418</v>
+        <v>279200.18505041802</v>
       </c>
     </row>
   </sheetData>

--- a/output/Tables/7000 steps/add_cases_prev_7000steps.xlsx
+++ b/output/Tables/7000 steps/add_cases_prev_7000steps.xlsx
@@ -594,22 +594,22 @@
         <v>4345382001.793251</v>
       </c>
       <c r="O2">
-        <v>66398.76344547827</v>
+        <v>68586.37060359692</v>
       </c>
       <c r="P2">
-        <v>57325.170730447</v>
+        <v>58710.64390858215</v>
       </c>
       <c r="Q2">
-        <v>75035.38575438136</v>
+        <v>77619.82193126234</v>
       </c>
       <c r="R2">
-        <v>118882.4624498344</v>
+        <v>122799.2240329562</v>
       </c>
       <c r="S2">
-        <v>102636.8128434906</v>
+        <v>105117.4081818382</v>
       </c>
       <c r="T2">
-        <v>134345.746313166</v>
+        <v>138973.0032199053</v>
       </c>
       <c r="U2">
         <v>0</v>
@@ -621,31 +621,31 @@
         <v>0</v>
       </c>
       <c r="X2">
-        <v>15811367505.82797</v>
+        <v>16332296796.38318</v>
       </c>
       <c r="Y2">
-        <v>13650696108.18425</v>
+        <v>13980615288.18448</v>
       </c>
       <c r="Z2">
-        <v>17867984259.65108</v>
+        <v>18483409428.2474</v>
       </c>
       <c r="AA2">
-        <v>50461.94606327493</v>
+        <v>52649.55322139358</v>
       </c>
       <c r="AB2">
-        <v>43859.79170851796</v>
+        <v>45245.26488665312</v>
       </c>
       <c r="AC2">
-        <v>56799.54469713276</v>
+        <v>59383.98087401374</v>
       </c>
       <c r="AD2">
-        <v>90290.2222158095</v>
+        <v>94206.98379893134</v>
       </c>
       <c r="AE2">
-        <v>78429.734844066</v>
+        <v>80910.3301824136</v>
       </c>
       <c r="AF2">
-        <v>101673.701186901</v>
+        <v>106300.9580936402</v>
       </c>
       <c r="AG2">
         <v>0</v>
@@ -657,13 +657,13 @@
         <v>0</v>
       </c>
       <c r="AJ2">
-        <v>12008599554.70266</v>
+        <v>12529528845.25787</v>
       </c>
       <c r="AK2">
-        <v>10431154734.26078</v>
+        <v>10761073914.26101</v>
       </c>
       <c r="AL2">
-        <v>13522602257.85783</v>
+        <v>14138027426.45415</v>
       </c>
     </row>
     <row r="3">
@@ -714,22 +714,22 @@
         <v>4380297498.956462</v>
       </c>
       <c r="O3">
-        <v>101339.8996129359</v>
+        <v>104678.695070751</v>
       </c>
       <c r="P3">
-        <v>87491.4945048355</v>
+        <v>89606.04763057169</v>
       </c>
       <c r="Q3">
-        <v>114521.3866220694</v>
+        <v>118465.835119762</v>
       </c>
       <c r="R3">
-        <v>155095.9907746791</v>
+        <v>160205.8615314264</v>
       </c>
       <c r="S3">
-        <v>133901.6525219916</v>
+        <v>137137.8774771607</v>
       </c>
       <c r="T3">
-        <v>175269.6419759695</v>
+        <v>181306.4364680289</v>
       </c>
       <c r="U3">
         <v>0</v>
@@ -741,31 +741,31 @@
         <v>0</v>
       </c>
       <c r="X3">
-        <v>20627766773.03232</v>
+        <v>21307379583.67971</v>
       </c>
       <c r="Y3">
-        <v>17808919785.42489</v>
+        <v>18239337704.46237</v>
       </c>
       <c r="Z3">
-        <v>23310862382.80394</v>
+        <v>24113756050.24784</v>
       </c>
       <c r="AA3">
-        <v>79619.32687347288</v>
+        <v>82958.12233128797</v>
       </c>
       <c r="AB3">
-        <v>69060.80023982331</v>
+        <v>71175.35336555949</v>
       </c>
       <c r="AC3">
-        <v>89742.60148621647</v>
+        <v>93687.04998390902</v>
       </c>
       <c r="AD3">
-        <v>126139.9875588061</v>
+        <v>131249.8583155535</v>
       </c>
       <c r="AE3">
-        <v>109220.3753189876</v>
+        <v>112456.6002741567</v>
       </c>
       <c r="AF3">
-        <v>142335.0743146427</v>
+        <v>148371.8688067021</v>
       </c>
       <c r="AG3">
         <v>0</v>
@@ -777,13 +777,13 @@
         <v>0</v>
       </c>
       <c r="AJ3">
-        <v>16776618345.32121</v>
+        <v>17456231155.96861</v>
       </c>
       <c r="AK3">
-        <v>14526309917.42536</v>
+        <v>14956727836.46284</v>
       </c>
       <c r="AL3">
-        <v>18930564883.84747</v>
+        <v>19733458551.29138</v>
       </c>
     </row>
     <row r="4">
@@ -798,112 +798,112 @@
         </is>
       </c>
       <c r="C4">
-        <v>777.3906568769762</v>
+        <v>830.3701511487852</v>
       </c>
       <c r="D4">
-        <v>22.40175943121739</v>
+        <v>23.96606678829604</v>
       </c>
       <c r="E4">
-        <v>1572.856985505977</v>
+        <v>1679.989000054051</v>
       </c>
       <c r="F4">
-        <v>205.4227740551028</v>
+        <v>218.1251200341125</v>
       </c>
       <c r="G4">
-        <v>3.840993288977415</v>
+        <v>4.107719637279583</v>
       </c>
       <c r="H4">
-        <v>525.5795513595959</v>
+        <v>558.0467703075753</v>
       </c>
       <c r="I4">
-        <v>34272821.88973517</v>
+        <v>36608528.85369654</v>
       </c>
       <c r="J4">
-        <v>987626.368044079</v>
+        <v>1056591.986495604</v>
       </c>
       <c r="K4">
-        <v>69342545.92000191</v>
+        <v>74065675.04538301</v>
       </c>
       <c r="L4">
-        <v>27321228.94932868</v>
+        <v>29010640.96453696</v>
       </c>
       <c r="M4">
-        <v>510852.1074339962</v>
+        <v>546326.7117581846</v>
       </c>
       <c r="N4">
-        <v>69902080.33082625</v>
+        <v>74220220.45090751</v>
       </c>
       <c r="O4">
-        <v>3575.27802381218</v>
+        <v>5267.734272269137</v>
       </c>
       <c r="P4">
-        <v>-36.87402175591831</v>
+        <v>-109.9778120386587</v>
       </c>
       <c r="Q4">
-        <v>7289.297888182457</v>
+        <v>10508.09459977117</v>
       </c>
       <c r="R4">
-        <v>975.3694705317358</v>
+        <v>1425.104132033504</v>
       </c>
       <c r="S4">
-        <v>-7.565501948791065</v>
+        <v>-22.37616814995075</v>
       </c>
       <c r="T4">
-        <v>2515.90166751479</v>
+        <v>3596.626500588687</v>
       </c>
       <c r="U4">
-        <v>157623282.2358067</v>
+        <v>232238600.8615297</v>
       </c>
       <c r="V4">
-        <v>-1625664.997153174</v>
+        <v>-4848591.799348344</v>
       </c>
       <c r="W4">
-        <v>321363275.9962993</v>
+        <v>463270366.6201096</v>
       </c>
       <c r="X4">
-        <v>129724139.5807209</v>
+        <v>189538849.5604561</v>
       </c>
       <c r="Y4">
-        <v>-1006211.759189212</v>
+        <v>-2976030.36394345</v>
       </c>
       <c r="Z4">
-        <v>334614921.779467</v>
+        <v>478351324.5782954</v>
       </c>
       <c r="AA4">
-        <v>2797.887366935204</v>
+        <v>4437.364121120352</v>
       </c>
       <c r="AB4">
-        <v>-59.27578118713571</v>
+        <v>-133.9438788269547</v>
       </c>
       <c r="AC4">
-        <v>5716.440902676481</v>
+        <v>8828.105599717122</v>
       </c>
       <c r="AD4">
-        <v>769.9466964766331</v>
+        <v>1206.979011999392</v>
       </c>
       <c r="AE4">
-        <v>-11.40649523776848</v>
+        <v>-26.48388778723034</v>
       </c>
       <c r="AF4">
-        <v>1990.322116155194</v>
+        <v>3038.579730281112</v>
       </c>
       <c r="AG4">
-        <v>123350460.3460715</v>
+        <v>195630072.0078331</v>
       </c>
       <c r="AH4">
-        <v>-2613291.365197253</v>
+        <v>-5905183.785843948</v>
       </c>
       <c r="AI4">
-        <v>252020730.0762974</v>
+        <v>389204691.5747266</v>
       </c>
       <c r="AJ4">
-        <v>102402910.6313922</v>
+        <v>160528208.5959191</v>
       </c>
       <c r="AK4">
-        <v>-1517063.866623208</v>
+        <v>-3522357.075701635</v>
       </c>
       <c r="AL4">
-        <v>264712841.4486407</v>
+        <v>404131104.1273879</v>
       </c>
     </row>
     <row r="5">
@@ -1038,112 +1038,112 @@
         </is>
       </c>
       <c r="C6">
-        <v>4568.353925209686</v>
+        <v>12451.16645341587</v>
       </c>
       <c r="D6">
-        <v>2849.464034995572</v>
+        <v>7769.141426128057</v>
       </c>
       <c r="E6">
-        <v>6238.16508253809</v>
+        <v>16996.05159522851</v>
       </c>
       <c r="F6">
-        <v>739.1413892267392</v>
+        <v>1941.523584318884</v>
       </c>
       <c r="G6">
-        <v>364.8571756365798</v>
+        <v>958.8599264275309</v>
       </c>
       <c r="H6">
-        <v>1223.379696474785</v>
+        <v>3211.797140461129</v>
       </c>
       <c r="I6">
-        <v>254466450.3420297</v>
+        <v>693554873.7881713</v>
       </c>
       <c r="J6">
-        <v>158720845.6773234</v>
+        <v>432756715.7181846</v>
       </c>
       <c r="K6">
-        <v>347478271.4275365</v>
+        <v>946714065.9574171</v>
       </c>
       <c r="L6">
-        <v>98305804.76715632</v>
+        <v>258222636.7144116</v>
       </c>
       <c r="M6">
-        <v>48526004.35966512</v>
+        <v>127528370.2148616</v>
       </c>
       <c r="N6">
-        <v>162709499.6311464</v>
+        <v>427169019.6813302</v>
       </c>
       <c r="O6">
-        <v>21087.17857458489</v>
+        <v>67272.25267452786</v>
       </c>
       <c r="P6">
-        <v>12932.80264864024</v>
+        <v>43957.41469438181</v>
       </c>
       <c r="Q6">
-        <v>28548.6070925464</v>
+        <v>88207.3628523323</v>
       </c>
       <c r="R6">
-        <v>3438.876348739352</v>
+        <v>10441.48314496201</v>
       </c>
       <c r="S6">
-        <v>1655.333554531869</v>
+        <v>5354.921969340434</v>
       </c>
       <c r="T6">
-        <v>5675.22734654423</v>
+        <v>16689.03844293452</v>
       </c>
       <c r="U6">
-        <v>1174598020.96153</v>
+        <v>3747199018.476547</v>
       </c>
       <c r="V6">
-        <v>720382973.1345592</v>
+        <v>2448515913.30646</v>
       </c>
       <c r="W6">
-        <v>1590214512.269022</v>
+        <v>4913326525.600606</v>
       </c>
       <c r="X6">
-        <v>457370554.3823338</v>
+        <v>1388717258.279947</v>
       </c>
       <c r="Y6">
-        <v>220159362.7527386</v>
+        <v>712204621.9222777</v>
       </c>
       <c r="Z6">
-        <v>754805237.0903827</v>
+        <v>2219642112.910292</v>
       </c>
       <c r="AA6">
-        <v>16518.8246493752</v>
+        <v>54821.08622111199</v>
       </c>
       <c r="AB6">
-        <v>10083.33861364467</v>
+        <v>36188.27326825375</v>
       </c>
       <c r="AC6">
-        <v>22310.44201000832</v>
+        <v>71211.31125710379</v>
       </c>
       <c r="AD6">
-        <v>2699.734959512612</v>
+        <v>8499.959560643121</v>
       </c>
       <c r="AE6">
-        <v>1290.47637889529</v>
+        <v>4396.062042912903</v>
       </c>
       <c r="AF6">
-        <v>4451.847650069445</v>
+        <v>13477.2413024734</v>
       </c>
       <c r="AG6">
-        <v>920131570.6195008</v>
+        <v>3053644144.688375</v>
       </c>
       <c r="AH6">
-        <v>561662127.4572358</v>
+        <v>2015759197.588276</v>
       </c>
       <c r="AI6">
-        <v>1242736240.841486</v>
+        <v>3966612459.643189</v>
       </c>
       <c r="AJ6">
-        <v>359064749.6151775</v>
+        <v>1130494621.565535</v>
       </c>
       <c r="AK6">
-        <v>171633358.3930735</v>
+        <v>584676251.7074161</v>
       </c>
       <c r="AL6">
-        <v>592095737.4592363</v>
+        <v>1792473093.228961</v>
       </c>
     </row>
     <row r="7">
@@ -1158,112 +1158,112 @@
         </is>
       </c>
       <c r="C7">
-        <v>5967.064047088697</v>
+        <v>13770.2100899151</v>
       </c>
       <c r="D7">
-        <v>3836.491649555051</v>
+        <v>8846.247302135826</v>
       </c>
       <c r="E7">
-        <v>8013.065296051683</v>
+        <v>18503.50329710171</v>
       </c>
       <c r="F7">
-        <v>786.1821219842466</v>
+        <v>1590.615778847993</v>
       </c>
       <c r="G7">
-        <v>397.5199683396013</v>
+        <v>805.0283972465458</v>
       </c>
       <c r="H7">
-        <v>1284.445847413027</v>
+        <v>2596.879168300507</v>
       </c>
       <c r="I7">
-        <v>332377401.5509345</v>
+        <v>767028242.4284511</v>
       </c>
       <c r="J7">
-        <v>213700257.8635158</v>
+        <v>492753667.2235696</v>
       </c>
       <c r="K7">
-        <v>446343763.1206713</v>
+        <v>1030682140.655158</v>
       </c>
       <c r="L7">
-        <v>104562222.2239048</v>
+        <v>211551898.586783</v>
       </c>
       <c r="M7">
-        <v>52870155.78916698</v>
+        <v>107068776.8337906</v>
       </c>
       <c r="N7">
-        <v>170831297.7059326</v>
+        <v>345384929.3839675</v>
       </c>
       <c r="O7">
-        <v>32689.22736066739</v>
+        <v>86461.39193134329</v>
       </c>
       <c r="P7">
-        <v>20048.35899201673</v>
+        <v>56496.09027614217</v>
       </c>
       <c r="Q7">
-        <v>44255.89249779395</v>
+        <v>113368.1580086796</v>
       </c>
       <c r="R7">
-        <v>4815.458054813043</v>
+        <v>10992.80153703313</v>
       </c>
       <c r="S7">
-        <v>2317.963337499747</v>
+        <v>5637.665994189798</v>
       </c>
       <c r="T7">
-        <v>7947.02003427077</v>
+        <v>17570.23259053153</v>
       </c>
       <c r="U7">
-        <v>1820855342.443885</v>
+        <v>4816072453.3597</v>
       </c>
       <c r="V7">
-        <v>1116733692.573322</v>
+        <v>3146945220.56166</v>
       </c>
       <c r="W7">
-        <v>2465141723.912116</v>
+        <v>6314833137.399492</v>
       </c>
       <c r="X7">
-        <v>640455921.2901347</v>
+        <v>1462042604.425406</v>
       </c>
       <c r="Y7">
-        <v>308289123.8874664</v>
+        <v>749809577.2272431</v>
       </c>
       <c r="Z7">
-        <v>1056953664.558012</v>
+        <v>2336840934.540693</v>
       </c>
       <c r="AA7">
-        <v>26722.16331357869</v>
+        <v>72691.18184142819</v>
       </c>
       <c r="AB7">
-        <v>16211.86734246167</v>
+        <v>47649.84297400635</v>
       </c>
       <c r="AC7">
-        <v>36242.82720174227</v>
+        <v>94864.6547115779</v>
       </c>
       <c r="AD7">
-        <v>4029.275932828796</v>
+        <v>9402.185758185135</v>
       </c>
       <c r="AE7">
-        <v>1920.443369160146</v>
+        <v>4832.637596943252</v>
       </c>
       <c r="AF7">
-        <v>6662.574186857743</v>
+        <v>14973.35342223102</v>
       </c>
       <c r="AG7">
-        <v>1488477940.89295</v>
+        <v>4049044210.931249</v>
       </c>
       <c r="AH7">
-        <v>903033434.7098062</v>
+        <v>2654191553.33809</v>
       </c>
       <c r="AI7">
-        <v>2018797960.791444</v>
+        <v>5284150996.744334</v>
       </c>
       <c r="AJ7">
-        <v>535893699.0662299</v>
+        <v>1250490705.838623</v>
       </c>
       <c r="AK7">
-        <v>255418968.0982994</v>
+        <v>642740800.3934524</v>
       </c>
       <c r="AL7">
-        <v>886122366.8520799</v>
+        <v>1991456005.156725</v>
       </c>
     </row>
     <row r="8">
@@ -1278,112 +1278,112 @@
         </is>
       </c>
       <c r="C8">
-        <v>2347.224404253075</v>
+        <v>12608.35094939108</v>
       </c>
       <c r="D8">
-        <v>73.16137126765993</v>
+        <v>341.5126919798212</v>
       </c>
       <c r="E8">
-        <v>4750.237302797428</v>
+        <v>25503.27169059733</v>
       </c>
       <c r="F8">
-        <v>449.5890124044093</v>
+        <v>3597.011972976959</v>
       </c>
       <c r="G8">
-        <v>8.92133771922863</v>
+        <v>72.0527039690197</v>
       </c>
       <c r="H8">
-        <v>1049.986423188863</v>
+        <v>8398.947917194482</v>
       </c>
       <c r="I8">
-        <v>34755351.7537753</v>
+        <v>186691852.5076337</v>
       </c>
       <c r="J8">
-        <v>1083300.42436024</v>
+        <v>5056778.43014523</v>
       </c>
       <c r="K8">
-        <v>70336763.74252151</v>
+        <v>377626943.9226753</v>
       </c>
       <c r="L8">
-        <v>59795338.64978644</v>
+        <v>478402592.4059356</v>
       </c>
       <c r="M8">
-        <v>1186537.916657408</v>
+        <v>9583009.62787962</v>
       </c>
       <c r="N8">
-        <v>139648194.2841187</v>
+        <v>1117060072.986866</v>
       </c>
       <c r="O8">
-        <v>10676.70647867835</v>
+        <v>80903.92992485018</v>
       </c>
       <c r="P8">
-        <v>-110.1153824553654</v>
+        <v>-1689.082390754535</v>
       </c>
       <c r="Q8">
-        <v>21767.73203914123</v>
+        <v>161387.440064886</v>
       </c>
       <c r="R8">
-        <v>2078.822191287258</v>
+        <v>23543.62622491</v>
       </c>
       <c r="S8">
-        <v>-16.96254972868347</v>
+        <v>-388.8818481542627</v>
       </c>
       <c r="T8">
-        <v>4894.022491592526</v>
+        <v>54230.82440651565</v>
       </c>
       <c r="U8">
-        <v>158089992.8297897</v>
+        <v>1197944490.39726</v>
       </c>
       <c r="V8">
-        <v>-1630478.468016595</v>
+        <v>-25010242.95990245</v>
       </c>
       <c r="W8">
-        <v>322314808.3035654</v>
+        <v>2389663825.040776</v>
       </c>
       <c r="X8">
-        <v>276483351.4412053</v>
+        <v>3131302287.913031</v>
       </c>
       <c r="Y8">
-        <v>-2256019.113914901</v>
+        <v>-51721285.80451694</v>
       </c>
       <c r="Z8">
-        <v>650904991.381806</v>
+        <v>7212699646.066581</v>
       </c>
       <c r="AA8">
-        <v>8329.482074425272</v>
+        <v>68295.5789754591</v>
       </c>
       <c r="AB8">
-        <v>-183.2767537230254</v>
+        <v>-2030.595082734356</v>
       </c>
       <c r="AC8">
-        <v>17017.4947363438</v>
+        <v>135884.1683742887</v>
       </c>
       <c r="AD8">
-        <v>1629.233178882849</v>
+        <v>19946.61425193305</v>
       </c>
       <c r="AE8">
-        <v>-25.88388744791209</v>
+        <v>-460.9345521232825</v>
       </c>
       <c r="AF8">
-        <v>3844.036068403663</v>
+        <v>45831.87648932116</v>
       </c>
       <c r="AG8">
-        <v>123334641.0760144</v>
+        <v>1011252637.889627</v>
       </c>
       <c r="AH8">
-        <v>-2713778.892376835</v>
+        <v>-30067021.39004768</v>
       </c>
       <c r="AI8">
-        <v>251978044.5610439</v>
+        <v>2012036881.1181</v>
       </c>
       <c r="AJ8">
-        <v>216688012.7914188</v>
+        <v>2652899695.507095</v>
       </c>
       <c r="AK8">
-        <v>-3442557.030572309</v>
+        <v>-61304295.43239656</v>
       </c>
       <c r="AL8">
-        <v>511256797.0976873</v>
+        <v>6095639573.079715</v>
       </c>
     </row>
     <row r="9">
@@ -1398,112 +1398,112 @@
         </is>
       </c>
       <c r="C9">
-        <v>2529.569307391621</v>
+        <v>7280.920694582312</v>
       </c>
       <c r="D9">
-        <v>34.23615350539696</v>
+        <v>113.2657565906829</v>
       </c>
       <c r="E9">
-        <v>5106.121412363852</v>
+        <v>14697.12783036198</v>
       </c>
       <c r="F9">
-        <v>343.3374105484882</v>
+        <v>1076.400255575184</v>
       </c>
       <c r="G9">
-        <v>3.280060594898655</v>
+        <v>13.75343852158111</v>
       </c>
       <c r="H9">
-        <v>800.4912417719837</v>
+        <v>2509.739008195952</v>
       </c>
       <c r="I9">
-        <v>37455332.73454773</v>
+        <v>107808592.7246803</v>
       </c>
       <c r="J9">
-        <v>506934.7249544119</v>
+        <v>1677126.057838241</v>
       </c>
       <c r="K9">
-        <v>75606339.75287163</v>
+        <v>217620371.78417</v>
       </c>
       <c r="L9">
-        <v>45663875.60294893</v>
+        <v>143161233.9914995</v>
       </c>
       <c r="M9">
-        <v>436248.0591215211</v>
+        <v>1829207.323370288</v>
       </c>
       <c r="N9">
-        <v>106465335.1556738</v>
+        <v>333795288.0900615</v>
       </c>
       <c r="O9">
-        <v>12750.78908252082</v>
+        <v>51212.84679198766</v>
       </c>
       <c r="P9">
-        <v>-131.5066607135276</v>
+        <v>-1069.202914828812</v>
       </c>
       <c r="Q9">
-        <v>25996.3838652124</v>
+        <v>102159.5644348961</v>
       </c>
       <c r="R9">
-        <v>1907.968223277289</v>
+        <v>8420.880817681866</v>
       </c>
       <c r="S9">
-        <v>-15.56843389671931</v>
+        <v>-139.0918996157926</v>
       </c>
       <c r="T9">
-        <v>4491.793207278004</v>
+        <v>19396.812734341</v>
       </c>
       <c r="U9">
-        <v>188800933.9448861</v>
+        <v>758308622.4489565</v>
       </c>
       <c r="V9">
-        <v>-1947219.125185205</v>
+        <v>-15831687.55987027</v>
       </c>
       <c r="W9">
-        <v>384928455.8921987</v>
+        <v>1512676670.587509</v>
       </c>
       <c r="X9">
-        <v>253759773.6958795</v>
+        <v>1119977148.751688</v>
       </c>
       <c r="Y9">
-        <v>-2070601.708263668</v>
+        <v>-18499222.64890042</v>
       </c>
       <c r="Z9">
-        <v>597408496.5679746</v>
+        <v>2579776093.667353</v>
       </c>
       <c r="AA9">
-        <v>10221.2197751292</v>
+        <v>43931.92609740535</v>
       </c>
       <c r="AB9">
-        <v>-165.7428142189246</v>
+        <v>-1182.468671419495</v>
       </c>
       <c r="AC9">
-        <v>20890.26245284855</v>
+        <v>87462.4366045341</v>
       </c>
       <c r="AD9">
-        <v>1564.630812728801</v>
+        <v>7344.480562106682</v>
       </c>
       <c r="AE9">
-        <v>-18.84849449161796</v>
+        <v>-152.8453381373737</v>
       </c>
       <c r="AF9">
-        <v>3691.30196550602</v>
+        <v>16887.07372614504</v>
       </c>
       <c r="AG9">
-        <v>151345601.2103384</v>
+        <v>650500029.7242762</v>
       </c>
       <c r="AH9">
-        <v>-2454153.850139617</v>
+        <v>-17508813.61770852</v>
       </c>
       <c r="AI9">
-        <v>309322116.139327</v>
+        <v>1295056298.803339</v>
       </c>
       <c r="AJ9">
-        <v>208095898.0929305</v>
+        <v>976815914.7601887</v>
       </c>
       <c r="AK9">
-        <v>-2506849.767385189</v>
+        <v>-20328429.97227071</v>
       </c>
       <c r="AL9">
-        <v>490943161.4123008</v>
+        <v>2245980805.577291</v>
       </c>
     </row>
     <row r="10">
@@ -1518,112 +1518,112 @@
         </is>
       </c>
       <c r="C10">
-        <v>3237.642755560177</v>
+        <v>2004.309455944744</v>
       </c>
       <c r="D10">
-        <v>-66.36838101779699</v>
+        <v>-38.22584290513367</v>
       </c>
       <c r="E10">
-        <v>6016.77774961595</v>
+        <v>3716.711599418889</v>
       </c>
       <c r="F10">
-        <v>862.9829262299427</v>
+        <v>671.3461051168656</v>
       </c>
       <c r="G10">
-        <v>-12.33997752082171</v>
+        <v>-9.529064761315126</v>
       </c>
       <c r="H10">
-        <v>2031.924478019441</v>
+        <v>1580.452775246205</v>
       </c>
       <c r="I10">
-        <v>243473972.8608811</v>
+        <v>150726075.3965008</v>
       </c>
       <c r="J10">
-        <v>-4990968.62091934</v>
+        <v>-2874621.612308952</v>
       </c>
       <c r="K10">
-        <v>452467703.5488692</v>
+        <v>279500428.9879004</v>
       </c>
       <c r="L10">
-        <v>114776729.1885824</v>
+        <v>89289031.98054312</v>
       </c>
       <c r="M10">
-        <v>-1641217.010269287</v>
+        <v>-1267365.613254912</v>
       </c>
       <c r="N10">
-        <v>270245955.5765857</v>
+        <v>210200219.1077453</v>
       </c>
       <c r="O10">
-        <v>14609.69221040514</v>
+        <v>12335.51081750371</v>
       </c>
       <c r="P10">
-        <v>-232.3548881812114</v>
+        <v>0</v>
       </c>
       <c r="Q10">
-        <v>27299.79210828945</v>
+        <v>22493.13134572677</v>
       </c>
       <c r="R10">
-        <v>4003.701699700935</v>
+        <v>4275.978687774265</v>
       </c>
       <c r="S10">
-        <v>-47.3866520456784</v>
+        <v>0</v>
       </c>
       <c r="T10">
-        <v>9498.442412923026</v>
+        <v>9899.21418616458</v>
       </c>
       <c r="U10">
-        <v>1098663463.914679</v>
+        <v>927642748.9870987</v>
       </c>
       <c r="V10">
-        <v>-17473319.9461153</v>
+        <v>0</v>
       </c>
       <c r="W10">
-        <v>2052971666.335473</v>
+        <v>1691505970.330006</v>
       </c>
       <c r="X10">
-        <v>532492326.0602244</v>
+        <v>568705165.4739773</v>
       </c>
       <c r="Y10">
-        <v>-6302424.722075228</v>
+        <v>0</v>
       </c>
       <c r="Z10">
-        <v>1263292840.918762</v>
+        <v>1316595486.759889</v>
       </c>
       <c r="AA10">
-        <v>11372.04945484496</v>
+        <v>10331.20136155897</v>
       </c>
       <c r="AB10">
-        <v>-165.9865071634144</v>
+        <v>38.22584290513367</v>
       </c>
       <c r="AC10">
-        <v>21283.0143586735</v>
+        <v>18776.41974630788</v>
       </c>
       <c r="AD10">
-        <v>3140.718773470992</v>
+        <v>3604.6325826574</v>
       </c>
       <c r="AE10">
-        <v>-35.04667452485669</v>
+        <v>9.529064761315126</v>
       </c>
       <c r="AF10">
-        <v>7466.517934903585</v>
+        <v>8318.761410918374</v>
       </c>
       <c r="AG10">
-        <v>855189491.0537977</v>
+        <v>776916673.5905979</v>
       </c>
       <c r="AH10">
-        <v>-12482351.32519596</v>
+        <v>2874621.612308952</v>
       </c>
       <c r="AI10">
-        <v>1600503962.786604</v>
+        <v>1412005541.342106</v>
       </c>
       <c r="AJ10">
-        <v>417715596.8716419</v>
+        <v>479416133.4934342</v>
       </c>
       <c r="AK10">
-        <v>-4661207.711805941</v>
+        <v>1267365.613254912</v>
       </c>
       <c r="AL10">
-        <v>993046885.3421767</v>
+        <v>1106395267.652144</v>
       </c>
     </row>
     <row r="11">
@@ -1638,112 +1638,112 @@
         </is>
       </c>
       <c r="C11">
-        <v>3222.915557927578</v>
+        <v>2148.040713968812</v>
       </c>
       <c r="D11">
-        <v>-45.8080836867474</v>
+        <v>-31.63323760894794</v>
       </c>
       <c r="E11">
-        <v>5925.365518466964</v>
+        <v>3953.733148619258</v>
       </c>
       <c r="F11">
-        <v>632.9623310563684</v>
+        <v>612.4907278556932</v>
       </c>
       <c r="G11">
-        <v>-7.065500841420956</v>
+        <v>-7.680382973848277</v>
       </c>
       <c r="H11">
-        <v>1479.682271232525</v>
+        <v>1436.537461637133</v>
       </c>
       <c r="I11">
-        <v>242366472.8717118</v>
+        <v>161534809.7311683</v>
       </c>
       <c r="J11">
-        <v>-3444813.701327092</v>
+        <v>-2378851.101430498</v>
       </c>
       <c r="K11">
-        <v>445593412.3542344</v>
+        <v>297324686.5093169</v>
       </c>
       <c r="L11">
-        <v>84183990.030497</v>
+        <v>81461266.8048072</v>
       </c>
       <c r="M11">
-        <v>-939711.6119089872</v>
+        <v>-1021490.935521821</v>
       </c>
       <c r="N11">
-        <v>196797742.0739258</v>
+        <v>191059482.3977386</v>
       </c>
       <c r="O11">
-        <v>16823.58541287801</v>
+        <v>16341.50219780824</v>
       </c>
       <c r="P11">
-        <v>-267.5650007624584</v>
+        <v>0</v>
       </c>
       <c r="Q11">
-        <v>31436.69131924065</v>
+        <v>29797.83818925521</v>
       </c>
       <c r="R11">
-        <v>3646.244714025668</v>
+        <v>4996.956599485138</v>
       </c>
       <c r="S11">
-        <v>-43.15589484347326</v>
+        <v>0</v>
       </c>
       <c r="T11">
-        <v>8650.406058519478</v>
+        <v>11568.33260154067</v>
       </c>
       <c r="U11">
-        <v>1265150446.633837</v>
+        <v>1228897306.777378</v>
       </c>
       <c r="V11">
-        <v>-20121155.62233757</v>
+        <v>0</v>
       </c>
       <c r="W11">
-        <v>2364070623.898221</v>
+        <v>2240827229.670175</v>
       </c>
       <c r="X11">
-        <v>484950546.9654139</v>
+        <v>664595227.7315234</v>
       </c>
       <c r="Y11">
-        <v>-5739734.014181944</v>
+        <v>0</v>
       </c>
       <c r="Z11">
-        <v>1150504005.783091</v>
+        <v>1538588236.004909</v>
       </c>
       <c r="AA11">
-        <v>13600.66985495043</v>
+        <v>14193.46148383943</v>
       </c>
       <c r="AB11">
-        <v>-221.756917075711</v>
+        <v>31.63323760894794</v>
       </c>
       <c r="AC11">
-        <v>25511.32580077369</v>
+        <v>25844.10504063595</v>
       </c>
       <c r="AD11">
-        <v>3013.2823829693</v>
+        <v>4384.465871629445</v>
       </c>
       <c r="AE11">
-        <v>-36.09039400205231</v>
+        <v>7.680382973848277</v>
       </c>
       <c r="AF11">
-        <v>7170.723787286954</v>
+        <v>10131.79513990353</v>
       </c>
       <c r="AG11">
-        <v>1022783973.762125</v>
+        <v>1067362497.04621</v>
       </c>
       <c r="AH11">
-        <v>-16676341.92101048</v>
+        <v>2378851.101430498</v>
       </c>
       <c r="AI11">
-        <v>1918477211.543987</v>
+        <v>1943502543.160858</v>
       </c>
       <c r="AJ11">
-        <v>400766556.9349169</v>
+        <v>583133960.9267162</v>
       </c>
       <c r="AK11">
-        <v>-4800022.402272956</v>
+        <v>1021490.935521821</v>
       </c>
       <c r="AL11">
-        <v>953706263.7091649</v>
+        <v>1347528753.60717</v>
       </c>
     </row>
     <row r="12">
@@ -1758,112 +1758,112 @@
         </is>
       </c>
       <c r="C12">
-        <v>2384.448403736423</v>
+        <v>5704.556738423242</v>
       </c>
       <c r="D12">
-        <v>1718.398198899412</v>
+        <v>4110.358339865177</v>
       </c>
       <c r="E12">
-        <v>2981.24789460943</v>
+        <v>7131.222289336152</v>
       </c>
       <c r="F12">
-        <v>636.4554083743607</v>
+        <v>1696.011621456228</v>
       </c>
       <c r="G12">
-        <v>368.1618173958173</v>
+        <v>981.3754516187024</v>
       </c>
       <c r="H12">
-        <v>904.9242175441377</v>
+        <v>2409.694859134266</v>
       </c>
       <c r="I12">
-        <v>40151726.67051771</v>
+        <v>96059030.91830906</v>
       </c>
       <c r="J12">
-        <v>28936107.27126723</v>
+        <v>69214324.08498967</v>
       </c>
       <c r="K12">
-        <v>50201233.29732811</v>
+        <v>120082652.1301314</v>
       </c>
       <c r="L12">
-        <v>84648569.31378996</v>
+        <v>225569545.6536784</v>
       </c>
       <c r="M12">
-        <v>48965521.7136437</v>
+        <v>130522935.0652874</v>
       </c>
       <c r="N12">
-        <v>120354920.9333703</v>
+        <v>320489416.2648574</v>
       </c>
       <c r="O12">
-        <v>11295.22216359617</v>
+        <v>32171.39524575697</v>
       </c>
       <c r="P12">
-        <v>8177.773310166796</v>
+        <v>23811.65577163275</v>
       </c>
       <c r="Q12">
-        <v>14005.53935045447</v>
+        <v>39090.87851330139</v>
       </c>
       <c r="R12">
-        <v>2815.738768641944</v>
+        <v>8964.67197227111</v>
       </c>
       <c r="S12">
-        <v>1634.767903873348</v>
+        <v>5320.807584618855</v>
       </c>
       <c r="T12">
-        <v>3976.311883475833</v>
+        <v>12405.74806267202</v>
       </c>
       <c r="U12">
-        <v>190200246.0127967</v>
+        <v>541734124.5433004</v>
       </c>
       <c r="V12">
-        <v>137705524.7698984</v>
+        <v>400964471.538523</v>
       </c>
       <c r="W12">
-        <v>235839277.1223028</v>
+        <v>658251303.2854826</v>
       </c>
       <c r="X12">
-        <v>374493256.2293786</v>
+        <v>1192301372.312057</v>
       </c>
       <c r="Y12">
-        <v>217424131.2151553</v>
+        <v>707667408.7543077</v>
       </c>
       <c r="Z12">
-        <v>528849480.5022858</v>
+        <v>1649964492.335379</v>
       </c>
       <c r="AA12">
-        <v>8910.773759859741</v>
+        <v>26466.83850733373</v>
       </c>
       <c r="AB12">
-        <v>6459.375111267384</v>
+        <v>19701.29743176757</v>
       </c>
       <c r="AC12">
-        <v>11024.29145584504</v>
+        <v>31959.65622396523</v>
       </c>
       <c r="AD12">
-        <v>2179.283360267584</v>
+        <v>7268.660350814882</v>
       </c>
       <c r="AE12">
-        <v>1266.606086477531</v>
+        <v>4339.432133000152</v>
       </c>
       <c r="AF12">
-        <v>3071.387665931696</v>
+        <v>9996.053203537755</v>
       </c>
       <c r="AG12">
-        <v>150048519.342279</v>
+        <v>445675093.6249913</v>
       </c>
       <c r="AH12">
-        <v>108769417.4986312</v>
+        <v>331750147.4535333</v>
       </c>
       <c r="AI12">
-        <v>185638043.8249747</v>
+        <v>538168651.1553513</v>
       </c>
       <c r="AJ12">
-        <v>289844686.9155886</v>
+        <v>966731826.6583791</v>
       </c>
       <c r="AK12">
-        <v>168458609.5015116</v>
+        <v>577144473.6890204</v>
       </c>
       <c r="AL12">
-        <v>408494559.5689155</v>
+        <v>1329475076.070521</v>
       </c>
     </row>
     <row r="13">
@@ -1878,112 +1878,112 @@
         </is>
       </c>
       <c r="C13">
-        <v>1190.702010578538</v>
+        <v>3638.22705415106</v>
       </c>
       <c r="D13">
-        <v>858.7854577214898</v>
+        <v>2627.225361846554</v>
       </c>
       <c r="E13">
-        <v>1486.42548531547</v>
+        <v>4538.771809711213</v>
       </c>
       <c r="F13">
-        <v>158.6886770578006</v>
+        <v>555.135456549922</v>
       </c>
       <c r="G13">
-        <v>92.24176815624003</v>
+        <v>323.2138405875617</v>
       </c>
       <c r="H13">
-        <v>224.6571567232756</v>
+        <v>785.0259857140907</v>
       </c>
       <c r="I13">
-        <v>20050231.15613202</v>
+        <v>61264105.36484969</v>
       </c>
       <c r="J13">
-        <v>14461088.32257216</v>
+        <v>44239847.86813409</v>
       </c>
       <c r="K13">
-        <v>25029918.74722721</v>
+        <v>76428378.50372709</v>
       </c>
       <c r="L13">
-        <v>21105594.04868748</v>
+        <v>73833015.72113962</v>
       </c>
       <c r="M13">
-        <v>12268155.16477992</v>
+        <v>42987440.7981457</v>
       </c>
       <c r="N13">
-        <v>29879401.84419566</v>
+        <v>104408456.0999741</v>
       </c>
       <c r="O13">
-        <v>6108.10108827936</v>
+        <v>22607.42410015239</v>
       </c>
       <c r="P13">
-        <v>4422.282743275283</v>
+        <v>16732.88324749115</v>
       </c>
       <c r="Q13">
-        <v>7573.755425914868</v>
+        <v>27469.8707422177</v>
       </c>
       <c r="R13">
-        <v>895.7120796130496</v>
+        <v>3724.500821296638</v>
       </c>
       <c r="S13">
-        <v>520.0345199527512</v>
+        <v>2210.605394170793</v>
       </c>
       <c r="T13">
-        <v>1264.900929732205</v>
+        <v>5154.144958247179</v>
       </c>
       <c r="U13">
-        <v>102854314.2255365</v>
+        <v>380686414.422466</v>
       </c>
       <c r="V13">
-        <v>74466819.11401233</v>
+        <v>281765021.0045031</v>
       </c>
       <c r="W13">
-        <v>127534467.6169806</v>
+        <v>462565153.4282026</v>
       </c>
       <c r="X13">
-        <v>119129706.5885356</v>
+        <v>495358609.2324529</v>
       </c>
       <c r="Y13">
-        <v>69164591.15371591</v>
+        <v>294010517.4247155</v>
       </c>
       <c r="Z13">
-        <v>168231823.6543833</v>
+        <v>685501279.4468747</v>
       </c>
       <c r="AA13">
-        <v>4917.399077700822</v>
+        <v>18969.19704600133</v>
       </c>
       <c r="AB13">
-        <v>3563.497285553793</v>
+        <v>14105.65788564459</v>
       </c>
       <c r="AC13">
-        <v>6087.329940599398</v>
+        <v>22931.09893250648</v>
       </c>
       <c r="AD13">
-        <v>737.023402555249</v>
+        <v>3169.365364746716</v>
       </c>
       <c r="AE13">
-        <v>427.7927517965112</v>
+        <v>1887.391553583232</v>
       </c>
       <c r="AF13">
-        <v>1040.24377300893</v>
+        <v>4369.118972533088</v>
       </c>
       <c r="AG13">
-        <v>82804083.06940451</v>
+        <v>319422309.0576164</v>
       </c>
       <c r="AH13">
-        <v>60005730.79144017</v>
+        <v>237525173.136369</v>
       </c>
       <c r="AI13">
-        <v>102504548.8697534</v>
+        <v>386136774.9244755</v>
       </c>
       <c r="AJ13">
-        <v>98024112.53984812</v>
+        <v>421525593.5113133</v>
       </c>
       <c r="AK13">
-        <v>56896435.98893599</v>
+        <v>251023076.6265698</v>
       </c>
       <c r="AL13">
-        <v>138352421.8101876</v>
+        <v>581092823.3469007</v>
       </c>
     </row>
     <row r="14">
@@ -1998,22 +1998,22 @@
         </is>
       </c>
       <c r="C14">
-        <v>132514.5131922857</v>
+        <v>67587.25211501982</v>
       </c>
       <c r="D14">
-        <v>98674.44200563467</v>
+        <v>50266.75700739733</v>
       </c>
       <c r="E14">
-        <v>160176.1595485081</v>
+        <v>81736.21956205854</v>
       </c>
       <c r="F14">
-        <v>150358.5827161974</v>
+        <v>64401.94708783021</v>
       </c>
       <c r="G14">
-        <v>69234.75185318149</v>
+        <v>29650.5062572388</v>
       </c>
       <c r="H14">
-        <v>277751.6065853683</v>
+        <v>118972.1819007881</v>
       </c>
       <c r="I14">
         <v>0</v>
@@ -2025,31 +2025,31 @@
         <v>0</v>
       </c>
       <c r="L14">
-        <v>19997691501.25425</v>
+        <v>8565458962.681417</v>
       </c>
       <c r="M14">
-        <v>9208221996.473137</v>
+        <v>3943517332.21276</v>
       </c>
       <c r="N14">
-        <v>36940963675.85399</v>
+        <v>15823300192.80481</v>
       </c>
       <c r="O14">
-        <v>627401.4401708276</v>
+        <v>424800.9076185662</v>
       </c>
       <c r="P14">
-        <v>461939.5259119386</v>
+        <v>319020.455855674</v>
       </c>
       <c r="Q14">
-        <v>755869.0542637333</v>
+        <v>508614.5913819045</v>
       </c>
       <c r="R14">
-        <v>720277.1109552021</v>
+        <v>410810.763891281</v>
       </c>
       <c r="S14">
-        <v>328055.8565353889</v>
+        <v>190846.1828195405</v>
       </c>
       <c r="T14">
-        <v>1326000.369545894</v>
+        <v>751602.4213941777</v>
       </c>
       <c r="U14">
         <v>0</v>
@@ -2061,31 +2061,31 @@
         <v>0</v>
       </c>
       <c r="X14">
-        <v>95796855757.04189</v>
+        <v>54637831597.54037</v>
       </c>
       <c r="Y14">
-        <v>43631428919.20672</v>
+        <v>25382542314.99888</v>
       </c>
       <c r="Z14">
-        <v>176358049149.6039</v>
+        <v>99963122045.42563</v>
       </c>
       <c r="AA14">
-        <v>494886.9269785419</v>
+        <v>357213.6555035464</v>
       </c>
       <c r="AB14">
-        <v>363265.083906304</v>
+        <v>268753.6988482766</v>
       </c>
       <c r="AC14">
-        <v>595692.8947152252</v>
+        <v>426878.371819846</v>
       </c>
       <c r="AD14">
-        <v>569918.5282390048</v>
+        <v>346408.8168034508</v>
       </c>
       <c r="AE14">
-        <v>258821.1046822074</v>
+        <v>161195.6765623017</v>
       </c>
       <c r="AF14">
-        <v>1048248.762960526</v>
+        <v>632630.2394933896</v>
       </c>
       <c r="AG14">
         <v>0</v>
@@ -2097,13 +2097,13 @@
         <v>0</v>
       </c>
       <c r="AJ14">
-        <v>75799164255.78763</v>
+        <v>46072372634.85895</v>
       </c>
       <c r="AK14">
-        <v>34423206922.73358</v>
+        <v>21439024982.78612</v>
       </c>
       <c r="AL14">
-        <v>139417085473.7499</v>
+        <v>84139821852.62082</v>
       </c>
     </row>
     <row r="15">
@@ -2118,22 +2118,22 @@
         </is>
       </c>
       <c r="C15">
-        <v>45862.4334559237</v>
+        <v>27318.78515242044</v>
       </c>
       <c r="D15">
-        <v>34205.12877766402</v>
+        <v>20406.04303923879</v>
       </c>
       <c r="E15">
-        <v>55395.18123943473</v>
+        <v>32984.48756594546</v>
       </c>
       <c r="F15">
-        <v>45689.63899675892</v>
+        <v>20856.25373275864</v>
       </c>
       <c r="G15">
-        <v>21039.32351696153</v>
+        <v>9613.8571875216</v>
       </c>
       <c r="H15">
-        <v>84384.72086729162</v>
+        <v>38506.48210546467</v>
       </c>
       <c r="I15">
         <v>0</v>
@@ -2145,31 +2145,31 @@
         <v>0</v>
       </c>
       <c r="L15">
-        <v>6076721986.568936</v>
+        <v>2773881746.4569</v>
       </c>
       <c r="M15">
-        <v>2798230027.755883</v>
+        <v>1278643005.940373</v>
       </c>
       <c r="N15">
-        <v>11223167875.34978</v>
+        <v>5121362120.026802</v>
       </c>
       <c r="O15">
-        <v>277727.4893059632</v>
+        <v>209223.0341274764</v>
       </c>
       <c r="P15">
-        <v>204483.5993806107</v>
+        <v>157124.0233384507</v>
       </c>
       <c r="Q15">
-        <v>334595.3662898528</v>
+        <v>250502.9676301416</v>
       </c>
       <c r="R15">
-        <v>285767.8531211635</v>
+        <v>172994.9280803206</v>
       </c>
       <c r="S15">
-        <v>130155.2088773413</v>
+        <v>80366.49614177944</v>
       </c>
       <c r="T15">
-        <v>526086.7978165785</v>
+        <v>316504.3817315627</v>
       </c>
       <c r="U15">
         <v>0</v>
@@ -2181,31 +2181,31 @@
         <v>0</v>
       </c>
       <c r="X15">
-        <v>38007124465.11475</v>
+        <v>23008325434.68265</v>
       </c>
       <c r="Y15">
-        <v>17310642780.68639</v>
+        <v>10688743986.85666</v>
       </c>
       <c r="Z15">
-        <v>69969544109.60495</v>
+        <v>42095082770.29784</v>
       </c>
       <c r="AA15">
-        <v>231865.0558500395</v>
+        <v>181904.248975056</v>
       </c>
       <c r="AB15">
-        <v>170278.4706029466</v>
+        <v>136717.9802992119</v>
       </c>
       <c r="AC15">
-        <v>279200.185050418</v>
+        <v>217518.4800641961</v>
       </c>
       <c r="AD15">
-        <v>240078.2141244046</v>
+        <v>152138.674347562</v>
       </c>
       <c r="AE15">
-        <v>109115.8853603797</v>
+        <v>70752.63895425784</v>
       </c>
       <c r="AF15">
-        <v>441702.0769492869</v>
+        <v>277997.899626098</v>
       </c>
       <c r="AG15">
         <v>0</v>
@@ -2217,13 +2217,13 @@
         <v>0</v>
       </c>
       <c r="AJ15">
-        <v>31930402478.54581</v>
+        <v>20234443688.22575</v>
       </c>
       <c r="AK15">
-        <v>14512412752.93051</v>
+        <v>9410100980.916292</v>
       </c>
       <c r="AL15">
-        <v>58746376234.25517</v>
+        <v>36973720650.27103</v>
       </c>
     </row>
   </sheetData>

--- a/output/Tables/7000 steps/add_cases_prev_7000steps.xlsx
+++ b/output/Tables/7000 steps/add_cases_prev_7000steps.xlsx
@@ -1,21 +1,173 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10119"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ines/Documents/PhD/PROJETS/MARCHE/HIA_walking_steps/output/Tables/7000 steps/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E697DCF5-5F8D-6F42-926B-45FAC5F02FCB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="240" yWindow="500" windowWidth="21100" windowHeight="11960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="47">
+  <si>
+    <t>disease</t>
+  </si>
+  <si>
+    <t>sex</t>
+  </si>
+  <si>
+    <t>tot_cases_mid_2019</t>
+  </si>
+  <si>
+    <t>tot_cases_low_2019</t>
+  </si>
+  <si>
+    <t>tot_cases_up_2019</t>
+  </si>
+  <si>
+    <t>tot_daly_mid_2019</t>
+  </si>
+  <si>
+    <t>tot_daly_low_2019</t>
+  </si>
+  <si>
+    <t>tot_daly_up_2019</t>
+  </si>
+  <si>
+    <t>tot_medic_costs_mid_2019</t>
+  </si>
+  <si>
+    <t>tot_medic_costs_low_2019</t>
+  </si>
+  <si>
+    <t>tot_medic_costs_up_2019</t>
+  </si>
+  <si>
+    <t>tot_soc_costs_mid_2019</t>
+  </si>
+  <si>
+    <t>tot_soc_costs_low_2019</t>
+  </si>
+  <si>
+    <t>tot_soc_costs_up_2019</t>
+  </si>
+  <si>
+    <t>tot_cases_mid_RECO</t>
+  </si>
+  <si>
+    <t>tot_cases_low_RECO</t>
+  </si>
+  <si>
+    <t>tot_cases_up_RECO</t>
+  </si>
+  <si>
+    <t>tot_daly_mid_RECO</t>
+  </si>
+  <si>
+    <t>tot_daly_low_RECO</t>
+  </si>
+  <si>
+    <t>tot_daly_up_RECO</t>
+  </si>
+  <si>
+    <t>tot_medic_costs_mid_RECO</t>
+  </si>
+  <si>
+    <t>tot_medic_costs_low_RECO</t>
+  </si>
+  <si>
+    <t>tot_medic_costs_up_RECO</t>
+  </si>
+  <si>
+    <t>tot_soc_costs_mid_RECO</t>
+  </si>
+  <si>
+    <t>tot_soc_costs_low_RECO</t>
+  </si>
+  <si>
+    <t>tot_soc_costs_up_RECO</t>
+  </si>
+  <si>
+    <t>tot_cases_mid_RECO_diff</t>
+  </si>
+  <si>
+    <t>tot_cases_low_RECO_diff</t>
+  </si>
+  <si>
+    <t>tot_cases_up_RECO_diff</t>
+  </si>
+  <si>
+    <t>tot_daly_mid_RECO_diff</t>
+  </si>
+  <si>
+    <t>tot_daly_low_RECO_diff</t>
+  </si>
+  <si>
+    <t>tot_daly_up_RECO_diff</t>
+  </si>
+  <si>
+    <t>tot_medic_costs_mid_RECO_diff</t>
+  </si>
+  <si>
+    <t>tot_medic_costs_low_RECO_diff</t>
+  </si>
+  <si>
+    <t>tot_medic_costs_up_RECO_diff</t>
+  </si>
+  <si>
+    <t>tot_soc_costs_mid_RECO_diff</t>
+  </si>
+  <si>
+    <t>tot_soc_costs_low_RECO_diff</t>
+  </si>
+  <si>
+    <t>tot_soc_costs_up_RECO_diff</t>
+  </si>
+  <si>
+    <t>mort</t>
+  </si>
+  <si>
+    <t>Female</t>
+  </si>
+  <si>
+    <t>Male</t>
+  </si>
+  <si>
+    <t>bc</t>
+  </si>
+  <si>
+    <t>cvd</t>
+  </si>
+  <si>
+    <t>cancer</t>
+  </si>
+  <si>
+    <t>diab2</t>
+  </si>
+  <si>
+    <t>dem</t>
+  </si>
+  <si>
+    <t>dep</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -63,13 +215,21 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -107,7 +267,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -141,6 +301,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -175,9 +336,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -350,230 +512,188 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AL15"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="3" max="3" width="17.1640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.33203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="16" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.1640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="22.83203125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="22.6640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="21.83203125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="20.33203125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="20.1640625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="19.33203125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="17.1640625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="17" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="16" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="16.33203125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="16" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="15.1640625" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="22.83203125" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="22.6640625" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="21.83203125" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="20.33203125" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="20.1640625" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="19.33203125" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="20.5" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="20.33203125" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="19.5" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="19.6640625" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="19.5" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="18.6640625" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="26.1640625" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="26" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="25.1640625" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="23.83203125" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="23.6640625" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="22.83203125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>disease</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>sex</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>tot_cases_mid_2019</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>tot_cases_low_2019</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>tot_cases_up_2019</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>tot_daly_mid_2019</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>tot_daly_low_2019</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>tot_daly_up_2019</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>tot_medic_costs_mid_2019</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>tot_medic_costs_low_2019</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>tot_medic_costs_up_2019</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>tot_soc_costs_mid_2019</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>tot_soc_costs_low_2019</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>tot_soc_costs_up_2019</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>tot_cases_mid_RECO</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>tot_cases_low_RECO</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>tot_cases_up_RECO</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>tot_daly_mid_RECO</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>tot_daly_low_RECO</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>tot_daly_up_RECO</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>tot_medic_costs_mid_RECO</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>tot_medic_costs_low_RECO</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>tot_medic_costs_up_RECO</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>tot_soc_costs_mid_RECO</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>tot_soc_costs_low_RECO</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>tot_soc_costs_up_RECO</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>tot_cases_mid_RECO_diff</t>
-        </is>
-      </c>
-      <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>tot_cases_low_RECO_diff</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
-        <is>
-          <t>tot_cases_up_RECO_diff</t>
-        </is>
-      </c>
-      <c r="AD1" s="1" t="inlineStr">
-        <is>
-          <t>tot_daly_mid_RECO_diff</t>
-        </is>
-      </c>
-      <c r="AE1" s="1" t="inlineStr">
-        <is>
-          <t>tot_daly_low_RECO_diff</t>
-        </is>
-      </c>
-      <c r="AF1" s="1" t="inlineStr">
-        <is>
-          <t>tot_daly_up_RECO_diff</t>
-        </is>
-      </c>
-      <c r="AG1" s="1" t="inlineStr">
-        <is>
-          <t>tot_medic_costs_mid_RECO_diff</t>
-        </is>
-      </c>
-      <c r="AH1" s="1" t="inlineStr">
-        <is>
-          <t>tot_medic_costs_low_RECO_diff</t>
-        </is>
-      </c>
-      <c r="AI1" s="1" t="inlineStr">
-        <is>
-          <t>tot_medic_costs_up_RECO_diff</t>
-        </is>
-      </c>
-      <c r="AJ1" s="1" t="inlineStr">
-        <is>
-          <t>tot_soc_costs_mid_RECO_diff</t>
-        </is>
-      </c>
-      <c r="AK1" s="1" t="inlineStr">
-        <is>
-          <t>tot_soc_costs_low_RECO_diff</t>
-        </is>
-      </c>
-      <c r="AL1" s="1" t="inlineStr">
-        <is>
-          <t>tot_soc_costs_up_RECO_diff</t>
-        </is>
+    <row r="1" spans="1:38" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Y1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Z1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AB1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AC1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="AD1" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="AE1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="AF1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="AG1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="AH1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AI1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="AJ1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="AK1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AL1" s="1" t="s">
+        <v>37</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>mort</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Female</t>
-        </is>
+    <row r="2" spans="1:38" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B2" t="s">
+        <v>39</v>
       </c>
       <c r="C2">
-        <v>15936.81738220334</v>
+        <v>20463.377275766281</v>
       </c>
       <c r="D2">
-        <v>13465.37902192904</v>
+        <v>17839.15714927057</v>
       </c>
       <c r="E2">
-        <v>18235.8410572486</v>
+        <v>22935.946428716881</v>
       </c>
       <c r="F2">
-        <v>28592.2402340249</v>
+        <v>42427.108481020623</v>
       </c>
       <c r="G2">
-        <v>24207.07799942461</v>
+        <v>36803.447414843911</v>
       </c>
       <c r="H2">
-        <v>32672.04512626504</v>
+        <v>47714.724979805469</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -585,31 +705,31 @@
         <v>0</v>
       </c>
       <c r="L2">
-        <v>3802767951.125311</v>
+        <v>5642805427.9757423</v>
       </c>
       <c r="M2">
-        <v>3219541373.923473</v>
+        <v>4894858506.1742401</v>
       </c>
       <c r="N2">
-        <v>4345382001.793251</v>
+        <v>6346058422.314127</v>
       </c>
       <c r="O2">
-        <v>68586.37060359692</v>
+        <v>60812.327020701341</v>
       </c>
       <c r="P2">
-        <v>58710.64390858215</v>
+        <v>52055.982049259008</v>
       </c>
       <c r="Q2">
-        <v>77619.82193126234</v>
+        <v>68821.865817244281</v>
       </c>
       <c r="R2">
-        <v>122799.2240329562</v>
+        <v>118382.8271450311</v>
       </c>
       <c r="S2">
-        <v>105117.4081818382</v>
+        <v>101336.9266843623</v>
       </c>
       <c r="T2">
-        <v>138973.0032199053</v>
+        <v>133974.92653204821</v>
       </c>
       <c r="U2">
         <v>0</v>
@@ -621,31 +741,31 @@
         <v>0</v>
       </c>
       <c r="X2">
-        <v>16332296796.38318</v>
+        <v>15744916010.289141</v>
       </c>
       <c r="Y2">
-        <v>13980615288.18448</v>
+        <v>13477811249.020189</v>
       </c>
       <c r="Z2">
-        <v>18483409428.2474</v>
+        <v>17818665228.762409</v>
       </c>
       <c r="AA2">
-        <v>52649.55322139358</v>
+        <v>40348.94974493506</v>
       </c>
       <c r="AB2">
-        <v>45245.26488665312</v>
+        <v>34216.824899988438</v>
       </c>
       <c r="AC2">
-        <v>59383.98087401374</v>
+        <v>45885.9193885274</v>
       </c>
       <c r="AD2">
-        <v>94206.98379893134</v>
+        <v>75955.718664010506</v>
       </c>
       <c r="AE2">
-        <v>80910.3301824136</v>
+        <v>64533.479269518437</v>
       </c>
       <c r="AF2">
-        <v>106300.9580936402</v>
+        <v>86260.20155224271</v>
       </c>
       <c r="AG2">
         <v>0</v>
@@ -657,43 +777,39 @@
         <v>0</v>
       </c>
       <c r="AJ2">
-        <v>12529528845.25787</v>
+        <v>10102110582.3134</v>
       </c>
       <c r="AK2">
-        <v>10761073914.26101</v>
+        <v>8582952742.845953</v>
       </c>
       <c r="AL2">
-        <v>14138027426.45415</v>
+        <v>11472606806.44828</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>mort</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Male</t>
-        </is>
+    <row r="3" spans="1:38" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B3" t="s">
+        <v>40</v>
       </c>
       <c r="C3">
-        <v>21720.57273946307</v>
+        <v>30626.342983446579</v>
       </c>
       <c r="D3">
-        <v>18430.69426501219</v>
+        <v>26777.123652054321</v>
       </c>
       <c r="E3">
-        <v>24778.78513585294</v>
+        <v>34254.768141260713</v>
       </c>
       <c r="F3">
-        <v>28956.00321587296</v>
+        <v>49488.992334981398</v>
       </c>
       <c r="G3">
-        <v>24681.27720300399</v>
+        <v>43131.107858199539</v>
       </c>
       <c r="H3">
-        <v>32934.56766132678</v>
+        <v>55475.146222208139</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -705,31 +821,31 @@
         <v>0</v>
       </c>
       <c r="L3">
-        <v>3851148427.711103</v>
+        <v>6582035980.5525265</v>
       </c>
       <c r="M3">
-        <v>3282609867.99953</v>
+        <v>5736437345.1405382</v>
       </c>
       <c r="N3">
-        <v>4380297498.956462</v>
+        <v>7378194447.5536823</v>
       </c>
       <c r="O3">
-        <v>104678.695070751</v>
+        <v>98411.136260928019</v>
       </c>
       <c r="P3">
-        <v>89606.04763057169</v>
+        <v>84240.95234675247</v>
       </c>
       <c r="Q3">
-        <v>118465.835119762</v>
+        <v>111372.7815803948</v>
       </c>
       <c r="R3">
-        <v>160205.8615314264</v>
+        <v>157474.83013748869</v>
       </c>
       <c r="S3">
-        <v>137137.8774771607</v>
+        <v>134800.0863058035</v>
       </c>
       <c r="T3">
-        <v>181306.4364680289</v>
+        <v>178215.70330019339</v>
       </c>
       <c r="U3">
         <v>0</v>
@@ -741,31 +857,31 @@
         <v>0</v>
       </c>
       <c r="X3">
-        <v>21307379583.67971</v>
+        <v>20944152408.285992</v>
       </c>
       <c r="Y3">
-        <v>18239337704.46237</v>
+        <v>17928411478.671871</v>
       </c>
       <c r="Z3">
-        <v>24113756050.24784</v>
+        <v>23702688538.92572</v>
       </c>
       <c r="AA3">
-        <v>82958.12233128797</v>
+        <v>67784.79327748144</v>
       </c>
       <c r="AB3">
-        <v>71175.35336555949</v>
+        <v>57463.828694698153</v>
       </c>
       <c r="AC3">
-        <v>93687.04998390902</v>
+        <v>77118.013439134142</v>
       </c>
       <c r="AD3">
-        <v>131249.8583155535</v>
+        <v>107985.8378025073</v>
       </c>
       <c r="AE3">
-        <v>112456.6002741567</v>
+        <v>91668.978447603964</v>
       </c>
       <c r="AF3">
-        <v>148371.8688067021</v>
+        <v>122740.5570779853</v>
       </c>
       <c r="AG3">
         <v>0</v>
@@ -777,145 +893,137 @@
         <v>0</v>
       </c>
       <c r="AJ3">
-        <v>17456231155.96861</v>
+        <v>14362116427.733471</v>
       </c>
       <c r="AK3">
-        <v>14956727836.46284</v>
+        <v>12191974133.53133</v>
       </c>
       <c r="AL3">
-        <v>19733458551.29138</v>
+        <v>16324494091.37204</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>bc</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Female</t>
-        </is>
+    <row r="4" spans="1:38" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B4" t="s">
+        <v>39</v>
       </c>
       <c r="C4">
-        <v>830.3701511487852</v>
+        <v>1056.137328627854</v>
       </c>
       <c r="D4">
-        <v>23.96606678829604</v>
+        <v>60.930053786220753</v>
       </c>
       <c r="E4">
-        <v>1679.989000054051</v>
+        <v>2137.5702310948918</v>
       </c>
       <c r="F4">
-        <v>218.1251200341125</v>
+        <v>296.6374997337918</v>
       </c>
       <c r="G4">
-        <v>4.107719637279583</v>
+        <v>12.497319540802421</v>
       </c>
       <c r="H4">
-        <v>558.0467703075753</v>
+        <v>759.76168196758886</v>
       </c>
       <c r="I4">
-        <v>36608528.85369654</v>
+        <v>46561926.407216176</v>
       </c>
       <c r="J4">
-        <v>1056591.986495604</v>
+        <v>2686223.2812731131</v>
       </c>
       <c r="K4">
-        <v>74065675.04538301</v>
+        <v>94239058.778280437</v>
       </c>
       <c r="L4">
-        <v>29010640.96453696</v>
+        <v>39452787.464594312</v>
       </c>
       <c r="M4">
-        <v>546326.7117581846</v>
+        <v>1662143.498926722</v>
       </c>
       <c r="N4">
-        <v>74220220.45090751</v>
+        <v>101048303.7016893</v>
       </c>
       <c r="O4">
-        <v>5267.734272269137</v>
+        <v>5035.9010316036329</v>
       </c>
       <c r="P4">
-        <v>-109.9778120386587</v>
+        <v>-105.13768319988129</v>
       </c>
       <c r="Q4">
-        <v>10508.09459977117</v>
+        <v>10045.63284707618</v>
       </c>
       <c r="R4">
-        <v>1425.104132033504</v>
+        <v>1395.2524551587869</v>
       </c>
       <c r="S4">
-        <v>-22.37616814995075</v>
+        <v>-21.907454231934391</v>
       </c>
       <c r="T4">
-        <v>3596.626500588687</v>
+        <v>3521.2879132382768</v>
       </c>
       <c r="U4">
-        <v>232238600.8615297</v>
+        <v>222017768.78030801</v>
       </c>
       <c r="V4">
-        <v>-4848591.799348344</v>
+        <v>-4635205.0392331639</v>
       </c>
       <c r="W4">
-        <v>463270366.6201096</v>
+        <v>442881815.32904661</v>
       </c>
       <c r="X4">
-        <v>189538849.5604561</v>
+        <v>185568576.53611869</v>
       </c>
       <c r="Y4">
-        <v>-2976030.36394345</v>
+        <v>-2913691.412847274</v>
       </c>
       <c r="Z4">
-        <v>478351324.5782954</v>
+        <v>468331292.46069092</v>
       </c>
       <c r="AA4">
-        <v>4437.364121120352</v>
+        <v>3979.7637029757789</v>
       </c>
       <c r="AB4">
-        <v>-133.9438788269547</v>
+        <v>-166.06773698610209</v>
       </c>
       <c r="AC4">
-        <v>8828.105599717122</v>
+        <v>7908.0626159812919</v>
       </c>
       <c r="AD4">
-        <v>1206.979011999392</v>
+        <v>1098.614955424996</v>
       </c>
       <c r="AE4">
-        <v>-26.48388778723034</v>
+        <v>-34.40477377273681</v>
       </c>
       <c r="AF4">
-        <v>3038.579730281112</v>
+        <v>2761.5262312706882</v>
       </c>
       <c r="AG4">
-        <v>195630072.0078331</v>
+        <v>175455842.37309191</v>
       </c>
       <c r="AH4">
-        <v>-5905183.785843948</v>
+        <v>-7321428.3205062766</v>
       </c>
       <c r="AI4">
-        <v>389204691.5747266</v>
+        <v>348642756.55076623</v>
       </c>
       <c r="AJ4">
-        <v>160528208.5959191</v>
+        <v>146115789.07152441</v>
       </c>
       <c r="AK4">
-        <v>-3522357.075701635</v>
+        <v>-4575834.9117739964</v>
       </c>
       <c r="AL4">
-        <v>404131104.1273879</v>
+        <v>367282988.75900161</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>bc</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Male</t>
-        </is>
+    <row r="5" spans="1:38" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B5" t="s">
+        <v>40</v>
       </c>
       <c r="C5">
         <v>0</v>
@@ -1026,994 +1134,958 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>cvd</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Female</t>
-        </is>
+    <row r="6" spans="1:38" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B6" t="s">
+        <v>39</v>
       </c>
       <c r="C6">
-        <v>12451.16645341587</v>
+        <v>15383.965169078831</v>
       </c>
       <c r="D6">
-        <v>7769.141426128057</v>
+        <v>9729.1062145317173</v>
       </c>
       <c r="E6">
-        <v>16996.05159522851</v>
+        <v>21012.330214165431</v>
       </c>
       <c r="F6">
-        <v>1941.523584318884</v>
+        <v>2608.8504010910592</v>
       </c>
       <c r="G6">
-        <v>958.8599264275309</v>
+        <v>1295.5314070041859</v>
       </c>
       <c r="H6">
-        <v>3211.797140461129</v>
+        <v>4336.1906751912311</v>
       </c>
       <c r="I6">
-        <v>693554873.7881713</v>
+        <v>856917627.84802961</v>
       </c>
       <c r="J6">
-        <v>432756715.7181846</v>
+        <v>541930674.36184478</v>
       </c>
       <c r="K6">
-        <v>946714065.9574171</v>
+        <v>1170428817.5894411</v>
       </c>
       <c r="L6">
-        <v>258222636.7144116</v>
+        <v>346977103.34511077</v>
       </c>
       <c r="M6">
-        <v>127528370.2148616</v>
+        <v>172305677.13155669</v>
       </c>
       <c r="N6">
-        <v>427169019.6813302</v>
+        <v>576713359.80043375</v>
       </c>
       <c r="O6">
-        <v>67272.25267452786</v>
+        <v>62026.800699346823</v>
       </c>
       <c r="P6">
-        <v>43957.41469438181</v>
+        <v>40529.901885378029</v>
       </c>
       <c r="Q6">
-        <v>88207.3628523323</v>
+        <v>81329.527380732266</v>
       </c>
       <c r="R6">
-        <v>10441.48314496201</v>
+        <v>10078.894699190099</v>
       </c>
       <c r="S6">
-        <v>5354.921969340434</v>
+        <v>5168.9682300931599</v>
       </c>
       <c r="T6">
-        <v>16689.03844293452</v>
+        <v>16109.498886490321</v>
       </c>
       <c r="U6">
-        <v>3747199018.476547</v>
+        <v>3455016852.5550218</v>
       </c>
       <c r="V6">
-        <v>2448515913.30646</v>
+        <v>2257596594.819324</v>
       </c>
       <c r="W6">
-        <v>4913326525.600606</v>
+        <v>4530217334.1615686</v>
       </c>
       <c r="X6">
-        <v>1388717258.279947</v>
+        <v>1340492994.9922831</v>
       </c>
       <c r="Y6">
-        <v>712204621.9222777</v>
+        <v>687472774.60239029</v>
       </c>
       <c r="Z6">
-        <v>2219642112.910292</v>
+        <v>2142563351.9032121</v>
       </c>
       <c r="AA6">
-        <v>54821.08622111199</v>
+        <v>46642.835530267992</v>
       </c>
       <c r="AB6">
-        <v>36188.27326825375</v>
+        <v>30800.79567084631</v>
       </c>
       <c r="AC6">
-        <v>71211.31125710379</v>
+        <v>60317.197166566839</v>
       </c>
       <c r="AD6">
-        <v>8499.959560643121</v>
+        <v>7470.044298099042</v>
       </c>
       <c r="AE6">
-        <v>4396.062042912903</v>
+        <v>3873.4368230889741</v>
       </c>
       <c r="AF6">
-        <v>13477.2413024734</v>
+        <v>11773.308211299091</v>
       </c>
       <c r="AG6">
-        <v>3053644144.688375</v>
+        <v>2598099224.7069931</v>
       </c>
       <c r="AH6">
-        <v>2015759197.588276</v>
+        <v>1715665920.45748</v>
       </c>
       <c r="AI6">
-        <v>3966612459.643189</v>
+        <v>3359788516.5721269</v>
       </c>
       <c r="AJ6">
-        <v>1130494621.565535</v>
+        <v>993515891.64717257</v>
       </c>
       <c r="AK6">
-        <v>584676251.7074161</v>
+        <v>515167097.4708336</v>
       </c>
       <c r="AL6">
-        <v>1792473093.228961</v>
+        <v>1565849992.102778</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>cvd</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Male</t>
-        </is>
+    <row r="7" spans="1:38" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>42</v>
+      </c>
+      <c r="B7" t="s">
+        <v>40</v>
       </c>
       <c r="C7">
-        <v>13770.2100899151</v>
+        <v>18924.582063234309</v>
       </c>
       <c r="D7">
-        <v>8846.247302135826</v>
+        <v>12240.197289777831</v>
       </c>
       <c r="E7">
-        <v>18503.50329710171</v>
+        <v>25508.559896471401</v>
       </c>
       <c r="F7">
-        <v>1590.615778847993</v>
+        <v>2449.2785101332411</v>
       </c>
       <c r="G7">
-        <v>805.0283972465458</v>
+        <v>1235.5295117824789</v>
       </c>
       <c r="H7">
-        <v>2596.879168300507</v>
+        <v>4037.7173363584729</v>
       </c>
       <c r="I7">
-        <v>767028242.4284511</v>
+        <v>1054137070.086274</v>
       </c>
       <c r="J7">
-        <v>492753667.2235696</v>
+        <v>681803469.43520474</v>
       </c>
       <c r="K7">
-        <v>1030682140.655158</v>
+        <v>1420877803.3532519</v>
       </c>
       <c r="L7">
-        <v>211551898.586783</v>
+        <v>325754041.84772098</v>
       </c>
       <c r="M7">
-        <v>107068776.8337906</v>
+        <v>164325425.06706971</v>
       </c>
       <c r="N7">
-        <v>345384929.3839675</v>
+        <v>537016405.735677</v>
       </c>
       <c r="O7">
-        <v>86461.39193134329</v>
+        <v>82750.82644288789</v>
       </c>
       <c r="P7">
-        <v>56496.09027614217</v>
+        <v>54071.511650600369</v>
       </c>
       <c r="Q7">
-        <v>113368.1580086796</v>
+        <v>108502.8653595535</v>
       </c>
       <c r="R7">
-        <v>10992.80153703313</v>
+        <v>10804.30530776621</v>
       </c>
       <c r="S7">
-        <v>5637.665994189798</v>
+        <v>5540.9955705319708</v>
       </c>
       <c r="T7">
-        <v>17570.23259053153</v>
+        <v>17268.951558621589</v>
       </c>
       <c r="U7">
-        <v>4816072453.3597</v>
+        <v>4609386534.5217505</v>
       </c>
       <c r="V7">
-        <v>3146945220.56166</v>
+        <v>3011891341.9617391</v>
       </c>
       <c r="W7">
-        <v>6314833137.399492</v>
+        <v>6043826606.2578449</v>
       </c>
       <c r="X7">
-        <v>1462042604.425406</v>
+        <v>1436972605.9329059</v>
       </c>
       <c r="Y7">
-        <v>749809577.2272431</v>
+        <v>736952410.88075209</v>
       </c>
       <c r="Z7">
-        <v>2336840934.540693</v>
+        <v>2296770557.2966719</v>
       </c>
       <c r="AA7">
-        <v>72691.18184142819</v>
+        <v>63826.244379653581</v>
       </c>
       <c r="AB7">
-        <v>47649.84297400635</v>
+        <v>41831.314360822536</v>
       </c>
       <c r="AC7">
-        <v>94864.6547115779</v>
+        <v>82994.305463082099</v>
       </c>
       <c r="AD7">
-        <v>9402.185758185135</v>
+        <v>8355.0267976329724</v>
       </c>
       <c r="AE7">
-        <v>4832.637596943252</v>
+        <v>4305.4660587494918</v>
       </c>
       <c r="AF7">
-        <v>14973.35342223102</v>
+        <v>13231.23422226312</v>
       </c>
       <c r="AG7">
-        <v>4049044210.931249</v>
+        <v>3555249464.4354758</v>
       </c>
       <c r="AH7">
-        <v>2654191553.33809</v>
+        <v>2330087872.5265341</v>
       </c>
       <c r="AI7">
-        <v>5284150996.744334</v>
+        <v>4622948802.9045935</v>
       </c>
       <c r="AJ7">
-        <v>1250490705.838623</v>
+        <v>1111218564.085186</v>
       </c>
       <c r="AK7">
-        <v>642740800.3934524</v>
+        <v>572626985.81368232</v>
       </c>
       <c r="AL7">
-        <v>1991456005.156725</v>
+        <v>1759754151.5609951</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>cancer</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Female</t>
-        </is>
+    <row r="8" spans="1:38" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>43</v>
+      </c>
+      <c r="B8" t="s">
+        <v>39</v>
       </c>
       <c r="C8">
-        <v>12608.35094939108</v>
+        <v>16858.195079461009</v>
       </c>
       <c r="D8">
-        <v>341.5126919798212</v>
+        <v>968.50307140482755</v>
       </c>
       <c r="E8">
-        <v>25503.27169059733</v>
+        <v>34126.387302877003</v>
       </c>
       <c r="F8">
-        <v>3597.011972976959</v>
+        <v>5081.8859919416727</v>
       </c>
       <c r="G8">
-        <v>72.0527039690197</v>
+        <v>230.71396026469961</v>
       </c>
       <c r="H8">
-        <v>8398.947917194482</v>
+        <v>11880.594263710949</v>
       </c>
       <c r="I8">
-        <v>186691852.5076337</v>
+        <v>249619294.54157951</v>
       </c>
       <c r="J8">
-        <v>5056778.43014523</v>
+        <v>14340624.97829131</v>
       </c>
       <c r="K8">
-        <v>377626943.9226753</v>
+        <v>505309416.79369998</v>
       </c>
       <c r="L8">
-        <v>478402592.4059356</v>
+        <v>675890836.92824244</v>
       </c>
       <c r="M8">
-        <v>9583009.62787962</v>
+        <v>30684956.715205051</v>
       </c>
       <c r="N8">
-        <v>1117060072.986866</v>
+        <v>1580119037.0735569</v>
       </c>
       <c r="O8">
-        <v>80903.92992485018</v>
+        <v>78495.714998487034</v>
       </c>
       <c r="P8">
-        <v>-1689.082390754535</v>
+        <v>-1638.804568292139</v>
       </c>
       <c r="Q8">
-        <v>161387.440064886</v>
+        <v>156583.5245758266</v>
       </c>
       <c r="R8">
-        <v>23543.62622491</v>
+        <v>23192.491223051009</v>
       </c>
       <c r="S8">
-        <v>-388.8818481542627</v>
+        <v>-383.08197573146339</v>
       </c>
       <c r="T8">
-        <v>54230.82440651565</v>
+        <v>53422.013544208778</v>
       </c>
       <c r="U8">
-        <v>1197944490.39726</v>
+        <v>1162286051.982595</v>
       </c>
       <c r="V8">
-        <v>-25010242.95990245</v>
+        <v>-24265779.242701739</v>
       </c>
       <c r="W8">
-        <v>2389663825.040776</v>
+        <v>2318532248.3942609</v>
       </c>
       <c r="X8">
-        <v>3131302287.913031</v>
+        <v>3084601332.6657839</v>
       </c>
       <c r="Y8">
-        <v>-51721285.80451694</v>
+        <v>-50949902.772284627</v>
       </c>
       <c r="Z8">
-        <v>7212699646.066581</v>
+        <v>7105127801.3797674</v>
       </c>
       <c r="AA8">
-        <v>68295.5789754591</v>
+        <v>61637.519919026017</v>
       </c>
       <c r="AB8">
-        <v>-2030.595082734356</v>
+        <v>-2607.3076396969659</v>
       </c>
       <c r="AC8">
-        <v>135884.1683742887</v>
+        <v>122457.13727294961</v>
       </c>
       <c r="AD8">
-        <v>19946.61425193305</v>
+        <v>18110.605231109341</v>
       </c>
       <c r="AE8">
-        <v>-460.9345521232825</v>
+        <v>-613.79593599616305</v>
       </c>
       <c r="AF8">
-        <v>45831.87648932116</v>
+        <v>41541.41928049783</v>
       </c>
       <c r="AG8">
-        <v>1011252637.889627</v>
+        <v>912666757.44101596</v>
       </c>
       <c r="AH8">
-        <v>-30067021.39004768</v>
+        <v>-38606404.220993049</v>
       </c>
       <c r="AI8">
-        <v>2012036881.1181</v>
+        <v>1813222831.6005609</v>
       </c>
       <c r="AJ8">
-        <v>2652899695.507095</v>
+        <v>2408710495.7375422</v>
       </c>
       <c r="AK8">
-        <v>-61304295.43239656</v>
+        <v>-81634859.487489671</v>
       </c>
       <c r="AL8">
-        <v>6095639573.079715</v>
+        <v>5525008764.3062115</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>cancer</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Male</t>
-        </is>
+    <row r="9" spans="1:38" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>43</v>
+      </c>
+      <c r="B9" t="s">
+        <v>40</v>
       </c>
       <c r="C9">
-        <v>7280.920694582312</v>
+        <v>9883.2734920185285</v>
       </c>
       <c r="D9">
-        <v>113.2657565906829</v>
+        <v>430.6174092848853</v>
       </c>
       <c r="E9">
-        <v>14697.12783036198</v>
+        <v>19969.781021917632</v>
       </c>
       <c r="F9">
-        <v>1076.400255575184</v>
+        <v>1605.8275695762629</v>
       </c>
       <c r="G9">
-        <v>13.75343852158111</v>
+        <v>63.630473402829679</v>
       </c>
       <c r="H9">
-        <v>2509.739008195952</v>
+        <v>3749.0283877820989</v>
       </c>
       <c r="I9">
-        <v>107808592.7246803</v>
+        <v>146341630.59631851</v>
       </c>
       <c r="J9">
-        <v>1677126.057838241</v>
+        <v>6376151.9792812876</v>
       </c>
       <c r="K9">
-        <v>217620371.78417</v>
+        <v>295692547.59153438</v>
       </c>
       <c r="L9">
-        <v>143161233.9914995</v>
+        <v>213575066.75364301</v>
       </c>
       <c r="M9">
-        <v>1829207.323370288</v>
+        <v>8462852.9625763465</v>
       </c>
       <c r="N9">
-        <v>333795288.0900615</v>
+        <v>498620775.57501918</v>
       </c>
       <c r="O9">
-        <v>51212.84679198766</v>
+        <v>49665.124841932273</v>
       </c>
       <c r="P9">
-        <v>-1069.202914828812</v>
+        <v>-1036.890147154239</v>
       </c>
       <c r="Q9">
-        <v>102159.5644348961</v>
+        <v>99072.163319973421</v>
       </c>
       <c r="R9">
-        <v>8420.880817681866</v>
+        <v>8301.6484321931348</v>
       </c>
       <c r="S9">
-        <v>-139.0918996157926</v>
+        <v>-137.12247867843229</v>
       </c>
       <c r="T9">
-        <v>19396.812734341</v>
+        <v>19122.17065077916</v>
       </c>
       <c r="U9">
-        <v>758308622.4489565</v>
+        <v>735391503.53449142</v>
       </c>
       <c r="V9">
-        <v>-15831687.55987027</v>
+        <v>-15353232.40891281</v>
       </c>
       <c r="W9">
-        <v>1512676670.587509</v>
+        <v>1466961522.2788451</v>
       </c>
       <c r="X9">
-        <v>1119977148.751688</v>
+        <v>1104119241.4816871</v>
       </c>
       <c r="Y9">
-        <v>-18499222.64890042</v>
+        <v>-18237289.664231502</v>
       </c>
       <c r="Z9">
-        <v>2579776093.667353</v>
+        <v>2543248696.553628</v>
       </c>
       <c r="AA9">
-        <v>43931.92609740535</v>
+        <v>39781.851349913733</v>
       </c>
       <c r="AB9">
-        <v>-1182.468671419495</v>
+        <v>-1467.507556439125</v>
       </c>
       <c r="AC9">
-        <v>87462.4366045341</v>
+        <v>79102.382298055789</v>
       </c>
       <c r="AD9">
-        <v>7344.480562106682</v>
+        <v>6695.8208626168716</v>
       </c>
       <c r="AE9">
-        <v>-152.8453381373737</v>
+        <v>-200.75295208126201</v>
       </c>
       <c r="AF9">
-        <v>16887.07372614504</v>
+        <v>15373.14226299706</v>
       </c>
       <c r="AG9">
-        <v>650500029.7242762</v>
+        <v>589049872.93817294</v>
       </c>
       <c r="AH9">
-        <v>-17508813.61770852</v>
+        <v>-21729384.388194099</v>
       </c>
       <c r="AI9">
-        <v>1295056298.803339</v>
+        <v>1171268974.6873109</v>
       </c>
       <c r="AJ9">
-        <v>976815914.7601887</v>
+        <v>890544174.72804379</v>
       </c>
       <c r="AK9">
-        <v>-20328429.97227071</v>
+        <v>-26700142.62680785</v>
       </c>
       <c r="AL9">
-        <v>2245980805.577291</v>
+        <v>2044627920.9786091</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>diab2</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Female</t>
-        </is>
+    <row r="10" spans="1:38" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>44</v>
+      </c>
+      <c r="B10" t="s">
+        <v>39</v>
       </c>
       <c r="C10">
-        <v>2004.309455944744</v>
+        <v>2642.136597655282</v>
       </c>
       <c r="D10">
-        <v>-38.22584290513367</v>
+        <v>-77.872790168370557</v>
       </c>
       <c r="E10">
-        <v>3716.711599418889</v>
+        <v>4972.0184620661921</v>
       </c>
       <c r="F10">
-        <v>671.3461051168656</v>
+        <v>925.63781419722295</v>
       </c>
       <c r="G10">
-        <v>-9.529064761315126</v>
+        <v>-20.626622289248289</v>
       </c>
       <c r="H10">
-        <v>1580.452775246205</v>
+        <v>2212.8898330864149</v>
       </c>
       <c r="I10">
-        <v>150726075.3965008</v>
+        <v>198691314.28027591</v>
       </c>
       <c r="J10">
-        <v>-2874621.612308952</v>
+        <v>-5856111.6934516374</v>
       </c>
       <c r="K10">
-        <v>279500428.9879004</v>
+        <v>373900760.36583889</v>
       </c>
       <c r="L10">
-        <v>89289031.98054312</v>
+        <v>123109829.2882307</v>
       </c>
       <c r="M10">
-        <v>-1267365.613254912</v>
+        <v>-2743340.7644700231</v>
       </c>
       <c r="N10">
-        <v>210200219.1077453</v>
+        <v>294314347.80049318</v>
       </c>
       <c r="O10">
-        <v>12335.51081750371</v>
+        <v>12056.6702807696</v>
       </c>
       <c r="P10">
         <v>0</v>
       </c>
       <c r="Q10">
-        <v>22493.13134572677</v>
+        <v>21984.680831592039</v>
       </c>
       <c r="R10">
-        <v>4275.978687774265</v>
+        <v>4204.4168412001727</v>
       </c>
       <c r="S10">
         <v>0</v>
       </c>
       <c r="T10">
-        <v>9899.21418616458</v>
+        <v>9733.5430969190547</v>
       </c>
       <c r="U10">
-        <v>927642748.9870987</v>
+        <v>906673661.78415251</v>
       </c>
       <c r="V10">
         <v>0</v>
       </c>
       <c r="W10">
-        <v>1691505970.330006</v>
+        <v>1653269983.216557</v>
       </c>
       <c r="X10">
-        <v>568705165.4739773</v>
+        <v>559187439.87962294</v>
       </c>
       <c r="Y10">
         <v>0</v>
       </c>
       <c r="Z10">
-        <v>1316595486.759889</v>
+        <v>1294561231.890234</v>
       </c>
       <c r="AA10">
-        <v>10331.20136155897</v>
+        <v>9414.5336831143213</v>
       </c>
       <c r="AB10">
-        <v>38.22584290513367</v>
+        <v>77.872790168370557</v>
       </c>
       <c r="AC10">
-        <v>18776.41974630788</v>
+        <v>17012.662369525849</v>
       </c>
       <c r="AD10">
-        <v>3604.6325826574</v>
+        <v>3278.77902700295</v>
       </c>
       <c r="AE10">
-        <v>9.529064761315126</v>
+        <v>20.626622289248289</v>
       </c>
       <c r="AF10">
-        <v>8318.761410918374</v>
+        <v>7520.6532638326398</v>
       </c>
       <c r="AG10">
-        <v>776916673.5905979</v>
+        <v>707982347.50387657</v>
       </c>
       <c r="AH10">
-        <v>2874621.612308952</v>
+        <v>5856111.6934516374</v>
       </c>
       <c r="AI10">
-        <v>1412005541.342106</v>
+        <v>1279369222.850718</v>
       </c>
       <c r="AJ10">
-        <v>479416133.4934342</v>
+        <v>436077610.59139222</v>
       </c>
       <c r="AK10">
-        <v>1267365.613254912</v>
+        <v>2743340.7644700231</v>
       </c>
       <c r="AL10">
-        <v>1106395267.652144</v>
+        <v>1000246884.089741</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>diab2</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Male</t>
-        </is>
+    <row r="11" spans="1:38" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>44</v>
+      </c>
+      <c r="B11" t="s">
+        <v>40</v>
       </c>
       <c r="C11">
-        <v>2148.040713968812</v>
+        <v>3126.1926537410732</v>
       </c>
       <c r="D11">
-        <v>-31.63323760894794</v>
+        <v>-82.81853487150974</v>
       </c>
       <c r="E11">
-        <v>3953.733148619258</v>
+        <v>5853.1299361032743</v>
       </c>
       <c r="F11">
-        <v>612.4907278556932</v>
+        <v>942.3777145710344</v>
       </c>
       <c r="G11">
-        <v>-7.680382973848277</v>
+        <v>-20.12635281937332</v>
       </c>
       <c r="H11">
-        <v>1436.537461637133</v>
+        <v>2247.6472436891258</v>
       </c>
       <c r="I11">
-        <v>161534809.7311683</v>
+        <v>235092813.75398299</v>
       </c>
       <c r="J11">
-        <v>-2378851.101430498</v>
+        <v>-6228036.6408723993</v>
       </c>
       <c r="K11">
-        <v>297324686.5093169</v>
+        <v>440161224.32490212</v>
       </c>
       <c r="L11">
-        <v>81461266.8048072</v>
+        <v>125336236.0379476</v>
       </c>
       <c r="M11">
-        <v>-1021490.935521821</v>
+        <v>-2676804.924976652</v>
       </c>
       <c r="N11">
-        <v>191059482.3977386</v>
+        <v>298937083.41065371</v>
       </c>
       <c r="O11">
-        <v>16341.50219780824</v>
+        <v>16096.82026023769</v>
       </c>
       <c r="P11">
         <v>0</v>
       </c>
       <c r="Q11">
-        <v>29797.83818925521</v>
+        <v>29351.67401809747</v>
       </c>
       <c r="R11">
-        <v>4996.956599485138</v>
+        <v>4938.0960707948789</v>
       </c>
       <c r="S11">
         <v>0</v>
       </c>
       <c r="T11">
-        <v>11568.33260154067</v>
+        <v>11432.066024188051</v>
       </c>
       <c r="U11">
-        <v>1228897306.777378</v>
+        <v>1210496980.3901379</v>
       </c>
       <c r="V11">
         <v>0</v>
       </c>
       <c r="W11">
-        <v>2240827229.670175</v>
+        <v>2207275237.8349309</v>
       </c>
       <c r="X11">
-        <v>664595227.7315234</v>
+        <v>656766777.41571891</v>
       </c>
       <c r="Y11">
         <v>0</v>
       </c>
       <c r="Z11">
-        <v>1538588236.004909</v>
+        <v>1520464781.217011</v>
       </c>
       <c r="AA11">
-        <v>14193.46148383943</v>
+        <v>12970.627606496621</v>
       </c>
       <c r="AB11">
-        <v>31.63323760894794</v>
+        <v>82.81853487150974</v>
       </c>
       <c r="AC11">
-        <v>25844.10504063595</v>
+        <v>23498.54408199419</v>
       </c>
       <c r="AD11">
-        <v>4384.465871629445</v>
+        <v>3995.7183562238438</v>
       </c>
       <c r="AE11">
-        <v>7.680382973848277</v>
+        <v>20.12635281937332</v>
       </c>
       <c r="AF11">
-        <v>10131.79513990353</v>
+        <v>9184.4187804989251</v>
       </c>
       <c r="AG11">
-        <v>1067362497.04621</v>
+        <v>975404166.63615489</v>
       </c>
       <c r="AH11">
-        <v>2378851.101430498</v>
+        <v>6228036.6408723993</v>
       </c>
       <c r="AI11">
-        <v>1943502543.160858</v>
+        <v>1767114013.5100291</v>
       </c>
       <c r="AJ11">
-        <v>583133960.9267162</v>
+        <v>531430541.37777132</v>
       </c>
       <c r="AK11">
-        <v>1021490.935521821</v>
+        <v>2676804.924976652</v>
       </c>
       <c r="AL11">
-        <v>1347528753.60717</v>
+        <v>1221527697.8063569</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>dem</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Female</t>
-        </is>
+    <row r="12" spans="1:38" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>45</v>
+      </c>
+      <c r="B12" t="s">
+        <v>39</v>
       </c>
       <c r="C12">
-        <v>5704.556738423242</v>
+        <v>6641.564563772612</v>
       </c>
       <c r="D12">
-        <v>4110.358339865177</v>
+        <v>4882.4975768912418</v>
       </c>
       <c r="E12">
-        <v>7131.222289336152</v>
+        <v>8227.84256480152</v>
       </c>
       <c r="F12">
-        <v>1696.011621456228</v>
+        <v>2132.8191250745049</v>
       </c>
       <c r="G12">
-        <v>981.3754516187024</v>
+        <v>1254.2807715331189</v>
       </c>
       <c r="H12">
-        <v>2409.694859134266</v>
+        <v>3011.0431334448949</v>
       </c>
       <c r="I12">
-        <v>96059030.91830906</v>
+        <v>111837305.6893671</v>
       </c>
       <c r="J12">
-        <v>69214324.08498967</v>
+        <v>82216376.69727169</v>
       </c>
       <c r="K12">
-        <v>120082652.1301314</v>
+        <v>138548640.9486931</v>
       </c>
       <c r="L12">
-        <v>225569545.6536784</v>
+        <v>283664943.63490921</v>
       </c>
       <c r="M12">
-        <v>130522935.0652874</v>
+        <v>166819342.61390489</v>
       </c>
       <c r="N12">
-        <v>320489416.2648574</v>
+        <v>400468736.74817097</v>
       </c>
       <c r="O12">
-        <v>32171.39524575697</v>
+        <v>28474.64780985158</v>
       </c>
       <c r="P12">
-        <v>23811.65577163275</v>
+        <v>21075.50843496856</v>
       </c>
       <c r="Q12">
-        <v>39090.87851330139</v>
+        <v>34599.027792888832</v>
       </c>
       <c r="R12">
-        <v>8964.67197227111</v>
+        <v>8475.0411745628644</v>
       </c>
       <c r="S12">
-        <v>5320.807584618855</v>
+        <v>5030.1966988924141</v>
       </c>
       <c r="T12">
-        <v>12405.74806267202</v>
+        <v>11728.17320673951</v>
       </c>
       <c r="U12">
-        <v>541734124.5433004</v>
+        <v>479484594.47009218</v>
       </c>
       <c r="V12">
-        <v>400964471.538523</v>
+        <v>354890486.53643668</v>
       </c>
       <c r="W12">
-        <v>658251303.2854826</v>
+        <v>582613029.0044533</v>
       </c>
       <c r="X12">
-        <v>1192301372.312057</v>
+        <v>1127180476.216861</v>
       </c>
       <c r="Y12">
-        <v>707667408.7543077</v>
+        <v>669016160.95269108</v>
       </c>
       <c r="Z12">
-        <v>1649964492.335379</v>
+        <v>1559847036.4963551</v>
       </c>
       <c r="AA12">
-        <v>26466.83850733373</v>
+        <v>21833.083246078961</v>
       </c>
       <c r="AB12">
-        <v>19701.29743176757</v>
+        <v>16193.010858077319</v>
       </c>
       <c r="AC12">
-        <v>31959.65622396523</v>
+        <v>26371.18522808731</v>
       </c>
       <c r="AD12">
-        <v>7268.660350814882</v>
+        <v>6342.2220494883604</v>
       </c>
       <c r="AE12">
-        <v>4339.432133000152</v>
+        <v>3775.915927359295</v>
       </c>
       <c r="AF12">
-        <v>9996.053203537755</v>
+        <v>8717.1300732946165</v>
       </c>
       <c r="AG12">
-        <v>445675093.6249913</v>
+        <v>367647288.78072512</v>
       </c>
       <c r="AH12">
-        <v>331750147.4535333</v>
+        <v>272674109.83916497</v>
       </c>
       <c r="AI12">
-        <v>538168651.1553513</v>
+        <v>444064388.0557602</v>
       </c>
       <c r="AJ12">
-        <v>966731826.6583791</v>
+        <v>843515532.58195186</v>
       </c>
       <c r="AK12">
-        <v>577144473.6890204</v>
+        <v>502196818.33878618</v>
       </c>
       <c r="AL12">
-        <v>1329475076.070521</v>
+        <v>1159378299.748184</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>dem</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Male</t>
-        </is>
+    <row r="13" spans="1:38" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>45</v>
+      </c>
+      <c r="B13" t="s">
+        <v>40</v>
       </c>
       <c r="C13">
-        <v>3638.22705415106</v>
+        <v>4576.5541362172344</v>
       </c>
       <c r="D13">
-        <v>2627.225361846554</v>
+        <v>3376.3433597340559</v>
       </c>
       <c r="E13">
-        <v>4538.771809711213</v>
+        <v>5652.3146401831355</v>
       </c>
       <c r="F13">
-        <v>555.135456549922</v>
+        <v>814.89415475720318</v>
       </c>
       <c r="G13">
-        <v>323.2138405875617</v>
+        <v>481.64524671107301</v>
       </c>
       <c r="H13">
-        <v>785.0259857140907</v>
+        <v>1146.226008474122</v>
       </c>
       <c r="I13">
-        <v>61264105.36484969</v>
+        <v>77064595.099762052</v>
       </c>
       <c r="J13">
-        <v>44239847.86813409</v>
+        <v>56854245.834561832</v>
       </c>
       <c r="K13">
-        <v>76428378.50372709</v>
+        <v>95179326.226043671</v>
       </c>
       <c r="L13">
-        <v>73833015.72113962</v>
+        <v>108380922.582708</v>
       </c>
       <c r="M13">
-        <v>42987440.7981457</v>
+        <v>64058817.812572703</v>
       </c>
       <c r="N13">
-        <v>104408456.0999741</v>
+        <v>152448059.12705821</v>
       </c>
       <c r="O13">
-        <v>22607.42410015239</v>
+        <v>20961.219199712828</v>
       </c>
       <c r="P13">
-        <v>16732.88324749115</v>
+        <v>15514.44481423692</v>
       </c>
       <c r="Q13">
-        <v>27469.8707422177</v>
+        <v>25469.597043190759</v>
       </c>
       <c r="R13">
-        <v>3724.500821296638</v>
+        <v>3640.729485625794</v>
       </c>
       <c r="S13">
-        <v>2210.605394170793</v>
+        <v>2160.8845388411492</v>
       </c>
       <c r="T13">
-        <v>5154.144958247179</v>
+        <v>5038.2181191592026</v>
       </c>
       <c r="U13">
-        <v>380686414.422466</v>
+        <v>352965970.10396409</v>
       </c>
       <c r="V13">
-        <v>281765021.0045031</v>
+        <v>261247736.226935</v>
       </c>
       <c r="W13">
-        <v>462565153.4282026</v>
+        <v>428882544.61029011</v>
       </c>
       <c r="X13">
-        <v>495358609.2324529</v>
+        <v>484217021.58823061</v>
       </c>
       <c r="Y13">
-        <v>294010517.4247155</v>
+        <v>287397643.66587281</v>
       </c>
       <c r="Z13">
-        <v>685501279.4468747</v>
+        <v>670083009.84817398</v>
       </c>
       <c r="AA13">
-        <v>18969.19704600133</v>
+        <v>16384.665063495599</v>
       </c>
       <c r="AB13">
-        <v>14105.65788564459</v>
+        <v>12138.101454502859</v>
       </c>
       <c r="AC13">
-        <v>22931.09893250648</v>
+        <v>19817.28240300763</v>
       </c>
       <c r="AD13">
-        <v>3169.365364746716</v>
+        <v>2825.835330868591</v>
       </c>
       <c r="AE13">
-        <v>1887.391553583232</v>
+        <v>1679.2392921300759</v>
       </c>
       <c r="AF13">
-        <v>4369.118972533088</v>
+        <v>3891.9921106850811</v>
       </c>
       <c r="AG13">
-        <v>319422309.0576164</v>
+        <v>275901375.00420201</v>
       </c>
       <c r="AH13">
-        <v>237525173.136369</v>
+        <v>204393490.3923732</v>
       </c>
       <c r="AI13">
-        <v>386136774.9244755</v>
+        <v>333703218.38424629</v>
       </c>
       <c r="AJ13">
-        <v>421525593.5113133</v>
+        <v>375836099.00552261</v>
       </c>
       <c r="AK13">
-        <v>251023076.6265698</v>
+        <v>223338825.85330001</v>
       </c>
       <c r="AL13">
-        <v>581092823.3469007</v>
+        <v>517634950.72111583</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>dep</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Female</t>
-        </is>
+    <row r="14" spans="1:38" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>46</v>
+      </c>
+      <c r="B14" t="s">
+        <v>39</v>
       </c>
       <c r="C14">
-        <v>67587.25211501982</v>
+        <v>92391.101291395025</v>
       </c>
       <c r="D14">
-        <v>50266.75700739733</v>
+        <v>68149.382492447796</v>
       </c>
       <c r="E14">
-        <v>81736.21956205854</v>
+        <v>112201.2114600035</v>
       </c>
       <c r="F14">
-        <v>64401.94708783021</v>
+        <v>93347.60397074536</v>
       </c>
       <c r="G14">
-        <v>29650.5062572388</v>
+        <v>42585.423339675792</v>
       </c>
       <c r="H14">
-        <v>118972.1819007881</v>
+        <v>173232.13512167311</v>
       </c>
       <c r="I14">
         <v>0</v>
@@ -2025,31 +2097,31 @@
         <v>0</v>
       </c>
       <c r="L14">
-        <v>8565458962.681417</v>
+        <v>12415231328.109131</v>
       </c>
       <c r="M14">
-        <v>3943517332.21276</v>
+        <v>5663861304.1768799</v>
       </c>
       <c r="N14">
-        <v>15823300192.80481</v>
+        <v>23039873971.182522</v>
       </c>
       <c r="O14">
-        <v>424800.9076185662</v>
+        <v>412256.25959497283</v>
       </c>
       <c r="P14">
-        <v>319020.455855674</v>
+        <v>309599.57360410242</v>
       </c>
       <c r="Q14">
-        <v>508614.5913819045</v>
+        <v>493594.87058065151</v>
       </c>
       <c r="R14">
-        <v>410810.763891281</v>
+        <v>405272.43687405728</v>
       </c>
       <c r="S14">
-        <v>190846.1828195405</v>
+        <v>188273.29850552769</v>
       </c>
       <c r="T14">
-        <v>751602.4213941777</v>
+        <v>741469.72682408465</v>
       </c>
       <c r="U14">
         <v>0</v>
@@ -2061,31 +2133,31 @@
         <v>0</v>
       </c>
       <c r="X14">
-        <v>54637831597.54037</v>
+        <v>53901234104.249619</v>
       </c>
       <c r="Y14">
-        <v>25382542314.99888</v>
+        <v>25040348701.235191</v>
       </c>
       <c r="Z14">
-        <v>99963122045.42563</v>
+        <v>98615473667.603256</v>
       </c>
       <c r="AA14">
-        <v>357213.6555035464</v>
+        <v>319865.1583035778</v>
       </c>
       <c r="AB14">
-        <v>268753.6988482766</v>
+        <v>241450.1911116546</v>
       </c>
       <c r="AC14">
-        <v>426878.371819846</v>
+        <v>381393.65912064799</v>
       </c>
       <c r="AD14">
-        <v>346408.8168034508</v>
+        <v>311924.83290331188</v>
       </c>
       <c r="AE14">
-        <v>161195.6765623017</v>
+        <v>145687.8751658519</v>
       </c>
       <c r="AF14">
-        <v>632630.2394933896</v>
+        <v>568237.59170241153</v>
       </c>
       <c r="AG14">
         <v>0</v>
@@ -2097,43 +2169,39 @@
         <v>0</v>
       </c>
       <c r="AJ14">
-        <v>46072372634.85895</v>
+        <v>41486002776.140488</v>
       </c>
       <c r="AK14">
-        <v>21439024982.78612</v>
+        <v>19376487397.058311</v>
       </c>
       <c r="AL14">
-        <v>84139821852.62082</v>
+        <v>75575599696.420731</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>dep</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Male</t>
-        </is>
+    <row r="15" spans="1:38" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
+        <v>46</v>
+      </c>
+      <c r="B15" t="s">
+        <v>40</v>
       </c>
       <c r="C15">
-        <v>27318.78515242044</v>
+        <v>41143.172649248423</v>
       </c>
       <c r="D15">
-        <v>20406.04303923879</v>
+        <v>30468.78972813642</v>
       </c>
       <c r="E15">
-        <v>32984.48756594546</v>
+        <v>49894.558910951033</v>
       </c>
       <c r="F15">
-        <v>20856.25373275864</v>
+        <v>34320.430846787109</v>
       </c>
       <c r="G15">
-        <v>9613.8571875216</v>
+        <v>15690.58497143784</v>
       </c>
       <c r="H15">
-        <v>38506.48210546467</v>
+        <v>63652.743374237019</v>
       </c>
       <c r="I15">
         <v>0</v>
@@ -2145,31 +2213,31 @@
         <v>0</v>
       </c>
       <c r="L15">
-        <v>2773881746.4569</v>
+        <v>4564617302.6226854</v>
       </c>
       <c r="M15">
-        <v>1278643005.940373</v>
+        <v>2086847801.2012329</v>
       </c>
       <c r="N15">
-        <v>5121362120.026802</v>
+        <v>8465814868.7735233</v>
       </c>
       <c r="O15">
-        <v>209223.0341274764</v>
+        <v>205076.27778749581</v>
       </c>
       <c r="P15">
-        <v>157124.0233384507</v>
+        <v>154009.85838687609</v>
       </c>
       <c r="Q15">
-        <v>250502.9676301416</v>
+        <v>245538.0517281426</v>
       </c>
       <c r="R15">
-        <v>172994.9280803206</v>
+        <v>171030.36687749409</v>
       </c>
       <c r="S15">
-        <v>80366.49614177944</v>
+        <v>79453.839903361208</v>
       </c>
       <c r="T15">
-        <v>316504.3817315627</v>
+        <v>312910.10162303981</v>
       </c>
       <c r="U15">
         <v>0</v>
@@ -2181,31 +2249,31 @@
         <v>0</v>
       </c>
       <c r="X15">
-        <v>23008325434.68265</v>
+        <v>22747038794.706711</v>
       </c>
       <c r="Y15">
-        <v>10688743986.85666</v>
+        <v>10567360707.147039</v>
       </c>
       <c r="Z15">
-        <v>42095082770.29784</v>
+        <v>41617043515.864288</v>
       </c>
       <c r="AA15">
-        <v>181904.248975056</v>
+        <v>163933.1051382474</v>
       </c>
       <c r="AB15">
-        <v>136717.9802992119</v>
+        <v>123541.06865873971</v>
       </c>
       <c r="AC15">
-        <v>217518.4800641961</v>
+        <v>195643.49281719161</v>
       </c>
       <c r="AD15">
-        <v>152138.674347562</v>
+        <v>136709.936030707</v>
       </c>
       <c r="AE15">
-        <v>70752.63895425784</v>
+        <v>63763.254931923373</v>
       </c>
       <c r="AF15">
-        <v>277997.899626098</v>
+        <v>249257.35824880269</v>
       </c>
       <c r="AG15">
         <v>0</v>
@@ -2217,13 +2285,13 @@
         <v>0</v>
       </c>
       <c r="AJ15">
-        <v>20234443688.22575</v>
+        <v>18182421492.08403</v>
       </c>
       <c r="AK15">
-        <v>9410100980.916292</v>
+        <v>8480512905.9458084</v>
       </c>
       <c r="AL15">
-        <v>36973720650.27103</v>
+        <v>33151228647.090771</v>
       </c>
     </row>
   </sheetData>

--- a/output/Tables/7000 steps/add_cases_prev_7000steps.xlsx
+++ b/output/Tables/7000 steps/add_cases_prev_7000steps.xlsx
@@ -1,173 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10119"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ines/Documents/PhD/PROJETS/MARCHE/HIA_walking_steps/output/Tables/7000 steps/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E697DCF5-5F8D-6F42-926B-45FAC5F02FCB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="500" windowWidth="21100" windowHeight="11960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="47">
-  <si>
-    <t>disease</t>
-  </si>
-  <si>
-    <t>sex</t>
-  </si>
-  <si>
-    <t>tot_cases_mid_2019</t>
-  </si>
-  <si>
-    <t>tot_cases_low_2019</t>
-  </si>
-  <si>
-    <t>tot_cases_up_2019</t>
-  </si>
-  <si>
-    <t>tot_daly_mid_2019</t>
-  </si>
-  <si>
-    <t>tot_daly_low_2019</t>
-  </si>
-  <si>
-    <t>tot_daly_up_2019</t>
-  </si>
-  <si>
-    <t>tot_medic_costs_mid_2019</t>
-  </si>
-  <si>
-    <t>tot_medic_costs_low_2019</t>
-  </si>
-  <si>
-    <t>tot_medic_costs_up_2019</t>
-  </si>
-  <si>
-    <t>tot_soc_costs_mid_2019</t>
-  </si>
-  <si>
-    <t>tot_soc_costs_low_2019</t>
-  </si>
-  <si>
-    <t>tot_soc_costs_up_2019</t>
-  </si>
-  <si>
-    <t>tot_cases_mid_RECO</t>
-  </si>
-  <si>
-    <t>tot_cases_low_RECO</t>
-  </si>
-  <si>
-    <t>tot_cases_up_RECO</t>
-  </si>
-  <si>
-    <t>tot_daly_mid_RECO</t>
-  </si>
-  <si>
-    <t>tot_daly_low_RECO</t>
-  </si>
-  <si>
-    <t>tot_daly_up_RECO</t>
-  </si>
-  <si>
-    <t>tot_medic_costs_mid_RECO</t>
-  </si>
-  <si>
-    <t>tot_medic_costs_low_RECO</t>
-  </si>
-  <si>
-    <t>tot_medic_costs_up_RECO</t>
-  </si>
-  <si>
-    <t>tot_soc_costs_mid_RECO</t>
-  </si>
-  <si>
-    <t>tot_soc_costs_low_RECO</t>
-  </si>
-  <si>
-    <t>tot_soc_costs_up_RECO</t>
-  </si>
-  <si>
-    <t>tot_cases_mid_RECO_diff</t>
-  </si>
-  <si>
-    <t>tot_cases_low_RECO_diff</t>
-  </si>
-  <si>
-    <t>tot_cases_up_RECO_diff</t>
-  </si>
-  <si>
-    <t>tot_daly_mid_RECO_diff</t>
-  </si>
-  <si>
-    <t>tot_daly_low_RECO_diff</t>
-  </si>
-  <si>
-    <t>tot_daly_up_RECO_diff</t>
-  </si>
-  <si>
-    <t>tot_medic_costs_mid_RECO_diff</t>
-  </si>
-  <si>
-    <t>tot_medic_costs_low_RECO_diff</t>
-  </si>
-  <si>
-    <t>tot_medic_costs_up_RECO_diff</t>
-  </si>
-  <si>
-    <t>tot_soc_costs_mid_RECO_diff</t>
-  </si>
-  <si>
-    <t>tot_soc_costs_low_RECO_diff</t>
-  </si>
-  <si>
-    <t>tot_soc_costs_up_RECO_diff</t>
-  </si>
-  <si>
-    <t>mort</t>
-  </si>
-  <si>
-    <t>Female</t>
-  </si>
-  <si>
-    <t>Male</t>
-  </si>
-  <si>
-    <t>bc</t>
-  </si>
-  <si>
-    <t>cvd</t>
-  </si>
-  <si>
-    <t>cancer</t>
-  </si>
-  <si>
-    <t>diab2</t>
-  </si>
-  <si>
-    <t>dem</t>
-  </si>
-  <si>
-    <t>dep</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -215,21 +63,13 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -267,7 +107,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -301,7 +141,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -336,10 +175,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -512,188 +350,230 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AL15"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="3" max="3" width="17.1640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="17" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="16" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16.33203125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="16" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.1640625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="22.83203125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="22.6640625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="21.83203125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="20.33203125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="20.1640625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="19.33203125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="17.1640625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="17" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="16" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="16.33203125" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="16" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="15.1640625" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="22.83203125" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="22.6640625" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="21.83203125" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="20.33203125" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="20.1640625" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="19.33203125" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="20.5" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="20.33203125" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="19.5" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="19.6640625" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="19.5" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="18.6640625" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="26.1640625" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="26" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="25.1640625" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="23.83203125" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="23.6640625" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="22.83203125" bestFit="1" customWidth="1"/>
-  </cols>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:AL13"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:38" s="1" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="R1" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="S1" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="T1" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="U1" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="V1" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="W1" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="X1" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="Y1" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="Z1" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="AA1" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AB1" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="AC1" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="AD1" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="AE1" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="AF1" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="AG1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="AH1" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="AI1" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="AJ1" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="AK1" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="AL1" s="1" t="s">
-        <v>37</v>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>sex</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>tot_cases_mid_2019</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>tot_cases_low_2019</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>tot_cases_up_2019</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>tot_daly_mid_2019</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>tot_daly_low_2019</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>tot_daly_up_2019</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>tot_medic_costs_mid_2019</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>tot_medic_costs_low_2019</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>tot_medic_costs_up_2019</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>tot_soc_costs_mid_2019</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>tot_soc_costs_low_2019</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>tot_soc_costs_up_2019</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>tot_cases_mid_RECO</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>tot_cases_low_RECO</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>tot_cases_up_RECO</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>tot_daly_mid_RECO</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>tot_daly_low_RECO</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>tot_daly_up_RECO</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>tot_medic_costs_mid_RECO</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>tot_medic_costs_low_RECO</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>tot_medic_costs_up_RECO</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>tot_soc_costs_mid_RECO</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>tot_soc_costs_low_RECO</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>tot_soc_costs_up_RECO</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>tot_cases_mid_RECO_diff</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>tot_cases_low_RECO_diff</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>tot_cases_up_RECO_diff</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>tot_daly_mid_RECO_diff</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>tot_daly_low_RECO_diff</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>tot_daly_up_RECO_diff</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>tot_medic_costs_mid_RECO_diff</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>tot_medic_costs_low_RECO_diff</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>tot_medic_costs_up_RECO_diff</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>tot_soc_costs_mid_RECO_diff</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>tot_soc_costs_low_RECO_diff</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>tot_soc_costs_up_RECO_diff</t>
+        </is>
       </c>
     </row>
-    <row r="2" spans="1:38" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
-        <v>38</v>
-      </c>
-      <c r="B2" t="s">
-        <v>39</v>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>mort</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
       </c>
       <c r="C2">
-        <v>20463.377275766281</v>
+        <v>24600.95049746287</v>
       </c>
       <c r="D2">
-        <v>17839.15714927057</v>
+        <v>21089.5996061323</v>
       </c>
       <c r="E2">
-        <v>22935.946428716881</v>
+        <v>27886.51173331669</v>
       </c>
       <c r="F2">
-        <v>42427.108481020623</v>
+        <v>287991.3626591965</v>
       </c>
       <c r="G2">
-        <v>36803.447414843911</v>
+        <v>247758.1126104651</v>
       </c>
       <c r="H2">
-        <v>47714.724979805469</v>
+        <v>325688.1692999321</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -705,31 +585,31 @@
         <v>0</v>
       </c>
       <c r="L2">
-        <v>5642805427.9757423</v>
+        <v>38302851233.67314</v>
       </c>
       <c r="M2">
-        <v>4894858506.1742401</v>
+        <v>32951828977.19185</v>
       </c>
       <c r="N2">
-        <v>6346058422.314127</v>
+        <v>43316526516.89098</v>
       </c>
       <c r="O2">
-        <v>60812.327020701341</v>
+        <v>60812.32702070134</v>
       </c>
       <c r="P2">
-        <v>52055.982049259008</v>
+        <v>52055.98204925901</v>
       </c>
       <c r="Q2">
-        <v>68821.865817244281</v>
+        <v>68821.86581724428</v>
       </c>
       <c r="R2">
-        <v>118382.8271450311</v>
+        <v>710296.9628701867</v>
       </c>
       <c r="S2">
-        <v>101336.9266843623</v>
+        <v>608021.5601061736</v>
       </c>
       <c r="T2">
-        <v>133974.92653204821</v>
+        <v>803849.5591922908</v>
       </c>
       <c r="U2">
         <v>0</v>
@@ -741,31 +621,31 @@
         <v>0</v>
       </c>
       <c r="X2">
-        <v>15744916010.289141</v>
+        <v>94469496061.73483</v>
       </c>
       <c r="Y2">
-        <v>13477811249.020189</v>
+        <v>80866867494.12109</v>
       </c>
       <c r="Z2">
-        <v>17818665228.762409</v>
+        <v>106911991372.5747</v>
       </c>
       <c r="AA2">
-        <v>40348.94974493506</v>
+        <v>36211.37652323848</v>
       </c>
       <c r="AB2">
-        <v>34216.824899988438</v>
+        <v>30966.38244312671</v>
       </c>
       <c r="AC2">
-        <v>45885.9193885274</v>
+        <v>40935.3540839276</v>
       </c>
       <c r="AD2">
-        <v>75955.718664010506</v>
+        <v>422305.6002109902</v>
       </c>
       <c r="AE2">
-        <v>64533.479269518437</v>
+        <v>360263.4474957085</v>
       </c>
       <c r="AF2">
-        <v>86260.20155224271</v>
+        <v>478161.3898923587</v>
       </c>
       <c r="AG2">
         <v>0</v>
@@ -777,39 +657,43 @@
         <v>0</v>
       </c>
       <c r="AJ2">
-        <v>10102110582.3134</v>
+        <v>56166644828.06169</v>
       </c>
       <c r="AK2">
-        <v>8582952742.845953</v>
+        <v>47915038516.92924</v>
       </c>
       <c r="AL2">
-        <v>11472606806.44828</v>
+        <v>63595464855.68369</v>
       </c>
     </row>
-    <row r="3" spans="1:38" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B3" t="s">
-        <v>40</v>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>mort</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
       </c>
       <c r="C3">
-        <v>30626.342983446579</v>
+        <v>34207.77804873243</v>
       </c>
       <c r="D3">
-        <v>26777.123652054321</v>
+        <v>29593.57874547202</v>
       </c>
       <c r="E3">
-        <v>34254.768141260713</v>
+        <v>38536.21438536532</v>
       </c>
       <c r="F3">
-        <v>49488.992334981398</v>
+        <v>320081.8490383019</v>
       </c>
       <c r="G3">
-        <v>43131.107858199539</v>
+        <v>276718.0067397309</v>
       </c>
       <c r="H3">
-        <v>55475.146222208139</v>
+        <v>360754.6054286612</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -821,16 +705,16 @@
         <v>0</v>
       </c>
       <c r="L3">
-        <v>6582035980.5525265</v>
+        <v>42570885922.09415</v>
       </c>
       <c r="M3">
-        <v>5736437345.1405382</v>
+        <v>36803494896.38421</v>
       </c>
       <c r="N3">
-        <v>7378194447.5536823</v>
+        <v>47980362522.01193</v>
       </c>
       <c r="O3">
-        <v>98411.136260928019</v>
+        <v>98411.13626092802</v>
       </c>
       <c r="P3">
         <v>84240.95234675247</v>
@@ -839,13 +723,13 @@
         <v>111372.7815803948</v>
       </c>
       <c r="R3">
-        <v>157474.83013748869</v>
+        <v>944848.9808249384</v>
       </c>
       <c r="S3">
-        <v>134800.0863058035</v>
+        <v>808800.5178348175</v>
       </c>
       <c r="T3">
-        <v>178215.70330019339</v>
+        <v>1069294.219801163</v>
       </c>
       <c r="U3">
         <v>0</v>
@@ -857,31 +741,31 @@
         <v>0</v>
       </c>
       <c r="X3">
-        <v>20944152408.285992</v>
+        <v>125664914449.7168</v>
       </c>
       <c r="Y3">
-        <v>17928411478.671871</v>
+        <v>107570468872.0307</v>
       </c>
       <c r="Z3">
-        <v>23702688538.92572</v>
+        <v>142216131233.5547</v>
       </c>
       <c r="AA3">
-        <v>67784.79327748144</v>
+        <v>64203.35821219559</v>
       </c>
       <c r="AB3">
-        <v>57463.828694698153</v>
+        <v>54647.37360128045</v>
       </c>
       <c r="AC3">
-        <v>77118.013439134142</v>
+        <v>72836.56719502952</v>
       </c>
       <c r="AD3">
-        <v>107985.8378025073</v>
+        <v>624767.1317866365</v>
       </c>
       <c r="AE3">
-        <v>91668.978447603964</v>
+        <v>532082.5110950866</v>
       </c>
       <c r="AF3">
-        <v>122740.5570779853</v>
+        <v>708539.6143725018</v>
       </c>
       <c r="AG3">
         <v>0</v>
@@ -893,1405 +777,1213 @@
         <v>0</v>
       </c>
       <c r="AJ3">
-        <v>14362116427.733471</v>
+        <v>83094028527.62267</v>
       </c>
       <c r="AK3">
-        <v>12191974133.53133</v>
+        <v>70766973975.64651</v>
       </c>
       <c r="AL3">
-        <v>16324494091.37204</v>
+        <v>94235768711.54276</v>
       </c>
     </row>
-    <row r="4" spans="1:38" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
-        <v>41</v>
-      </c>
-      <c r="B4" t="s">
-        <v>39</v>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>cvd</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
       </c>
       <c r="C4">
-        <v>1056.137328627854</v>
+        <v>18574.73159296868</v>
       </c>
       <c r="D4">
-        <v>60.930053786220753</v>
+        <v>11620.21651129571</v>
       </c>
       <c r="E4">
-        <v>2137.5702310948918</v>
+        <v>25438.54197189181</v>
       </c>
       <c r="F4">
-        <v>296.6374997337918</v>
+        <v>18227.96056128219</v>
       </c>
       <c r="G4">
-        <v>12.497319540802421</v>
+        <v>9008.98298610265</v>
       </c>
       <c r="H4">
-        <v>759.76168196758886</v>
+        <v>30294.58102630371</v>
       </c>
       <c r="I4">
-        <v>46561926.407216176</v>
+        <v>1034649699.191539</v>
       </c>
       <c r="J4">
-        <v>2686223.2812731131</v>
+        <v>647269300.1121955</v>
       </c>
       <c r="K4">
-        <v>94239058.778280437</v>
+        <v>1416977664.91832</v>
       </c>
       <c r="L4">
-        <v>39452787.464594312</v>
+        <v>2424318754.650531</v>
       </c>
       <c r="M4">
-        <v>1662143.498926722</v>
+        <v>1198194737.151653</v>
       </c>
       <c r="N4">
-        <v>101048303.7016893</v>
+        <v>4029179276.498394</v>
       </c>
       <c r="O4">
-        <v>5035.9010316036329</v>
+        <v>62026.80069934682</v>
       </c>
       <c r="P4">
-        <v>-105.13768319988129</v>
+        <v>40529.90188537803</v>
       </c>
       <c r="Q4">
-        <v>10045.63284707618</v>
+        <v>81329.52738073227</v>
       </c>
       <c r="R4">
-        <v>1395.2524551587869</v>
+        <v>60473.36819514075</v>
       </c>
       <c r="S4">
-        <v>-21.907454231934391</v>
+        <v>31013.80938055905</v>
       </c>
       <c r="T4">
-        <v>3521.2879132382768</v>
+        <v>96656.99331894201</v>
       </c>
       <c r="U4">
-        <v>222017768.78030801</v>
+        <v>3455016852.555022</v>
       </c>
       <c r="V4">
-        <v>-4635205.0392331639</v>
+        <v>2257596594.819324</v>
       </c>
       <c r="W4">
-        <v>442881815.32904661</v>
+        <v>4530217334.161569</v>
       </c>
       <c r="X4">
-        <v>185568576.53611869</v>
+        <v>8042957969.953719</v>
       </c>
       <c r="Y4">
-        <v>-2913691.412847274</v>
+        <v>4124836647.614353</v>
       </c>
       <c r="Z4">
-        <v>468331292.46069092</v>
+        <v>12855380111.41929</v>
       </c>
       <c r="AA4">
-        <v>3979.7637029757789</v>
+        <v>43452.06910637814</v>
       </c>
       <c r="AB4">
-        <v>-166.06773698610209</v>
+        <v>28909.68537408232</v>
       </c>
       <c r="AC4">
-        <v>7908.0626159812919</v>
+        <v>55890.98540884045</v>
       </c>
       <c r="AD4">
-        <v>1098.614955424996</v>
+        <v>42245.40763385856</v>
       </c>
       <c r="AE4">
-        <v>-34.40477377273681</v>
+        <v>22004.8263944564</v>
       </c>
       <c r="AF4">
-        <v>2761.5262312706882</v>
+        <v>66362.4122926383</v>
       </c>
       <c r="AG4">
-        <v>175455842.37309191</v>
+        <v>2420367153.363483</v>
       </c>
       <c r="AH4">
-        <v>-7321428.3205062766</v>
+        <v>1610327294.707129</v>
       </c>
       <c r="AI4">
-        <v>348642756.55076623</v>
+        <v>3113239669.243249</v>
       </c>
       <c r="AJ4">
-        <v>146115789.07152441</v>
+        <v>5618639215.303188</v>
       </c>
       <c r="AK4">
-        <v>-4575834.9117739964</v>
+        <v>2926641910.4627</v>
       </c>
       <c r="AL4">
-        <v>367282988.75900161</v>
+        <v>8826200834.920893</v>
       </c>
     </row>
-    <row r="5" spans="1:38" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B5" t="s">
-        <v>40</v>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>cvd</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
       </c>
       <c r="C5">
-        <v>0</v>
+        <v>21083.53521120251</v>
       </c>
       <c r="D5">
-        <v>0</v>
+        <v>13511.51035665206</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>28536.52674465354</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>16049.30625829875</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>8044.622459631398</v>
       </c>
       <c r="H5">
-        <v>0</v>
+        <v>26519.2752860746</v>
       </c>
       <c r="I5">
-        <v>0</v>
+        <v>1174395078.3344</v>
       </c>
       <c r="J5">
-        <v>0</v>
+        <v>752618149.88623</v>
       </c>
       <c r="K5">
-        <v>0</v>
+        <v>1589541612.730696</v>
       </c>
       <c r="L5">
-        <v>0</v>
+        <v>2134557732.353734</v>
       </c>
       <c r="M5">
-        <v>0</v>
+        <v>1069934787.130976</v>
       </c>
       <c r="N5">
-        <v>0</v>
+        <v>3527063613.047921</v>
       </c>
       <c r="O5">
-        <v>0</v>
+        <v>82750.82644288789</v>
       </c>
       <c r="P5">
-        <v>0</v>
+        <v>54071.51165060037</v>
       </c>
       <c r="Q5">
-        <v>0</v>
+        <v>108502.8653595535</v>
       </c>
       <c r="R5">
-        <v>0</v>
+        <v>64825.8318465973</v>
       </c>
       <c r="S5">
-        <v>0</v>
+        <v>33245.97342319173</v>
       </c>
       <c r="T5">
-        <v>0</v>
+        <v>103613.709351729</v>
       </c>
       <c r="U5">
-        <v>0</v>
+        <v>4609386534.52175</v>
       </c>
       <c r="V5">
-        <v>0</v>
+        <v>3011891341.961739</v>
       </c>
       <c r="W5">
-        <v>0</v>
+        <v>6043826606.257845</v>
       </c>
       <c r="X5">
-        <v>0</v>
+        <v>8621835635.597441</v>
       </c>
       <c r="Y5">
-        <v>0</v>
+        <v>4421714465.2845</v>
       </c>
       <c r="Z5">
-        <v>0</v>
+        <v>13780623343.77996</v>
       </c>
       <c r="AA5">
-        <v>0</v>
+        <v>61667.29123168538</v>
       </c>
       <c r="AB5">
-        <v>0</v>
+        <v>40560.00129394831</v>
       </c>
       <c r="AC5">
-        <v>0</v>
+        <v>79966.33861489996</v>
       </c>
       <c r="AD5">
-        <v>0</v>
+        <v>48776.52558829855</v>
       </c>
       <c r="AE5">
-        <v>0</v>
+        <v>25201.35096356033</v>
       </c>
       <c r="AF5">
-        <v>0</v>
+        <v>77094.43406565441</v>
       </c>
       <c r="AG5">
-        <v>0</v>
+        <v>3434991456.18735</v>
       </c>
       <c r="AH5">
-        <v>0</v>
+        <v>2259273192.075509</v>
       </c>
       <c r="AI5">
-        <v>0</v>
+        <v>4454284993.527149</v>
       </c>
       <c r="AJ5">
-        <v>0</v>
+        <v>6487277903.243707</v>
       </c>
       <c r="AK5">
-        <v>0</v>
+        <v>3351779678.153524</v>
       </c>
       <c r="AL5">
-        <v>0</v>
+        <v>10253559730.73204</v>
       </c>
     </row>
-    <row r="6" spans="1:38" x14ac:dyDescent="0.2">
-      <c r="A6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B6" t="s">
-        <v>39</v>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>cancer</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
       </c>
       <c r="C6">
-        <v>15383.965169078831</v>
+        <v>19639.00221098947</v>
       </c>
       <c r="D6">
-        <v>9729.1062145317173</v>
+        <v>945.2686101049807</v>
       </c>
       <c r="E6">
-        <v>21012.330214165431</v>
+        <v>39758.20605733652</v>
       </c>
       <c r="F6">
-        <v>2608.8504010910592</v>
+        <v>34999.51625488111</v>
       </c>
       <c r="G6">
-        <v>1295.5314070041859</v>
+        <v>1312.171796566891</v>
       </c>
       <c r="H6">
-        <v>4336.1906751912311</v>
+        <v>81802.08996450927</v>
       </c>
       <c r="I6">
-        <v>856917627.84802961</v>
+        <v>290794705.7381204</v>
       </c>
       <c r="J6">
-        <v>541930674.36184478</v>
+        <v>13996592.30982444</v>
       </c>
       <c r="K6">
-        <v>1170428817.5894411</v>
+        <v>588699757.0909815</v>
       </c>
       <c r="L6">
-        <v>346977103.34511077</v>
+        <v>4654935661.899187</v>
       </c>
       <c r="M6">
-        <v>172305677.13155669</v>
+        <v>174518848.9433964</v>
       </c>
       <c r="N6">
-        <v>576713359.80043375</v>
+        <v>10879677965.27973</v>
       </c>
       <c r="O6">
-        <v>62026.800699346823</v>
+        <v>78495.71499848703</v>
       </c>
       <c r="P6">
-        <v>40529.901885378029</v>
+        <v>-1638.804568292139</v>
       </c>
       <c r="Q6">
-        <v>81329.527380732266</v>
+        <v>156583.5245758266</v>
       </c>
       <c r="R6">
-        <v>10078.894699190099</v>
+        <v>139154.9473383052</v>
       </c>
       <c r="S6">
-        <v>5168.9682300931599</v>
+        <v>-2298.491854388779</v>
       </c>
       <c r="T6">
-        <v>16109.498886490321</v>
+        <v>320532.081265252</v>
       </c>
       <c r="U6">
-        <v>3455016852.5550218</v>
+        <v>1162286051.982595</v>
       </c>
       <c r="V6">
-        <v>2257596594.819324</v>
+        <v>-24265779.24270174</v>
       </c>
       <c r="W6">
-        <v>4530217334.1615686</v>
+        <v>2318532248.394261</v>
       </c>
       <c r="X6">
-        <v>1340492994.9922831</v>
+        <v>18507607995.9946</v>
       </c>
       <c r="Y6">
-        <v>687472774.60239029</v>
+        <v>-305699416.6337076</v>
       </c>
       <c r="Z6">
-        <v>2142563351.9032121</v>
+        <v>42630766808.27852</v>
       </c>
       <c r="AA6">
-        <v>46642.835530267992</v>
+        <v>58856.71278749756</v>
       </c>
       <c r="AB6">
-        <v>30800.79567084631</v>
+        <v>-2584.07317839712</v>
       </c>
       <c r="AC6">
-        <v>60317.197166566839</v>
+        <v>116825.3185184901</v>
       </c>
       <c r="AD6">
-        <v>7470.044298099042</v>
+        <v>104155.4310834241</v>
       </c>
       <c r="AE6">
-        <v>3873.4368230889741</v>
+        <v>-3610.66365095567</v>
       </c>
       <c r="AF6">
-        <v>11773.308211299091</v>
+        <v>238729.9913007428</v>
       </c>
       <c r="AG6">
-        <v>2598099224.7069931</v>
+        <v>871491346.2444751</v>
       </c>
       <c r="AH6">
-        <v>1715665920.45748</v>
+        <v>-38262371.55252618</v>
       </c>
       <c r="AI6">
-        <v>3359788516.5721269</v>
+        <v>1729832491.303279</v>
       </c>
       <c r="AJ6">
-        <v>993515891.64717257</v>
+        <v>13852672334.09541</v>
       </c>
       <c r="AK6">
-        <v>515167097.4708336</v>
+        <v>-480218265.577104</v>
       </c>
       <c r="AL6">
-        <v>1565849992.102778</v>
+        <v>31751088842.99879</v>
       </c>
     </row>
-    <row r="7" spans="1:38" x14ac:dyDescent="0.2">
-      <c r="A7" t="s">
-        <v>42</v>
-      </c>
-      <c r="B7" t="s">
-        <v>40</v>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>cancer</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
       </c>
       <c r="C7">
-        <v>18924.582063234309</v>
+        <v>10911.63767997198</v>
       </c>
       <c r="D7">
-        <v>12240.197289777831</v>
+        <v>460.823121919975</v>
       </c>
       <c r="E7">
-        <v>25508.559896471401</v>
+        <v>22052.50879113228</v>
       </c>
       <c r="F7">
-        <v>2449.2785101332411</v>
+        <v>10507.83350574811</v>
       </c>
       <c r="G7">
-        <v>1235.5295117824789</v>
+        <v>393.2500430385832</v>
       </c>
       <c r="H7">
-        <v>4037.7173363584729</v>
+        <v>24534.90924659295</v>
       </c>
       <c r="I7">
-        <v>1054137070.086274</v>
+        <v>161568619.1273454</v>
       </c>
       <c r="J7">
-        <v>681803469.43520474</v>
+        <v>6823407.966269104</v>
       </c>
       <c r="K7">
-        <v>1420877803.3532519</v>
+        <v>326531497.6702951</v>
       </c>
       <c r="L7">
-        <v>325754041.84772098</v>
+        <v>1397541856.264498</v>
       </c>
       <c r="M7">
-        <v>164325425.06706971</v>
+        <v>52302255.72413157</v>
       </c>
       <c r="N7">
-        <v>537016405.735677</v>
+        <v>3263142929.796862</v>
       </c>
       <c r="O7">
-        <v>82750.82644288789</v>
+        <v>49665.12484193227</v>
       </c>
       <c r="P7">
-        <v>54071.511650600369</v>
+        <v>-1036.890147154239</v>
       </c>
       <c r="Q7">
-        <v>108502.8653595535</v>
+        <v>99072.16331997342</v>
       </c>
       <c r="R7">
-        <v>10804.30530776621</v>
+        <v>49809.89059315866</v>
       </c>
       <c r="S7">
-        <v>5540.9955705319708</v>
+        <v>-822.7348720705954</v>
       </c>
       <c r="T7">
-        <v>17268.951558621589</v>
+        <v>114733.0239046752</v>
       </c>
       <c r="U7">
-        <v>4609386534.5217505</v>
+        <v>735391503.5344914</v>
       </c>
       <c r="V7">
-        <v>3011891341.9617391</v>
+        <v>-15353232.40891281</v>
       </c>
       <c r="W7">
-        <v>6043826606.2578449</v>
+        <v>1466961522.278845</v>
       </c>
       <c r="X7">
-        <v>1436972605.9329059</v>
+        <v>6624715448.890102</v>
       </c>
       <c r="Y7">
-        <v>736952410.88075209</v>
+        <v>-109423737.9853892</v>
       </c>
       <c r="Z7">
-        <v>2296770557.2966719</v>
+        <v>15259492179.32179</v>
       </c>
       <c r="AA7">
-        <v>63826.244379653581</v>
+        <v>38753.48716196029</v>
       </c>
       <c r="AB7">
-        <v>41831.314360822536</v>
+        <v>-1497.713269074214</v>
       </c>
       <c r="AC7">
-        <v>82994.305463082099</v>
+        <v>77019.65452884114</v>
       </c>
       <c r="AD7">
-        <v>8355.0267976329724</v>
+        <v>39302.05708741055</v>
       </c>
       <c r="AE7">
-        <v>4305.4660587494918</v>
+        <v>-1215.984915109179</v>
       </c>
       <c r="AF7">
-        <v>13231.23422226312</v>
+        <v>90198.1146580822</v>
       </c>
       <c r="AG7">
-        <v>3555249464.4354758</v>
+        <v>573822884.407146</v>
       </c>
       <c r="AH7">
-        <v>2330087872.5265341</v>
+        <v>-22176640.37518191</v>
       </c>
       <c r="AI7">
-        <v>4622948802.9045935</v>
+        <v>1140430024.60855</v>
       </c>
       <c r="AJ7">
-        <v>1111218564.085186</v>
+        <v>5227173592.625605</v>
       </c>
       <c r="AK7">
-        <v>572626985.81368232</v>
+        <v>-161725993.7095208</v>
       </c>
       <c r="AL7">
-        <v>1759754151.5609951</v>
+        <v>11996349249.52493</v>
       </c>
     </row>
-    <row r="8" spans="1:38" x14ac:dyDescent="0.2">
-      <c r="A8" t="s">
-        <v>43</v>
-      </c>
-      <c r="B8" t="s">
-        <v>39</v>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>diab2</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
       </c>
       <c r="C8">
-        <v>16858.195079461009</v>
+        <v>3079.152031990513</v>
       </c>
       <c r="D8">
-        <v>968.50307140482755</v>
+        <v>-81.5652831526404</v>
       </c>
       <c r="E8">
-        <v>34126.387302877003</v>
+        <v>5771.468572331606</v>
       </c>
       <c r="F8">
-        <v>5081.8859919416727</v>
+        <v>6408.052173675374</v>
       </c>
       <c r="G8">
-        <v>230.71396026469961</v>
+        <v>-127.5342819378562</v>
       </c>
       <c r="H8">
-        <v>11880.594263710949</v>
+        <v>15253.19523882721</v>
       </c>
       <c r="I8">
-        <v>249619294.54157951</v>
+        <v>231555311.9577184</v>
       </c>
       <c r="J8">
-        <v>14340624.97829131</v>
+        <v>-6133790.858361734</v>
       </c>
       <c r="K8">
-        <v>505309416.79369998</v>
+        <v>434020208.1079093</v>
       </c>
       <c r="L8">
-        <v>675890836.92824244</v>
+        <v>852270939.0988246</v>
       </c>
       <c r="M8">
-        <v>30684956.715205051</v>
+        <v>-16962059.49773488</v>
       </c>
       <c r="N8">
-        <v>1580119037.0735569</v>
+        <v>2028674966.764018</v>
       </c>
       <c r="O8">
-        <v>78495.714998487034</v>
+        <v>12056.6702807696</v>
       </c>
       <c r="P8">
-        <v>-1638.804568292139</v>
+        <v>0</v>
       </c>
       <c r="Q8">
-        <v>156583.5245758266</v>
+        <v>21984.68083159204</v>
       </c>
       <c r="R8">
-        <v>23192.491223051009</v>
+        <v>25226.50104720105</v>
       </c>
       <c r="S8">
-        <v>-383.08197573146339</v>
+        <v>0</v>
       </c>
       <c r="T8">
-        <v>53422.013544208778</v>
+        <v>58401.25858151415</v>
       </c>
       <c r="U8">
-        <v>1162286051.982595</v>
+        <v>906673661.7841525</v>
       </c>
       <c r="V8">
-        <v>-24265779.242701739</v>
+        <v>0</v>
       </c>
       <c r="W8">
-        <v>2318532248.3942609</v>
+        <v>1653269983.216557</v>
       </c>
       <c r="X8">
-        <v>3084601332.6657839</v>
+        <v>3355124639.277739</v>
       </c>
       <c r="Y8">
-        <v>-50949902.772284627</v>
+        <v>0</v>
       </c>
       <c r="Z8">
-        <v>7105127801.3797674</v>
+        <v>7767367391.341382</v>
       </c>
       <c r="AA8">
-        <v>61637.519919026017</v>
+        <v>8977.518248779092</v>
       </c>
       <c r="AB8">
-        <v>-2607.3076396969659</v>
+        <v>81.5652831526404</v>
       </c>
       <c r="AC8">
-        <v>122457.13727294961</v>
+        <v>16213.21225926043</v>
       </c>
       <c r="AD8">
-        <v>18110.605231109341</v>
+        <v>18818.44887352567</v>
       </c>
       <c r="AE8">
-        <v>-613.79593599616305</v>
+        <v>127.5342819378562</v>
       </c>
       <c r="AF8">
-        <v>41541.41928049783</v>
+        <v>43148.06334268694</v>
       </c>
       <c r="AG8">
-        <v>912666757.44101596</v>
+        <v>675118349.8264341</v>
       </c>
       <c r="AH8">
-        <v>-38606404.220993049</v>
+        <v>6133790.858361734</v>
       </c>
       <c r="AI8">
-        <v>1813222831.6005609</v>
+        <v>1219249775.108648</v>
       </c>
       <c r="AJ8">
-        <v>2408710495.7375422</v>
+        <v>2502853700.178915</v>
       </c>
       <c r="AK8">
-        <v>-81634859.487489671</v>
+        <v>16962059.49773488</v>
       </c>
       <c r="AL8">
-        <v>5525008764.3062115</v>
+        <v>5738692424.577364</v>
       </c>
     </row>
-    <row r="9" spans="1:38" x14ac:dyDescent="0.2">
-      <c r="A9" t="s">
-        <v>43</v>
-      </c>
-      <c r="B9" t="s">
-        <v>40</v>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>diab2</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
       </c>
       <c r="C9">
-        <v>9883.2734920185285</v>
+        <v>3415.492903387784</v>
       </c>
       <c r="D9">
-        <v>430.6174092848853</v>
+        <v>-87.66933312498075</v>
       </c>
       <c r="E9">
-        <v>19969.781021917632</v>
+        <v>6389.26496163765</v>
       </c>
       <c r="F9">
-        <v>1605.8275695762629</v>
+        <v>6139.17200634873</v>
       </c>
       <c r="G9">
-        <v>63.630473402829679</v>
+        <v>-127.3253159773389</v>
       </c>
       <c r="H9">
-        <v>3749.0283877820989</v>
+        <v>14631.56693980678</v>
       </c>
       <c r="I9">
-        <v>146341630.59631851</v>
+        <v>256848481.8276645</v>
       </c>
       <c r="J9">
-        <v>6376151.9792812876</v>
+        <v>-6592821.520331657</v>
       </c>
       <c r="K9">
-        <v>295692547.59153438</v>
+        <v>480479114.3801115</v>
       </c>
       <c r="L9">
-        <v>213575066.75364301</v>
+        <v>816509876.8443811</v>
       </c>
       <c r="M9">
-        <v>8462852.9625763465</v>
+        <v>-16934267.02498607</v>
       </c>
       <c r="N9">
-        <v>498620775.57501918</v>
+        <v>1945998402.994302</v>
       </c>
       <c r="O9">
-        <v>49665.124841932273</v>
+        <v>16096.82026023769</v>
       </c>
       <c r="P9">
-        <v>-1036.890147154239</v>
+        <v>0</v>
       </c>
       <c r="Q9">
-        <v>99072.163319973421</v>
+        <v>29351.67401809747</v>
       </c>
       <c r="R9">
-        <v>8301.6484321931348</v>
+        <v>29628.57642476932</v>
       </c>
       <c r="S9">
-        <v>-137.12247867843229</v>
+        <v>0</v>
       </c>
       <c r="T9">
-        <v>19122.17065077916</v>
+        <v>68592.39614512841</v>
       </c>
       <c r="U9">
-        <v>735391503.53449142</v>
+        <v>1210496980.390138</v>
       </c>
       <c r="V9">
-        <v>-15353232.40891281</v>
+        <v>0</v>
       </c>
       <c r="W9">
-        <v>1466961522.2788451</v>
+        <v>2207275237.834931</v>
       </c>
       <c r="X9">
-        <v>1104119241.4816871</v>
+        <v>3940600664.494319</v>
       </c>
       <c r="Y9">
-        <v>-18237289.664231502</v>
+        <v>0</v>
       </c>
       <c r="Z9">
-        <v>2543248696.553628</v>
+        <v>9122788687.302078</v>
       </c>
       <c r="AA9">
-        <v>39781.851349913733</v>
+        <v>12681.3273568499</v>
       </c>
       <c r="AB9">
-        <v>-1467.507556439125</v>
+        <v>87.66933312498075</v>
       </c>
       <c r="AC9">
-        <v>79102.382298055789</v>
+        <v>22962.40905645982</v>
       </c>
       <c r="AD9">
-        <v>6695.8208626168716</v>
+        <v>23489.40441842059</v>
       </c>
       <c r="AE9">
-        <v>-200.75295208126201</v>
+        <v>127.3253159773389</v>
       </c>
       <c r="AF9">
-        <v>15373.14226299706</v>
+        <v>53960.82920532163</v>
       </c>
       <c r="AG9">
-        <v>589049872.93817294</v>
+        <v>953648498.5624734</v>
       </c>
       <c r="AH9">
-        <v>-21729384.388194099</v>
+        <v>6592821.520331657</v>
       </c>
       <c r="AI9">
-        <v>1171268974.6873109</v>
+        <v>1726796123.45482</v>
       </c>
       <c r="AJ9">
-        <v>890544174.72804379</v>
+        <v>3124090787.649939</v>
       </c>
       <c r="AK9">
-        <v>-26700142.62680785</v>
+        <v>16934267.02498607</v>
       </c>
       <c r="AL9">
-        <v>2044627920.9786091</v>
+        <v>7176790284.307776</v>
       </c>
     </row>
-    <row r="10" spans="1:38" x14ac:dyDescent="0.2">
-      <c r="A10" t="s">
-        <v>44</v>
-      </c>
-      <c r="B10" t="s">
-        <v>39</v>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>dem</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
       </c>
       <c r="C10">
-        <v>2642.136597655282</v>
+        <v>8289.94422304287</v>
       </c>
       <c r="D10">
-        <v>-77.872790168370557</v>
+        <v>6022.233564455917</v>
       </c>
       <c r="E10">
-        <v>4972.0184620661921</v>
+        <v>10331.62833484003</v>
       </c>
       <c r="F10">
-        <v>925.63781419722295</v>
+        <v>15290.61964606795</v>
       </c>
       <c r="G10">
-        <v>-20.626622289248289</v>
+        <v>8925.728926396978</v>
       </c>
       <c r="H10">
-        <v>2212.8898330864149</v>
+        <v>21658.62276182612</v>
       </c>
       <c r="I10">
-        <v>198691314.28027591</v>
+        <v>139594370.7718183</v>
       </c>
       <c r="J10">
-        <v>-5856111.6934516374</v>
+        <v>101408390.9918734</v>
       </c>
       <c r="K10">
-        <v>373900760.36583889</v>
+        <v>173974289.5303712</v>
       </c>
       <c r="L10">
-        <v>123109829.2882307</v>
+        <v>2033652412.927037</v>
       </c>
       <c r="M10">
-        <v>-2743340.7644700231</v>
+        <v>1187121947.210798</v>
       </c>
       <c r="N10">
-        <v>294314347.80049318</v>
+        <v>2880596827.322874</v>
       </c>
       <c r="O10">
-        <v>12056.6702807696</v>
+        <v>28474.64780985158</v>
       </c>
       <c r="P10">
-        <v>0</v>
+        <v>21075.50843496856</v>
       </c>
       <c r="Q10">
-        <v>21984.680831592039</v>
+        <v>34599.02779288883</v>
       </c>
       <c r="R10">
-        <v>4204.4168412001727</v>
+        <v>50850.24704737742</v>
       </c>
       <c r="S10">
-        <v>0</v>
+        <v>30181.18019335427</v>
       </c>
       <c r="T10">
-        <v>9733.5430969190547</v>
+        <v>70369.03924043707</v>
       </c>
       <c r="U10">
-        <v>906673661.78415251</v>
+        <v>479484594.4700922</v>
       </c>
       <c r="V10">
-        <v>0</v>
+        <v>354890486.5364367</v>
       </c>
       <c r="W10">
-        <v>1653269983.216557</v>
+        <v>582613029.0044533</v>
       </c>
       <c r="X10">
-        <v>559187439.87962294</v>
+        <v>6763082857.301196</v>
       </c>
       <c r="Y10">
-        <v>0</v>
+        <v>4014096965.716117</v>
       </c>
       <c r="Z10">
-        <v>1294561231.890234</v>
+        <v>9359082218.97813</v>
       </c>
       <c r="AA10">
-        <v>9414.5336831143213</v>
+        <v>20184.7035868087</v>
       </c>
       <c r="AB10">
-        <v>77.872790168370557</v>
+        <v>15053.27487051265</v>
       </c>
       <c r="AC10">
-        <v>17012.662369525849</v>
+        <v>24267.3994580488</v>
       </c>
       <c r="AD10">
-        <v>3278.77902700295</v>
+        <v>35559.62740130947</v>
       </c>
       <c r="AE10">
-        <v>20.626622289248289</v>
+        <v>21255.45126695729</v>
       </c>
       <c r="AF10">
-        <v>7520.6532638326398</v>
+        <v>48710.41647861095</v>
       </c>
       <c r="AG10">
-        <v>707982347.50387657</v>
+        <v>339890223.6982739</v>
       </c>
       <c r="AH10">
-        <v>5856111.6934516374</v>
+        <v>253482095.5445634</v>
       </c>
       <c r="AI10">
-        <v>1279369222.850718</v>
+        <v>408638739.4740821</v>
       </c>
       <c r="AJ10">
-        <v>436077610.59139222</v>
+        <v>4729430444.374159</v>
       </c>
       <c r="AK10">
-        <v>2743340.7644700231</v>
+        <v>2826975018.50532</v>
       </c>
       <c r="AL10">
-        <v>1000246884.089741</v>
+        <v>6478485391.655256</v>
       </c>
     </row>
-    <row r="11" spans="1:38" x14ac:dyDescent="0.2">
-      <c r="A11" t="s">
-        <v>44</v>
-      </c>
-      <c r="B11" t="s">
-        <v>40</v>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>dem</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
       </c>
       <c r="C11">
-        <v>3126.1926537410732</v>
+        <v>5199.494302381868</v>
       </c>
       <c r="D11">
-        <v>-82.81853487150974</v>
+        <v>3806.472494643124</v>
       </c>
       <c r="E11">
-        <v>5853.1299361032743</v>
+        <v>6449.432056470911</v>
       </c>
       <c r="F11">
-        <v>942.3777145710344</v>
+        <v>5399.633159346871</v>
       </c>
       <c r="G11">
-        <v>-20.12635281937332</v>
+        <v>3171.963608625719</v>
       </c>
       <c r="H11">
-        <v>2247.6472436891258</v>
+        <v>7618.96876310422</v>
       </c>
       <c r="I11">
-        <v>235092813.75398299</v>
+        <v>87554284.55780822</v>
       </c>
       <c r="J11">
-        <v>-6228036.6408723993</v>
+        <v>64097190.33729566</v>
       </c>
       <c r="K11">
-        <v>440161224.32490212</v>
+        <v>108601986.3989135</v>
       </c>
       <c r="L11">
-        <v>125336236.0379476</v>
+        <v>718151210.1931338</v>
       </c>
       <c r="M11">
-        <v>-2676804.924976652</v>
+        <v>421871159.9472206</v>
       </c>
       <c r="N11">
-        <v>298937083.41065371</v>
+        <v>1013322845.492861</v>
       </c>
       <c r="O11">
-        <v>16096.82026023769</v>
+        <v>20961.21919971283</v>
       </c>
       <c r="P11">
-        <v>0</v>
+        <v>15514.44481423692</v>
       </c>
       <c r="Q11">
-        <v>29351.67401809747</v>
+        <v>25469.59704319076</v>
       </c>
       <c r="R11">
-        <v>4938.0960707948789</v>
+        <v>21844.37691375475</v>
       </c>
       <c r="S11">
-        <v>0</v>
+        <v>12965.30723304689</v>
       </c>
       <c r="T11">
-        <v>11432.066024188051</v>
+        <v>30229.30871495516</v>
       </c>
       <c r="U11">
-        <v>1210496980.3901379</v>
+        <v>352965970.1039641</v>
       </c>
       <c r="V11">
-        <v>0</v>
+        <v>261247736.226935</v>
       </c>
       <c r="W11">
-        <v>2207275237.8349309</v>
+        <v>428882544.6102901</v>
       </c>
       <c r="X11">
-        <v>656766777.41571891</v>
+        <v>2905302129.529381</v>
       </c>
       <c r="Y11">
-        <v>0</v>
+        <v>1724385861.995237</v>
       </c>
       <c r="Z11">
-        <v>1520464781.217011</v>
+        <v>4020498059.089036</v>
       </c>
       <c r="AA11">
-        <v>12970.627606496621</v>
+        <v>15761.72489733097</v>
       </c>
       <c r="AB11">
-        <v>82.81853487150974</v>
+        <v>11707.97231959379</v>
       </c>
       <c r="AC11">
-        <v>23498.54408199419</v>
+        <v>19020.16498671985</v>
       </c>
       <c r="AD11">
-        <v>3995.7183562238438</v>
+        <v>16444.74375440787</v>
       </c>
       <c r="AE11">
-        <v>20.12635281937332</v>
+        <v>9793.343624421172</v>
       </c>
       <c r="AF11">
-        <v>9184.4187804989251</v>
+        <v>22610.33995185094</v>
       </c>
       <c r="AG11">
-        <v>975404166.63615489</v>
+        <v>265411685.5461559</v>
       </c>
       <c r="AH11">
-        <v>6228036.6408723993</v>
+        <v>197150545.8896394</v>
       </c>
       <c r="AI11">
-        <v>1767114013.5100291</v>
+        <v>320280558.2113765</v>
       </c>
       <c r="AJ11">
-        <v>531430541.37777132</v>
+        <v>2187150919.336247</v>
       </c>
       <c r="AK11">
-        <v>2676804.924976652</v>
+        <v>1302514702.048016</v>
       </c>
       <c r="AL11">
-        <v>1221527697.8063569</v>
+        <v>3007175213.596175</v>
       </c>
     </row>
-    <row r="12" spans="1:38" x14ac:dyDescent="0.2">
-      <c r="A12" t="s">
-        <v>45</v>
-      </c>
-      <c r="B12" t="s">
-        <v>39</v>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>dep</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
       </c>
       <c r="C12">
-        <v>6641.564563772612</v>
+        <v>107153.1553122108</v>
       </c>
       <c r="D12">
-        <v>4882.4975768912418</v>
+        <v>79218.0166650977</v>
       </c>
       <c r="E12">
-        <v>8227.84256480152</v>
+        <v>129974.2989825751</v>
       </c>
       <c r="F12">
-        <v>2132.8191250745049</v>
+        <v>319829.3050394356</v>
       </c>
       <c r="G12">
-        <v>1254.2807715331189</v>
+        <v>146325.7040484844</v>
       </c>
       <c r="H12">
-        <v>3011.0431334448949</v>
+        <v>592720.3022994641</v>
       </c>
       <c r="I12">
-        <v>111837305.6893671</v>
+        <v>0</v>
       </c>
       <c r="J12">
-        <v>82216376.69727169</v>
+        <v>0</v>
       </c>
       <c r="K12">
-        <v>138548640.9486931</v>
+        <v>0</v>
       </c>
       <c r="L12">
-        <v>283664943.63490921</v>
+        <v>42537297570.24494</v>
       </c>
       <c r="M12">
-        <v>166819342.61390489</v>
+        <v>19461318638.44842</v>
       </c>
       <c r="N12">
-        <v>400468736.74817097</v>
+        <v>78831800205.82874</v>
       </c>
       <c r="O12">
-        <v>28474.64780985158</v>
+        <v>412256.2595949728</v>
       </c>
       <c r="P12">
-        <v>21075.50843496856</v>
+        <v>309599.5736041024</v>
       </c>
       <c r="Q12">
-        <v>34599.027792888832</v>
+        <v>493594.8705806515</v>
       </c>
       <c r="R12">
-        <v>8475.0411745628644</v>
+        <v>1215817.310622175</v>
       </c>
       <c r="S12">
-        <v>5030.1966988924141</v>
+        <v>564819.8955165836</v>
       </c>
       <c r="T12">
-        <v>11728.17320673951</v>
+        <v>2224409.18047226</v>
       </c>
       <c r="U12">
-        <v>479484594.47009218</v>
+        <v>0</v>
       </c>
       <c r="V12">
-        <v>354890486.53643668</v>
+        <v>0</v>
       </c>
       <c r="W12">
-        <v>582613029.0044533</v>
+        <v>0</v>
       </c>
       <c r="X12">
-        <v>1127180476.216861</v>
+        <v>161703702312.7493</v>
       </c>
       <c r="Y12">
-        <v>669016160.95269108</v>
+        <v>75121046103.70561</v>
       </c>
       <c r="Z12">
-        <v>1559847036.4963551</v>
+        <v>295846421002.8105</v>
       </c>
       <c r="AA12">
-        <v>21833.083246078961</v>
+        <v>305103.104282762</v>
       </c>
       <c r="AB12">
-        <v>16193.010858077319</v>
+        <v>230381.5569390047</v>
       </c>
       <c r="AC12">
-        <v>26371.18522808731</v>
+        <v>363620.5715980764</v>
       </c>
       <c r="AD12">
-        <v>6342.2220494883604</v>
+        <v>895988.0055827398</v>
       </c>
       <c r="AE12">
-        <v>3775.915927359295</v>
+        <v>418494.1914680992</v>
       </c>
       <c r="AF12">
-        <v>8717.1300732946165</v>
+        <v>1631688.878172796</v>
       </c>
       <c r="AG12">
-        <v>367647288.78072512</v>
+        <v>0</v>
       </c>
       <c r="AH12">
-        <v>272674109.83916497</v>
+        <v>0</v>
       </c>
       <c r="AI12">
-        <v>444064388.0557602</v>
+        <v>0</v>
       </c>
       <c r="AJ12">
-        <v>843515532.58195186</v>
+        <v>119166404742.5044</v>
       </c>
       <c r="AK12">
-        <v>502196818.33878618</v>
+        <v>55659727465.25719</v>
       </c>
       <c r="AL12">
-        <v>1159378299.748184</v>
+        <v>217014620796.9818</v>
       </c>
     </row>
-    <row r="13" spans="1:38" x14ac:dyDescent="0.2">
-      <c r="A13" t="s">
-        <v>45</v>
-      </c>
-      <c r="B13" t="s">
-        <v>40</v>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>dep</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
       </c>
       <c r="C13">
-        <v>4576.5541362172344</v>
+        <v>44955.61251605048</v>
       </c>
       <c r="D13">
-        <v>3376.3433597340559</v>
+        <v>33286.7661588011</v>
       </c>
       <c r="E13">
-        <v>5652.3146401831355</v>
+        <v>54504.37393346629</v>
       </c>
       <c r="F13">
-        <v>814.89415475720318</v>
+        <v>111660.4564958147</v>
       </c>
       <c r="G13">
-        <v>481.64524671107301</v>
+        <v>51036.47626420549</v>
       </c>
       <c r="H13">
-        <v>1146.226008474122</v>
+        <v>207035.5004800728</v>
       </c>
       <c r="I13">
-        <v>77064595.099762052</v>
+        <v>0</v>
       </c>
       <c r="J13">
-        <v>56854245.834561832</v>
+        <v>0</v>
       </c>
       <c r="K13">
-        <v>95179326.226043671</v>
+        <v>0</v>
       </c>
       <c r="L13">
-        <v>108380922.582708</v>
+        <v>14850840713.94335</v>
       </c>
       <c r="M13">
-        <v>64058817.812572703</v>
+        <v>6787851343.139331</v>
       </c>
       <c r="N13">
-        <v>152448059.12705821</v>
+        <v>27535721563.84969</v>
       </c>
       <c r="O13">
-        <v>20961.219199712828</v>
+        <v>205076.2777874958</v>
       </c>
       <c r="P13">
-        <v>15514.44481423692</v>
+        <v>154009.8583868761</v>
       </c>
       <c r="Q13">
-        <v>25469.597043190759</v>
+        <v>245538.0517281426</v>
       </c>
       <c r="R13">
-        <v>3640.729485625794</v>
+        <v>513091.1006324803</v>
       </c>
       <c r="S13">
-        <v>2160.8845388411492</v>
+        <v>238361.5197100842</v>
       </c>
       <c r="T13">
-        <v>5038.2181191592026</v>
+        <v>938730.3048691241</v>
       </c>
       <c r="U13">
-        <v>352965970.10396409</v>
+        <v>0</v>
       </c>
       <c r="V13">
-        <v>261247736.226935</v>
+        <v>0</v>
       </c>
       <c r="W13">
-        <v>428882544.61029011</v>
+        <v>0</v>
       </c>
       <c r="X13">
-        <v>484217021.58823061</v>
+        <v>68241116384.11989</v>
       </c>
       <c r="Y13">
-        <v>287397643.66587281</v>
+        <v>31702082121.4412</v>
       </c>
       <c r="Z13">
-        <v>670083009.84817398</v>
+        <v>124851130547.5935</v>
       </c>
       <c r="AA13">
-        <v>16384.665063495599</v>
+        <v>160120.6652714454</v>
       </c>
       <c r="AB13">
-        <v>12138.101454502859</v>
+        <v>120723.0922280751</v>
       </c>
       <c r="AC13">
-        <v>19817.28240300763</v>
+        <v>191033.6777946763</v>
       </c>
       <c r="AD13">
-        <v>2825.835330868591</v>
+        <v>401430.6441366656</v>
       </c>
       <c r="AE13">
-        <v>1679.2392921300759</v>
+        <v>187325.0434458787</v>
       </c>
       <c r="AF13">
-        <v>3891.9921106850811</v>
+        <v>731694.8043890513</v>
       </c>
       <c r="AG13">
-        <v>275901375.00420201</v>
+        <v>0</v>
       </c>
       <c r="AH13">
-        <v>204393490.3923732</v>
+        <v>0</v>
       </c>
       <c r="AI13">
-        <v>333703218.38424629</v>
+        <v>0</v>
       </c>
       <c r="AJ13">
-        <v>375836099.00552261</v>
+        <v>53390275670.17654</v>
       </c>
       <c r="AK13">
-        <v>223338825.85330001</v>
+        <v>24914230778.30187</v>
       </c>
       <c r="AL13">
-        <v>517634950.72111583</v>
-      </c>
-    </row>
-    <row r="14" spans="1:38" x14ac:dyDescent="0.2">
-      <c r="A14" t="s">
-        <v>46</v>
-      </c>
-      <c r="B14" t="s">
-        <v>39</v>
-      </c>
-      <c r="C14">
-        <v>92391.101291395025</v>
-      </c>
-      <c r="D14">
-        <v>68149.382492447796</v>
-      </c>
-      <c r="E14">
-        <v>112201.2114600035</v>
-      </c>
-      <c r="F14">
-        <v>93347.60397074536</v>
-      </c>
-      <c r="G14">
-        <v>42585.423339675792</v>
-      </c>
-      <c r="H14">
-        <v>173232.13512167311</v>
-      </c>
-      <c r="I14">
-        <v>0</v>
-      </c>
-      <c r="J14">
-        <v>0</v>
-      </c>
-      <c r="K14">
-        <v>0</v>
-      </c>
-      <c r="L14">
-        <v>12415231328.109131</v>
-      </c>
-      <c r="M14">
-        <v>5663861304.1768799</v>
-      </c>
-      <c r="N14">
-        <v>23039873971.182522</v>
-      </c>
-      <c r="O14">
-        <v>412256.25959497283</v>
-      </c>
-      <c r="P14">
-        <v>309599.57360410242</v>
-      </c>
-      <c r="Q14">
-        <v>493594.87058065151</v>
-      </c>
-      <c r="R14">
-        <v>405272.43687405728</v>
-      </c>
-      <c r="S14">
-        <v>188273.29850552769</v>
-      </c>
-      <c r="T14">
-        <v>741469.72682408465</v>
-      </c>
-      <c r="U14">
-        <v>0</v>
-      </c>
-      <c r="V14">
-        <v>0</v>
-      </c>
-      <c r="W14">
-        <v>0</v>
-      </c>
-      <c r="X14">
-        <v>53901234104.249619</v>
-      </c>
-      <c r="Y14">
-        <v>25040348701.235191</v>
-      </c>
-      <c r="Z14">
-        <v>98615473667.603256</v>
-      </c>
-      <c r="AA14">
-        <v>319865.1583035778</v>
-      </c>
-      <c r="AB14">
-        <v>241450.1911116546</v>
-      </c>
-      <c r="AC14">
-        <v>381393.65912064799</v>
-      </c>
-      <c r="AD14">
-        <v>311924.83290331188</v>
-      </c>
-      <c r="AE14">
-        <v>145687.8751658519</v>
-      </c>
-      <c r="AF14">
-        <v>568237.59170241153</v>
-      </c>
-      <c r="AG14">
-        <v>0</v>
-      </c>
-      <c r="AH14">
-        <v>0</v>
-      </c>
-      <c r="AI14">
-        <v>0</v>
-      </c>
-      <c r="AJ14">
-        <v>41486002776.140488</v>
-      </c>
-      <c r="AK14">
-        <v>19376487397.058311</v>
-      </c>
-      <c r="AL14">
-        <v>75575599696.420731</v>
-      </c>
-    </row>
-    <row r="15" spans="1:38" x14ac:dyDescent="0.2">
-      <c r="A15" t="s">
-        <v>46</v>
-      </c>
-      <c r="B15" t="s">
-        <v>40</v>
-      </c>
-      <c r="C15">
-        <v>41143.172649248423</v>
-      </c>
-      <c r="D15">
-        <v>30468.78972813642</v>
-      </c>
-      <c r="E15">
-        <v>49894.558910951033</v>
-      </c>
-      <c r="F15">
-        <v>34320.430846787109</v>
-      </c>
-      <c r="G15">
-        <v>15690.58497143784</v>
-      </c>
-      <c r="H15">
-        <v>63652.743374237019</v>
-      </c>
-      <c r="I15">
-        <v>0</v>
-      </c>
-      <c r="J15">
-        <v>0</v>
-      </c>
-      <c r="K15">
-        <v>0</v>
-      </c>
-      <c r="L15">
-        <v>4564617302.6226854</v>
-      </c>
-      <c r="M15">
-        <v>2086847801.2012329</v>
-      </c>
-      <c r="N15">
-        <v>8465814868.7735233</v>
-      </c>
-      <c r="O15">
-        <v>205076.27778749581</v>
-      </c>
-      <c r="P15">
-        <v>154009.85838687609</v>
-      </c>
-      <c r="Q15">
-        <v>245538.0517281426</v>
-      </c>
-      <c r="R15">
-        <v>171030.36687749409</v>
-      </c>
-      <c r="S15">
-        <v>79453.839903361208</v>
-      </c>
-      <c r="T15">
-        <v>312910.10162303981</v>
-      </c>
-      <c r="U15">
-        <v>0</v>
-      </c>
-      <c r="V15">
-        <v>0</v>
-      </c>
-      <c r="W15">
-        <v>0</v>
-      </c>
-      <c r="X15">
-        <v>22747038794.706711</v>
-      </c>
-      <c r="Y15">
-        <v>10567360707.147039</v>
-      </c>
-      <c r="Z15">
-        <v>41617043515.864288</v>
-      </c>
-      <c r="AA15">
-        <v>163933.1051382474</v>
-      </c>
-      <c r="AB15">
-        <v>123541.06865873971</v>
-      </c>
-      <c r="AC15">
-        <v>195643.49281719161</v>
-      </c>
-      <c r="AD15">
-        <v>136709.936030707</v>
-      </c>
-      <c r="AE15">
-        <v>63763.254931923373</v>
-      </c>
-      <c r="AF15">
-        <v>249257.35824880269</v>
-      </c>
-      <c r="AG15">
-        <v>0</v>
-      </c>
-      <c r="AH15">
-        <v>0</v>
-      </c>
-      <c r="AI15">
-        <v>0</v>
-      </c>
-      <c r="AJ15">
-        <v>18182421492.08403</v>
-      </c>
-      <c r="AK15">
-        <v>8480512905.9458084</v>
-      </c>
-      <c r="AL15">
-        <v>33151228647.090771</v>
+        <v>97315408983.74382</v>
       </c>
     </row>
   </sheetData>

--- a/output/Tables/7000 steps/add_cases_prev_7000steps.xlsx
+++ b/output/Tables/7000 steps/add_cases_prev_7000steps.xlsx
@@ -558,22 +558,22 @@
         </is>
       </c>
       <c r="C2">
-        <v>24600.95049746287</v>
+        <v>72284.62766557239</v>
       </c>
       <c r="D2">
-        <v>21089.5996061323</v>
+        <v>48084.4110669566</v>
       </c>
       <c r="E2">
-        <v>27886.51173331669</v>
+        <v>94627.90013825431</v>
       </c>
       <c r="F2">
-        <v>287991.3626591965</v>
+        <v>862722.7836801845</v>
       </c>
       <c r="G2">
-        <v>247758.1126104651</v>
+        <v>573192.0302250907</v>
       </c>
       <c r="H2">
-        <v>325688.1692999321</v>
+        <v>1128350.466164012</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -585,31 +585,31 @@
         <v>0</v>
       </c>
       <c r="L2">
-        <v>38302851233.67314</v>
+        <v>114742130229.4645</v>
       </c>
       <c r="M2">
-        <v>32951828977.19185</v>
+        <v>76234540019.93706</v>
       </c>
       <c r="N2">
-        <v>43316526516.89098</v>
+        <v>150070611999.8136</v>
       </c>
       <c r="O2">
-        <v>60812.32702070134</v>
+        <v>238857.6635929984</v>
       </c>
       <c r="P2">
-        <v>52055.98204925901</v>
+        <v>152710.3587038377</v>
       </c>
       <c r="Q2">
-        <v>68821.86581724428</v>
+        <v>313164.55456395</v>
       </c>
       <c r="R2">
-        <v>710296.9628701867</v>
+        <v>2789892.795100919</v>
       </c>
       <c r="S2">
-        <v>608021.5601061736</v>
+        <v>1783679.54821443</v>
       </c>
       <c r="T2">
-        <v>803849.5591922908</v>
+        <v>3657808.258342886</v>
       </c>
       <c r="U2">
         <v>0</v>
@@ -621,31 +621,31 @@
         <v>0</v>
       </c>
       <c r="X2">
-        <v>94469496061.73483</v>
+        <v>371055741748.4222</v>
       </c>
       <c r="Y2">
-        <v>80866867494.12109</v>
+        <v>237229379912.5192</v>
       </c>
       <c r="Z2">
-        <v>106911991372.5747</v>
+        <v>486488498359.6038</v>
       </c>
       <c r="AA2">
-        <v>36211.37652323848</v>
+        <v>166573.035927426</v>
       </c>
       <c r="AB2">
-        <v>30966.38244312671</v>
+        <v>104625.9476368811</v>
       </c>
       <c r="AC2">
-        <v>40935.3540839276</v>
+        <v>218536.6544256957</v>
       </c>
       <c r="AD2">
-        <v>422305.6002109902</v>
+        <v>1927170.011420734</v>
       </c>
       <c r="AE2">
-        <v>360263.4474957085</v>
+        <v>1210487.517989339</v>
       </c>
       <c r="AF2">
-        <v>478161.3898923587</v>
+        <v>2529457.792178874</v>
       </c>
       <c r="AG2">
         <v>0</v>
@@ -657,13 +657,13 @@
         <v>0</v>
       </c>
       <c r="AJ2">
-        <v>56166644828.06169</v>
+        <v>256313611518.9577</v>
       </c>
       <c r="AK2">
-        <v>47915038516.92924</v>
+        <v>160994839892.5822</v>
       </c>
       <c r="AL2">
-        <v>63595464855.68369</v>
+        <v>336417886359.7902</v>
       </c>
     </row>
     <row r="3">
@@ -678,22 +678,22 @@
         </is>
       </c>
       <c r="C3">
-        <v>34207.77804873243</v>
+        <v>102046.0169206659</v>
       </c>
       <c r="D3">
-        <v>29593.57874547202</v>
+        <v>68124.49124786434</v>
       </c>
       <c r="E3">
-        <v>38536.21438536532</v>
+        <v>133109.0796819582</v>
       </c>
       <c r="F3">
-        <v>320081.8490383019</v>
+        <v>960283.214914445</v>
       </c>
       <c r="G3">
-        <v>276718.0067397309</v>
+        <v>640089.9770229163</v>
       </c>
       <c r="H3">
-        <v>360754.6054286612</v>
+        <v>1253185.008134241</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -705,31 +705,31 @@
         <v>0</v>
       </c>
       <c r="L3">
-        <v>42570885922.09415</v>
+        <v>127717667583.6212</v>
       </c>
       <c r="M3">
-        <v>36803494896.38421</v>
+        <v>85131966944.04787</v>
       </c>
       <c r="N3">
-        <v>47980362522.01193</v>
+        <v>166673606081.8541</v>
       </c>
       <c r="O3">
-        <v>98411.13626092802</v>
+        <v>386537.6516641976</v>
       </c>
       <c r="P3">
-        <v>84240.95234675247</v>
+        <v>247127.5258672922</v>
       </c>
       <c r="Q3">
-        <v>111372.7815803948</v>
+        <v>506786.7184361271</v>
       </c>
       <c r="R3">
-        <v>944848.9808249384</v>
+        <v>3711162.375536832</v>
       </c>
       <c r="S3">
-        <v>808800.5178348175</v>
+        <v>2372680.570727288</v>
       </c>
       <c r="T3">
-        <v>1069294.219801163</v>
+        <v>4865678.139721884</v>
       </c>
       <c r="U3">
         <v>0</v>
@@ -741,31 +741,31 @@
         <v>0</v>
       </c>
       <c r="X3">
-        <v>125664914449.7168</v>
+        <v>493584595946.3987</v>
       </c>
       <c r="Y3">
-        <v>107570468872.0307</v>
+        <v>315566515906.7293</v>
       </c>
       <c r="Z3">
-        <v>142216131233.5547</v>
+        <v>647135192583.0106</v>
       </c>
       <c r="AA3">
-        <v>64203.35821219559</v>
+        <v>284491.6347435317</v>
       </c>
       <c r="AB3">
-        <v>54647.37360128045</v>
+        <v>179003.0346194279</v>
       </c>
       <c r="AC3">
-        <v>72836.56719502952</v>
+        <v>373677.6387541689</v>
       </c>
       <c r="AD3">
-        <v>624767.1317866365</v>
+        <v>2750879.160622388</v>
       </c>
       <c r="AE3">
-        <v>532082.5110950866</v>
+        <v>1732590.593704372</v>
       </c>
       <c r="AF3">
-        <v>708539.6143725018</v>
+        <v>3612493.131587643</v>
       </c>
       <c r="AG3">
         <v>0</v>
@@ -777,19 +777,19 @@
         <v>0</v>
       </c>
       <c r="AJ3">
-        <v>83094028527.62267</v>
+        <v>365866928362.7775</v>
       </c>
       <c r="AK3">
-        <v>70766973975.64651</v>
+        <v>230434548962.6815</v>
       </c>
       <c r="AL3">
-        <v>94235768711.54276</v>
+        <v>480461586501.1565</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>cvd</t>
+          <t>cancer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -798,118 +798,118 @@
         </is>
       </c>
       <c r="C4">
-        <v>18574.73159296868</v>
+        <v>493853.5704780469</v>
       </c>
       <c r="D4">
-        <v>11620.21651129571</v>
+        <v>328226.9507208758</v>
       </c>
       <c r="E4">
-        <v>25438.54197189181</v>
+        <v>645753.0722034946</v>
       </c>
       <c r="F4">
-        <v>18227.96056128219</v>
+        <v>877790.6419214751</v>
       </c>
       <c r="G4">
-        <v>9008.98298610265</v>
+        <v>461701.5622686198</v>
       </c>
       <c r="H4">
-        <v>30294.58102630371</v>
+        <v>1325023.531220962</v>
       </c>
       <c r="I4">
-        <v>1034649699.191539</v>
+        <v>7312489818.068479</v>
       </c>
       <c r="J4">
-        <v>647269300.1121955</v>
+        <v>4860056459.324021</v>
       </c>
       <c r="K4">
-        <v>1416977664.91832</v>
+        <v>9561665740.117142</v>
       </c>
       <c r="L4">
-        <v>2424318754.650531</v>
+        <v>116746155375.5562</v>
       </c>
       <c r="M4">
-        <v>1198194737.151653</v>
+        <v>61406307781.72644</v>
       </c>
       <c r="N4">
-        <v>4029179276.498394</v>
+        <v>176228129652.388</v>
       </c>
       <c r="O4">
-        <v>62026.80069934682</v>
+        <v>1601497.101714449</v>
       </c>
       <c r="P4">
-        <v>40529.90188537803</v>
+        <v>1023895.123091814</v>
       </c>
       <c r="Q4">
-        <v>81329.52738073227</v>
+        <v>2099711.262974003</v>
       </c>
       <c r="R4">
-        <v>60473.36819514075</v>
+        <v>2839088.029911194</v>
       </c>
       <c r="S4">
-        <v>31013.80938055905</v>
+        <v>1436055.674794394</v>
       </c>
       <c r="T4">
-        <v>96656.99331894201</v>
+        <v>4298184.135274271</v>
       </c>
       <c r="U4">
-        <v>3455016852.555022</v>
+        <v>23713367585.0858</v>
       </c>
       <c r="V4">
-        <v>2257596594.819324</v>
+        <v>15160815087.62029</v>
       </c>
       <c r="W4">
-        <v>4530217334.161569</v>
+        <v>31090424670.85612</v>
       </c>
       <c r="X4">
-        <v>8042957969.953719</v>
+        <v>377598707978.1888</v>
       </c>
       <c r="Y4">
-        <v>4124836647.614353</v>
+        <v>190995404747.6544</v>
       </c>
       <c r="Z4">
-        <v>12855380111.41929</v>
+        <v>571658489991.478</v>
       </c>
       <c r="AA4">
-        <v>43452.06910637814</v>
+        <v>1107643.531236402</v>
       </c>
       <c r="AB4">
-        <v>28909.68537408232</v>
+        <v>695668.1723709384</v>
       </c>
       <c r="AC4">
-        <v>55890.98540884045</v>
+        <v>1453958.190770509</v>
       </c>
       <c r="AD4">
-        <v>42245.40763385856</v>
+        <v>1961297.387989719</v>
       </c>
       <c r="AE4">
-        <v>22004.8263944564</v>
+        <v>974354.1125257743</v>
       </c>
       <c r="AF4">
-        <v>66362.4122926383</v>
+        <v>2973160.604053308</v>
       </c>
       <c r="AG4">
-        <v>2420367153.363483</v>
+        <v>16400877767.01732</v>
       </c>
       <c r="AH4">
-        <v>1610327294.707129</v>
+        <v>10300758628.29627</v>
       </c>
       <c r="AI4">
-        <v>3113239669.243249</v>
+        <v>21528758930.73898</v>
       </c>
       <c r="AJ4">
-        <v>5618639215.303188</v>
+        <v>260852552602.6326</v>
       </c>
       <c r="AK4">
-        <v>2926641910.4627</v>
+        <v>129589096965.928</v>
       </c>
       <c r="AL4">
-        <v>8826200834.920893</v>
+        <v>395430360339.09</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>cvd</t>
+          <t>cancer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -918,118 +918,118 @@
         </is>
       </c>
       <c r="C5">
-        <v>21083.53521120251</v>
+        <v>268310.6174033448</v>
       </c>
       <c r="D5">
-        <v>13511.51035665206</v>
+        <v>178827.4807946069</v>
       </c>
       <c r="E5">
-        <v>28536.52674465354</v>
+        <v>350082.5690477403</v>
       </c>
       <c r="F5">
-        <v>16049.30625829875</v>
+        <v>262176.4920945704</v>
       </c>
       <c r="G5">
-        <v>8044.622459631398</v>
+        <v>138259.677997432</v>
       </c>
       <c r="H5">
-        <v>26519.2752860746</v>
+        <v>395254.567807476</v>
       </c>
       <c r="I5">
-        <v>1174395078.3344</v>
+        <v>3972875311.891338</v>
       </c>
       <c r="J5">
-        <v>752618149.88623</v>
+        <v>2647898508.125763</v>
       </c>
       <c r="K5">
-        <v>1589541612.730696</v>
+        <v>5183672599.889918</v>
       </c>
       <c r="L5">
-        <v>2134557732.353734</v>
+        <v>34869473448.57787</v>
       </c>
       <c r="M5">
-        <v>1069934787.130976</v>
+        <v>18388537173.65845</v>
       </c>
       <c r="N5">
-        <v>3527063613.047921</v>
+        <v>52568857518.3943</v>
       </c>
       <c r="O5">
-        <v>82750.82644288789</v>
+        <v>1013285.291970063</v>
       </c>
       <c r="P5">
-        <v>54071.51165060037</v>
+        <v>647830.0008399205</v>
       </c>
       <c r="Q5">
-        <v>108502.8653595535</v>
+        <v>1328511.015023229</v>
       </c>
       <c r="R5">
-        <v>64825.8318465973</v>
+        <v>1016238.853588316</v>
       </c>
       <c r="S5">
-        <v>33245.97342319173</v>
+        <v>514029.7015333133</v>
       </c>
       <c r="T5">
-        <v>103613.709351729</v>
+        <v>1538515.774123152</v>
       </c>
       <c r="U5">
-        <v>4609386534.52175</v>
+        <v>15003715318.20083</v>
       </c>
       <c r="V5">
-        <v>3011891341.961739</v>
+        <v>9592418822.43663</v>
       </c>
       <c r="W5">
-        <v>6043826606.257845</v>
+        <v>19671262599.44902</v>
       </c>
       <c r="X5">
-        <v>8621835635.597441</v>
+        <v>135159767527.246</v>
       </c>
       <c r="Y5">
-        <v>4421714465.2845</v>
+        <v>68365950303.93067</v>
       </c>
       <c r="Z5">
-        <v>13780623343.77996</v>
+        <v>204622597958.3792</v>
       </c>
       <c r="AA5">
-        <v>61667.29123168538</v>
+        <v>744974.6745667181</v>
       </c>
       <c r="AB5">
-        <v>40560.00129394831</v>
+        <v>469002.5200453136</v>
       </c>
       <c r="AC5">
-        <v>79966.33861489996</v>
+        <v>978428.4459754886</v>
       </c>
       <c r="AD5">
-        <v>48776.52558829855</v>
+        <v>754062.3614937454</v>
       </c>
       <c r="AE5">
-        <v>25201.35096356033</v>
+        <v>375770.0235358813</v>
       </c>
       <c r="AF5">
-        <v>77094.43406565441</v>
+        <v>1143261.206315676</v>
       </c>
       <c r="AG5">
-        <v>3434991456.18735</v>
+        <v>11030840006.30949</v>
       </c>
       <c r="AH5">
-        <v>2259273192.075509</v>
+        <v>6944520314.310867</v>
       </c>
       <c r="AI5">
-        <v>4454284993.527149</v>
+        <v>14487589999.5591</v>
       </c>
       <c r="AJ5">
-        <v>6487277903.243707</v>
+        <v>100290294078.6681</v>
       </c>
       <c r="AK5">
-        <v>3351779678.153524</v>
+        <v>49977413130.27222</v>
       </c>
       <c r="AL5">
-        <v>10253559730.73204</v>
+        <v>152053740439.9849</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>cancer</t>
+          <t>cvd</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1038,118 +1038,118 @@
         </is>
       </c>
       <c r="C6">
-        <v>19639.00221098947</v>
+        <v>117886.5436723316</v>
       </c>
       <c r="D6">
-        <v>945.2686101049807</v>
+        <v>78284.21539504752</v>
       </c>
       <c r="E6">
-        <v>39758.20605733652</v>
+        <v>154304.8252597238</v>
       </c>
       <c r="F6">
-        <v>34999.51625488111</v>
+        <v>115659.0802036981</v>
       </c>
       <c r="G6">
-        <v>1312.171796566891</v>
+        <v>60245.46088767755</v>
       </c>
       <c r="H6">
-        <v>81802.08996450927</v>
+        <v>184413.4626555989</v>
       </c>
       <c r="I6">
-        <v>290794705.7381204</v>
+        <v>6566516255.636278</v>
       </c>
       <c r="J6">
-        <v>13996592.30982444</v>
+        <v>4360587365.934971</v>
       </c>
       <c r="K6">
-        <v>588699757.0909815</v>
+        <v>8595087376.617168</v>
       </c>
       <c r="L6">
-        <v>4654935661.899187</v>
+        <v>15382657667.09185</v>
       </c>
       <c r="M6">
-        <v>174518848.9433964</v>
+        <v>8012646298.061114</v>
       </c>
       <c r="N6">
-        <v>10879677965.27973</v>
+        <v>24526990533.19465</v>
       </c>
       <c r="O6">
-        <v>78495.71499848703</v>
+        <v>377828.9153114689</v>
       </c>
       <c r="P6">
-        <v>-1638.804568292139</v>
+        <v>241559.7151792117</v>
       </c>
       <c r="Q6">
-        <v>156583.5245758266</v>
+        <v>495368.7572131407</v>
       </c>
       <c r="R6">
-        <v>139154.9473383052</v>
+        <v>368366.3650677601</v>
       </c>
       <c r="S6">
-        <v>-2298.491854388779</v>
+        <v>184843.4516761787</v>
       </c>
       <c r="T6">
-        <v>320532.081265252</v>
+        <v>588726.5818257635</v>
       </c>
       <c r="U6">
-        <v>1162286051.982595</v>
+        <v>21045826240.67933</v>
       </c>
       <c r="V6">
-        <v>-24265779.24270174</v>
+        <v>13455359254.91232</v>
       </c>
       <c r="W6">
-        <v>2318532248.394261</v>
+        <v>27593030514.28617</v>
       </c>
       <c r="X6">
-        <v>18507607995.9946</v>
+        <v>48992726554.01208</v>
       </c>
       <c r="Y6">
-        <v>-305699416.6337076</v>
+        <v>24584179072.93177</v>
       </c>
       <c r="Z6">
-        <v>42630766808.27852</v>
+        <v>78300635382.82654</v>
       </c>
       <c r="AA6">
-        <v>58856.71278749756</v>
+        <v>259942.3716391373</v>
       </c>
       <c r="AB6">
-        <v>-2584.07317839712</v>
+        <v>163275.4997841642</v>
       </c>
       <c r="AC6">
-        <v>116825.3185184901</v>
+        <v>341063.9319534169</v>
       </c>
       <c r="AD6">
-        <v>104155.4310834241</v>
+        <v>252707.2848640619</v>
       </c>
       <c r="AE6">
-        <v>-3610.66365095567</v>
+        <v>124597.9907885011</v>
       </c>
       <c r="AF6">
-        <v>238729.9913007428</v>
+        <v>404313.1191701646</v>
       </c>
       <c r="AG6">
-        <v>871491346.2444751</v>
+        <v>14479309985.04305</v>
       </c>
       <c r="AH6">
-        <v>-38262371.55252618</v>
+        <v>9094771888.977354</v>
       </c>
       <c r="AI6">
-        <v>1729832491.303279</v>
+        <v>18997943137.669</v>
       </c>
       <c r="AJ6">
-        <v>13852672334.09541</v>
+        <v>33610068886.92023</v>
       </c>
       <c r="AK6">
-        <v>-480218265.577104</v>
+        <v>16571532774.87065</v>
       </c>
       <c r="AL6">
-        <v>31751088842.99879</v>
+        <v>53773644849.63189</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>cancer</t>
+          <t>cvd</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1158,112 +1158,112 @@
         </is>
       </c>
       <c r="C7">
-        <v>10911.63767997198</v>
+        <v>135035.9127274927</v>
       </c>
       <c r="D7">
-        <v>460.823121919975</v>
+        <v>90022.72424851448</v>
       </c>
       <c r="E7">
-        <v>22052.50879113228</v>
+        <v>176137.8008177906</v>
       </c>
       <c r="F7">
-        <v>10507.83350574811</v>
+        <v>102600.5343959853</v>
       </c>
       <c r="G7">
-        <v>393.2500430385832</v>
+        <v>53643.65289969727</v>
       </c>
       <c r="H7">
-        <v>24534.90924659295</v>
+        <v>163218.2456202052</v>
       </c>
       <c r="I7">
-        <v>161568619.1273454</v>
+        <v>7521770410.746783</v>
       </c>
       <c r="J7">
-        <v>6823407.966269104</v>
+        <v>5014445786.090731</v>
       </c>
       <c r="K7">
-        <v>326531497.6702951</v>
+        <v>9811227781.152529</v>
       </c>
       <c r="L7">
-        <v>1397541856.264498</v>
+        <v>13645871074.66604</v>
       </c>
       <c r="M7">
-        <v>52302255.72413157</v>
+        <v>7134605835.659737</v>
       </c>
       <c r="N7">
-        <v>3263142929.796862</v>
+        <v>21708026667.48729</v>
       </c>
       <c r="O7">
-        <v>49665.12484193227</v>
+        <v>504066.8653473335</v>
       </c>
       <c r="P7">
-        <v>-1036.890147154239</v>
+        <v>322268.2105317547</v>
       </c>
       <c r="Q7">
-        <v>99072.16331997342</v>
+        <v>660878.4201537042</v>
       </c>
       <c r="R7">
-        <v>49809.89059315866</v>
+        <v>394878.8822671145</v>
       </c>
       <c r="S7">
-        <v>-822.7348720705954</v>
+        <v>198147.2319788455</v>
       </c>
       <c r="T7">
-        <v>114733.0239046752</v>
+        <v>631099.1356377783</v>
       </c>
       <c r="U7">
-        <v>735391503.5344914</v>
+        <v>28077532533.5774</v>
       </c>
       <c r="V7">
-        <v>-15353232.40891281</v>
+        <v>17950983863.03995</v>
       </c>
       <c r="W7">
-        <v>1466961522.278845</v>
+        <v>36812249759.40205</v>
       </c>
       <c r="X7">
-        <v>6624715448.890102</v>
+        <v>52518891341.52622</v>
       </c>
       <c r="Y7">
-        <v>-109423737.9853892</v>
+        <v>26353581853.18645</v>
       </c>
       <c r="Z7">
-        <v>15259492179.32179</v>
+        <v>83936185039.82452</v>
       </c>
       <c r="AA7">
-        <v>38753.48716196029</v>
+        <v>369030.9526198409</v>
       </c>
       <c r="AB7">
-        <v>-1497.713269074214</v>
+        <v>232245.4862832402</v>
       </c>
       <c r="AC7">
-        <v>77019.65452884114</v>
+        <v>484740.6193359137</v>
       </c>
       <c r="AD7">
-        <v>39302.05708741055</v>
+        <v>292278.3478711292</v>
       </c>
       <c r="AE7">
-        <v>-1215.984915109179</v>
+        <v>144503.5790791482</v>
       </c>
       <c r="AF7">
-        <v>90198.1146580822</v>
+        <v>467880.8900175731</v>
       </c>
       <c r="AG7">
-        <v>573822884.407146</v>
+        <v>20555762122.83062</v>
       </c>
       <c r="AH7">
-        <v>-22176640.37518191</v>
+        <v>12936538076.94922</v>
       </c>
       <c r="AI7">
-        <v>1140430024.60855</v>
+        <v>27001021978.24952</v>
       </c>
       <c r="AJ7">
-        <v>5227173592.625605</v>
+        <v>38873020266.86018</v>
       </c>
       <c r="AK7">
-        <v>-161725993.7095208</v>
+        <v>19218976017.52671</v>
       </c>
       <c r="AL7">
-        <v>11996349249.52493</v>
+        <v>62228158372.33723</v>
       </c>
     </row>
     <row r="8">
@@ -1278,112 +1278,112 @@
         </is>
       </c>
       <c r="C8">
-        <v>3079.152031990513</v>
+        <v>34465.89219477386</v>
       </c>
       <c r="D8">
-        <v>-81.5652831526404</v>
+        <v>22889.33619511552</v>
       </c>
       <c r="E8">
-        <v>5771.468572331606</v>
+        <v>45065.06656815319</v>
       </c>
       <c r="F8">
-        <v>6408.052173675374</v>
+        <v>71849.66141899109</v>
       </c>
       <c r="G8">
-        <v>-127.5342819378562</v>
+        <v>35529.94280500161</v>
       </c>
       <c r="H8">
-        <v>15253.19523882721</v>
+        <v>119257.8196139966</v>
       </c>
       <c r="I8">
-        <v>231555311.9577184</v>
+        <v>2591869558.939158</v>
       </c>
       <c r="J8">
-        <v>-6133790.858361734</v>
+        <v>1721300971.20888</v>
       </c>
       <c r="K8">
-        <v>434020208.1079093</v>
+        <v>3388938070.991676</v>
       </c>
       <c r="L8">
-        <v>852270939.0988246</v>
+        <v>9556004968.725815</v>
       </c>
       <c r="M8">
-        <v>-16962059.49773488</v>
+        <v>4725482393.065215</v>
       </c>
       <c r="N8">
-        <v>2028674966.764018</v>
+        <v>15861290008.66155</v>
       </c>
       <c r="O8">
-        <v>12056.6702807696</v>
+        <v>110697.7559144882</v>
       </c>
       <c r="P8">
-        <v>0</v>
+        <v>70773.08619335832</v>
       </c>
       <c r="Q8">
-        <v>21984.68083159204</v>
+        <v>145135.0268637823</v>
       </c>
       <c r="R8">
-        <v>25226.50104720105</v>
+        <v>231615.9429153254</v>
       </c>
       <c r="S8">
-        <v>0</v>
+        <v>110199.9339510133</v>
       </c>
       <c r="T8">
-        <v>58401.25858151415</v>
+        <v>385544.2932301505</v>
       </c>
       <c r="U8">
-        <v>906673661.7841525</v>
+        <v>8324581942.525422</v>
       </c>
       <c r="V8">
-        <v>0</v>
+        <v>5322206854.826803</v>
       </c>
       <c r="W8">
-        <v>1653269983.216557</v>
+        <v>10914299155.18317</v>
       </c>
       <c r="X8">
-        <v>3355124639.277739</v>
+        <v>30804920407.73828</v>
       </c>
       <c r="Y8">
-        <v>0</v>
+        <v>14656591215.48477</v>
       </c>
       <c r="Z8">
-        <v>7767367391.341382</v>
+        <v>51277390999.61002</v>
       </c>
       <c r="AA8">
-        <v>8977.518248779092</v>
+        <v>76231.86371971437</v>
       </c>
       <c r="AB8">
-        <v>81.5652831526404</v>
+        <v>47883.7499982428</v>
       </c>
       <c r="AC8">
-        <v>16213.21225926043</v>
+        <v>100069.9602956291</v>
       </c>
       <c r="AD8">
-        <v>18818.44887352567</v>
+        <v>159766.2814963343</v>
       </c>
       <c r="AE8">
-        <v>127.5342819378562</v>
+        <v>74669.99114601171</v>
       </c>
       <c r="AF8">
-        <v>43148.06334268694</v>
+        <v>266286.4736161539</v>
       </c>
       <c r="AG8">
-        <v>675118349.8264341</v>
+        <v>5732712383.586264</v>
       </c>
       <c r="AH8">
-        <v>6133790.858361734</v>
+        <v>3600905883.617923</v>
       </c>
       <c r="AI8">
-        <v>1219249775.108648</v>
+        <v>7525361084.191498</v>
       </c>
       <c r="AJ8">
-        <v>2502853700.178915</v>
+        <v>21248915439.01246</v>
       </c>
       <c r="AK8">
-        <v>16962059.49773488</v>
+        <v>9931108822.419556</v>
       </c>
       <c r="AL8">
-        <v>5738692424.577364</v>
+        <v>35416100990.94846</v>
       </c>
     </row>
     <row r="9">
@@ -1398,112 +1398,112 @@
         </is>
       </c>
       <c r="C9">
-        <v>3415.492903387784</v>
+        <v>38037.68714566478</v>
       </c>
       <c r="D9">
-        <v>-87.66933312498075</v>
+        <v>25352.85630764702</v>
       </c>
       <c r="E9">
-        <v>6389.26496163765</v>
+        <v>49653.47049522461</v>
       </c>
       <c r="F9">
-        <v>6139.17200634873</v>
+        <v>69441.81173547711</v>
       </c>
       <c r="G9">
-        <v>-127.3253159773389</v>
+        <v>34466.93513057644</v>
       </c>
       <c r="H9">
-        <v>14631.56693980678</v>
+        <v>115138.653168651</v>
       </c>
       <c r="I9">
-        <v>256848481.8276645</v>
+        <v>2860472111.041142</v>
       </c>
       <c r="J9">
-        <v>-6592821.520331657</v>
+        <v>1906560147.191354</v>
       </c>
       <c r="K9">
-        <v>480479114.3801115</v>
+        <v>3733990634.711379</v>
       </c>
       <c r="L9">
-        <v>816509876.8443811</v>
+        <v>9235760960.818455</v>
       </c>
       <c r="M9">
-        <v>-16934267.02498607</v>
+        <v>4584102372.366666</v>
       </c>
       <c r="N9">
-        <v>1945998402.994302</v>
+        <v>15313440871.43058</v>
       </c>
       <c r="O9">
-        <v>16096.82026023769</v>
+        <v>147792.2045367108</v>
       </c>
       <c r="P9">
-        <v>0</v>
+        <v>94488.91121571569</v>
       </c>
       <c r="Q9">
-        <v>29351.67401809747</v>
+        <v>193769.2900681982</v>
       </c>
       <c r="R9">
-        <v>29628.57642476932</v>
+        <v>272033.3927016482</v>
       </c>
       <c r="S9">
-        <v>0</v>
+        <v>129430.0449738508</v>
       </c>
       <c r="T9">
-        <v>68592.39614512841</v>
+        <v>452822.5510041864</v>
       </c>
       <c r="U9">
-        <v>1210496980.390138</v>
+        <v>11114121573.36506</v>
       </c>
       <c r="V9">
-        <v>0</v>
+        <v>7105660612.333069</v>
       </c>
       <c r="W9">
-        <v>2207275237.834931</v>
+        <v>14571644382.41854</v>
       </c>
       <c r="X9">
-        <v>3940600664.494319</v>
+        <v>36180441229.31921</v>
       </c>
       <c r="Y9">
-        <v>0</v>
+        <v>17214195981.52216</v>
       </c>
       <c r="Z9">
-        <v>9122788687.302078</v>
+        <v>60225399283.5568</v>
       </c>
       <c r="AA9">
-        <v>12681.3273568499</v>
+        <v>109754.517391046</v>
       </c>
       <c r="AB9">
-        <v>87.66933312498075</v>
+        <v>69136.05490806868</v>
       </c>
       <c r="AC9">
-        <v>22962.40905645982</v>
+        <v>144115.8195729736</v>
       </c>
       <c r="AD9">
-        <v>23489.40441842059</v>
+        <v>202591.5809661711</v>
       </c>
       <c r="AE9">
-        <v>127.3253159773389</v>
+        <v>94963.1098432744</v>
       </c>
       <c r="AF9">
-        <v>53960.82920532163</v>
+        <v>337683.8978355355</v>
       </c>
       <c r="AG9">
-        <v>953648498.5624734</v>
+        <v>8253649462.323915</v>
       </c>
       <c r="AH9">
-        <v>6592821.520331657</v>
+        <v>5199100465.141715</v>
       </c>
       <c r="AI9">
-        <v>1726796123.45482</v>
+        <v>10837653747.70716</v>
       </c>
       <c r="AJ9">
-        <v>3124090787.649939</v>
+        <v>26944680268.50075</v>
       </c>
       <c r="AK9">
-        <v>16934267.02498607</v>
+        <v>12630093609.1555</v>
       </c>
       <c r="AL9">
-        <v>7176790284.307776</v>
+        <v>44911958412.12622</v>
       </c>
     </row>
     <row r="10">
@@ -1518,112 +1518,112 @@
         </is>
       </c>
       <c r="C10">
-        <v>8289.94422304287</v>
+        <v>34578.19430233459</v>
       </c>
       <c r="D10">
-        <v>6022.233564455917</v>
+        <v>22976.43108481871</v>
       </c>
       <c r="E10">
-        <v>10331.62833484003</v>
+        <v>45290.09011992066</v>
       </c>
       <c r="F10">
-        <v>15290.61964606795</v>
+        <v>63821.90412607118</v>
       </c>
       <c r="G10">
-        <v>8925.728926396978</v>
+        <v>33947.24246429134</v>
       </c>
       <c r="H10">
-        <v>21658.62276182612</v>
+        <v>95135.70951498931</v>
       </c>
       <c r="I10">
-        <v>139594370.7718183</v>
+        <v>582262213.8570119</v>
       </c>
       <c r="J10">
-        <v>101408390.9918734</v>
+        <v>386900123.0372596</v>
       </c>
       <c r="K10">
-        <v>173974289.5303712</v>
+        <v>762639827.5293336</v>
       </c>
       <c r="L10">
-        <v>2033652412.927037</v>
+        <v>8488313248.767467</v>
       </c>
       <c r="M10">
-        <v>1187121947.210798</v>
+        <v>4514983247.750748</v>
       </c>
       <c r="N10">
-        <v>2880596827.322874</v>
+        <v>12653049365.49358</v>
       </c>
       <c r="O10">
-        <v>28474.64780985158</v>
+        <v>112326.0658534857</v>
       </c>
       <c r="P10">
-        <v>21075.50843496856</v>
+        <v>71814.12373481671</v>
       </c>
       <c r="Q10">
-        <v>34599.02779288883</v>
+        <v>147269.8922437222</v>
       </c>
       <c r="R10">
-        <v>50850.24704737742</v>
+        <v>200592.7601511383</v>
       </c>
       <c r="S10">
-        <v>30181.18019335427</v>
+        <v>102841.410234836</v>
       </c>
       <c r="T10">
-        <v>70369.03924043707</v>
+        <v>299524.0469838683</v>
       </c>
       <c r="U10">
-        <v>479484594.4700922</v>
+        <v>1891458622.90685</v>
       </c>
       <c r="V10">
-        <v>354890486.5364367</v>
+        <v>1209278029.570587</v>
       </c>
       <c r="W10">
-        <v>582613029.0044533</v>
+        <v>2479877715.492043</v>
       </c>
       <c r="X10">
-        <v>6763082857.301196</v>
+        <v>26678837100.1014</v>
       </c>
       <c r="Y10">
-        <v>4014096965.716117</v>
+        <v>13677907561.23319</v>
       </c>
       <c r="Z10">
-        <v>9359082218.97813</v>
+        <v>39836698248.85449</v>
       </c>
       <c r="AA10">
-        <v>20184.7035868087</v>
+        <v>77747.87155115113</v>
       </c>
       <c r="AB10">
-        <v>15053.27487051265</v>
+        <v>48837.692649998</v>
       </c>
       <c r="AC10">
-        <v>24267.3994580488</v>
+        <v>101979.8021238015</v>
       </c>
       <c r="AD10">
-        <v>35559.62740130947</v>
+        <v>136770.8560250672</v>
       </c>
       <c r="AE10">
-        <v>21255.45126695729</v>
+        <v>68894.16777054468</v>
       </c>
       <c r="AF10">
-        <v>48710.41647861095</v>
+        <v>204388.337468879</v>
       </c>
       <c r="AG10">
-        <v>339890223.6982739</v>
+        <v>1309196409.049838</v>
       </c>
       <c r="AH10">
-        <v>253482095.5445634</v>
+        <v>822377906.5333271</v>
       </c>
       <c r="AI10">
-        <v>408638739.4740821</v>
+        <v>1717237887.962709</v>
       </c>
       <c r="AJ10">
-        <v>4729430444.374159</v>
+        <v>18190523851.33393</v>
       </c>
       <c r="AK10">
-        <v>2826975018.50532</v>
+        <v>9162924313.482443</v>
       </c>
       <c r="AL10">
-        <v>6478485391.655256</v>
+        <v>27183648883.36091</v>
       </c>
     </row>
     <row r="11">
@@ -1638,112 +1638,112 @@
         </is>
       </c>
       <c r="C11">
-        <v>5199.494302381868</v>
+        <v>22179.61976357391</v>
       </c>
       <c r="D11">
-        <v>3806.472494643124</v>
+        <v>14812.73631561984</v>
       </c>
       <c r="E11">
-        <v>6449.432056470911</v>
+        <v>28924.54663747968</v>
       </c>
       <c r="F11">
-        <v>5399.633159346871</v>
+        <v>22945.96982162615</v>
       </c>
       <c r="G11">
-        <v>3171.963608625719</v>
+        <v>12259.37490255628</v>
       </c>
       <c r="H11">
-        <v>7618.96876310422</v>
+        <v>34083.43398095013</v>
       </c>
       <c r="I11">
-        <v>87554284.55780822</v>
+        <v>373482617.198818</v>
       </c>
       <c r="J11">
-        <v>64097190.33729566</v>
+        <v>249431666.8187215</v>
       </c>
       <c r="K11">
-        <v>108601986.3989135</v>
+        <v>487060440.8285231</v>
       </c>
       <c r="L11">
-        <v>718151210.1931338</v>
+        <v>3051813986.276278</v>
       </c>
       <c r="M11">
-        <v>421871159.9472206</v>
+        <v>1630496862.039985</v>
       </c>
       <c r="N11">
-        <v>1013322845.492861</v>
+        <v>4533096719.466367</v>
       </c>
       <c r="O11">
-        <v>20961.21919971283</v>
+        <v>82687.28392776458</v>
       </c>
       <c r="P11">
-        <v>15514.44481423692</v>
+        <v>52864.97656768151</v>
       </c>
       <c r="Q11">
-        <v>25469.59704319076</v>
+        <v>108410.6997021651</v>
       </c>
       <c r="R11">
-        <v>21844.37691375475</v>
+        <v>86171.141997193</v>
       </c>
       <c r="S11">
-        <v>12965.30723304689</v>
+        <v>44178.87145009841</v>
       </c>
       <c r="T11">
-        <v>30229.30871495516</v>
+        <v>128670.2928100386</v>
       </c>
       <c r="U11">
-        <v>352965970.1039641</v>
+        <v>1392371174.059618</v>
       </c>
       <c r="V11">
-        <v>261247736.226935</v>
+        <v>890193340.4231979</v>
       </c>
       <c r="W11">
-        <v>428882544.6102901</v>
+        <v>1825527772.28476</v>
       </c>
       <c r="X11">
-        <v>2905302129.529381</v>
+        <v>11460761885.62667</v>
       </c>
       <c r="Y11">
-        <v>1724385861.995237</v>
+        <v>5875789902.863089</v>
       </c>
       <c r="Z11">
-        <v>4020498059.089036</v>
+        <v>17113148943.73514</v>
       </c>
       <c r="AA11">
-        <v>15761.72489733097</v>
+        <v>60507.66416419068</v>
       </c>
       <c r="AB11">
-        <v>11707.97231959379</v>
+        <v>38052.24025206167</v>
       </c>
       <c r="AC11">
-        <v>19020.16498671985</v>
+        <v>79486.15306468545</v>
       </c>
       <c r="AD11">
-        <v>16444.74375440787</v>
+        <v>63225.17217556686</v>
       </c>
       <c r="AE11">
-        <v>9793.343624421172</v>
+        <v>31919.49654754213</v>
       </c>
       <c r="AF11">
-        <v>22610.33995185094</v>
+        <v>94586.85882908848</v>
       </c>
       <c r="AG11">
-        <v>265411685.5461559</v>
+        <v>1018888556.8608</v>
       </c>
       <c r="AH11">
-        <v>197150545.8896394</v>
+        <v>640761673.6044763</v>
       </c>
       <c r="AI11">
-        <v>320280558.2113765</v>
+        <v>1338467331.456237</v>
       </c>
       <c r="AJ11">
-        <v>2187150919.336247</v>
+        <v>8408947899.350391</v>
       </c>
       <c r="AK11">
-        <v>1302514702.048016</v>
+        <v>4245293040.823104</v>
       </c>
       <c r="AL11">
-        <v>3007175213.596175</v>
+        <v>12580052224.26877</v>
       </c>
     </row>
     <row r="12">
@@ -1758,22 +1758,22 @@
         </is>
       </c>
       <c r="C12">
-        <v>107153.1553122108</v>
+        <v>757338.2337135491</v>
       </c>
       <c r="D12">
-        <v>79218.0166650977</v>
+        <v>503307.8258941504</v>
       </c>
       <c r="E12">
-        <v>129974.2989825751</v>
+        <v>990407.5383711181</v>
       </c>
       <c r="F12">
-        <v>319829.3050394356</v>
+        <v>2256046.518983672</v>
       </c>
       <c r="G12">
-        <v>146325.7040484844</v>
+        <v>927611.059660397</v>
       </c>
       <c r="H12">
-        <v>592720.3022994641</v>
+        <v>4507562.785151743</v>
       </c>
       <c r="I12">
         <v>0</v>
@@ -1785,31 +1785,31 @@
         <v>0</v>
       </c>
       <c r="L12">
-        <v>42537297570.24494</v>
+        <v>300054187024.8284</v>
       </c>
       <c r="M12">
-        <v>19461318638.44842</v>
+        <v>123372270934.8328</v>
       </c>
       <c r="N12">
-        <v>78831800205.82874</v>
+        <v>599505850425.1819</v>
       </c>
       <c r="O12">
-        <v>412256.2595949728</v>
+        <v>2427778.301906202</v>
       </c>
       <c r="P12">
-        <v>309599.5736041024</v>
+        <v>1552166.632464546</v>
       </c>
       <c r="Q12">
-        <v>493594.8705806515</v>
+        <v>3183042.566270728</v>
       </c>
       <c r="R12">
-        <v>1215817.310622175</v>
+        <v>7159951.649273743</v>
       </c>
       <c r="S12">
-        <v>564819.8955165836</v>
+        <v>2831704.788760517</v>
       </c>
       <c r="T12">
-        <v>2224409.18047226</v>
+        <v>14344535.42419801</v>
       </c>
       <c r="U12">
         <v>0</v>
@@ -1821,31 +1821,31 @@
         <v>0</v>
       </c>
       <c r="X12">
-        <v>161703702312.7493</v>
+        <v>952273569353.4078</v>
       </c>
       <c r="Y12">
-        <v>75121046103.70561</v>
+        <v>376616736905.1488</v>
       </c>
       <c r="Z12">
-        <v>295846421002.8105</v>
+        <v>1907823211418.336</v>
       </c>
       <c r="AA12">
-        <v>305103.104282762</v>
+        <v>1670440.068192653</v>
       </c>
       <c r="AB12">
-        <v>230381.5569390047</v>
+        <v>1048858.806570396</v>
       </c>
       <c r="AC12">
-        <v>363620.5715980764</v>
+        <v>2192635.02789961</v>
       </c>
       <c r="AD12">
-        <v>895988.0055827398</v>
+        <v>4903905.130290071</v>
       </c>
       <c r="AE12">
-        <v>418494.1914680992</v>
+        <v>1904093.72910012</v>
       </c>
       <c r="AF12">
-        <v>1631688.878172796</v>
+        <v>9836972.63904627</v>
       </c>
       <c r="AG12">
         <v>0</v>
@@ -1857,13 +1857,13 @@
         <v>0</v>
       </c>
       <c r="AJ12">
-        <v>119166404742.5044</v>
+        <v>652219382328.5793</v>
       </c>
       <c r="AK12">
-        <v>55659727465.25719</v>
+        <v>253244465970.316</v>
       </c>
       <c r="AL12">
-        <v>217014620796.9818</v>
+        <v>1308317360993.154</v>
       </c>
     </row>
     <row r="13">
@@ -1878,22 +1878,22 @@
         </is>
       </c>
       <c r="C13">
-        <v>44955.61251605048</v>
+        <v>316394.7589704457</v>
       </c>
       <c r="D13">
-        <v>33286.7661588011</v>
+        <v>210975.1801000892</v>
       </c>
       <c r="E13">
-        <v>54504.37393346629</v>
+        <v>413107.0182192521</v>
       </c>
       <c r="F13">
-        <v>111660.4564958147</v>
+        <v>794459.7810503439</v>
       </c>
       <c r="G13">
-        <v>51036.47626420549</v>
+        <v>327638.2462736432</v>
       </c>
       <c r="H13">
-        <v>207035.5004800728</v>
+        <v>1586199.486621887</v>
       </c>
       <c r="I13">
         <v>0</v>
@@ -1905,31 +1905,31 @@
         <v>0</v>
       </c>
       <c r="L13">
-        <v>14850840713.94335</v>
+        <v>105663150879.6957</v>
       </c>
       <c r="M13">
-        <v>6787851343.139331</v>
+        <v>43575886754.39455</v>
       </c>
       <c r="N13">
-        <v>27535721563.84969</v>
+        <v>210964531720.711</v>
       </c>
       <c r="O13">
-        <v>205076.2777874958</v>
+        <v>1207694.791432209</v>
       </c>
       <c r="P13">
-        <v>154009.8583868761</v>
+        <v>772123.0377545063</v>
       </c>
       <c r="Q13">
-        <v>245538.0517281426</v>
+        <v>1583399.903184671</v>
       </c>
       <c r="R13">
-        <v>513091.1006324803</v>
+        <v>3021594.97163374</v>
       </c>
       <c r="S13">
-        <v>238361.5197100842</v>
+        <v>1195017.141175513</v>
       </c>
       <c r="T13">
-        <v>938730.3048691241</v>
+        <v>6053585.028409338</v>
       </c>
       <c r="U13">
         <v>0</v>
@@ -1941,31 +1941,31 @@
         <v>0</v>
       </c>
       <c r="X13">
-        <v>68241116384.11989</v>
+        <v>401872131227.2874</v>
       </c>
       <c r="Y13">
-        <v>31702082121.4412</v>
+        <v>158937279776.3433</v>
       </c>
       <c r="Z13">
-        <v>124851130547.5935</v>
+        <v>805126808778.4419</v>
       </c>
       <c r="AA13">
-        <v>160120.6652714454</v>
+        <v>891300.0324617629</v>
       </c>
       <c r="AB13">
-        <v>120723.0922280751</v>
+        <v>561147.8576544172</v>
       </c>
       <c r="AC13">
-        <v>191033.6777946763</v>
+        <v>1170292.884965419</v>
       </c>
       <c r="AD13">
-        <v>401430.6441366656</v>
+        <v>2227135.190583396</v>
       </c>
       <c r="AE13">
-        <v>187325.0434458787</v>
+        <v>867378.8949018702</v>
       </c>
       <c r="AF13">
-        <v>731694.8043890513</v>
+        <v>4467385.541787451</v>
       </c>
       <c r="AG13">
         <v>0</v>
@@ -1977,13 +1977,13 @@
         <v>0</v>
       </c>
       <c r="AJ13">
-        <v>53390275670.17654</v>
+        <v>296208980347.5917</v>
       </c>
       <c r="AK13">
-        <v>24914230778.30187</v>
+        <v>115361393021.9487</v>
       </c>
       <c r="AL13">
-        <v>97315408983.74382</v>
+        <v>594162277057.731</v>
       </c>
     </row>
   </sheetData>
